--- a/outputs/validation_frame_member_loads.xlsx
+++ b/outputs/validation_frame_member_loads.xlsx
@@ -643,25 +643,25 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>3.595119805279563</v>
+        <v>3.595119805279023</v>
       </c>
       <c r="F6" t="n">
-        <v>5.264656553662592e-05</v>
+        <v>5.264656576807992e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007516730126563289</v>
+        <v>0.007516730126564649</v>
       </c>
       <c r="H6" t="n">
-        <v>-5.817587131184721e-06</v>
+        <v>-5.81758716827277e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5733905572099365</v>
+        <v>0.5733905572098467</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01497636114535011</v>
+        <v>0.01497636114528572</v>
       </c>
       <c r="K6" t="n">
-        <v>3.595127663702197</v>
+        <v>3.595127663701657</v>
       </c>
     </row>
     <row r="7">
@@ -678,25 +678,25 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>3.595119805277692</v>
+        <v>3.595119805277716</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.264656732975187e-05</v>
+        <v>-5.264656709829736e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007516730126563006</v>
+        <v>0.007516730126563812</v>
       </c>
       <c r="H7" t="n">
-        <v>5.817587439357226e-06</v>
+        <v>5.817587402268885e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5733905572095976</v>
+        <v>0.5733905572096085</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.01497636114489171</v>
+        <v>-0.0149763611449562</v>
       </c>
       <c r="K7" t="n">
-        <v>3.595127663700326</v>
+        <v>3.59512766370035</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +713,25 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>3.596176627224334</v>
+        <v>3.596176627224358</v>
       </c>
       <c r="F8" t="n">
-        <v>5.264656733141418e-05</v>
+        <v>5.264656709531542e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.007516730126563017</v>
+        <v>-0.007516730126563806</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.817587439646455e-06</v>
+        <v>-5.817587401731315e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5737082536248554</v>
+        <v>0.5737082536248662</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04500689564371815</v>
+        <v>0.04500689564365364</v>
       </c>
       <c r="K8" t="n">
-        <v>3.596184483337589</v>
+        <v>3.596184483337613</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +748,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>3.596176627226205</v>
+        <v>3.596176627225665</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.264656553496323e-05</v>
+        <v>-5.264656577106183e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.00751673012656329</v>
+        <v>-0.007516730126564661</v>
       </c>
       <c r="H9" t="n">
-        <v>5.817587130890855e-06</v>
+        <v>5.817587168809183e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5737082536251945</v>
+        <v>0.5737082536251048</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.04500689564325982</v>
+        <v>-0.0450068956433242</v>
       </c>
       <c r="K9" t="n">
-        <v>3.59618448333946</v>
+        <v>3.59618448333892</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>8.113133295381624</v>
+        <v>8.113133295380457</v>
       </c>
       <c r="F10" t="n">
-        <v>5.27481476618041e-05</v>
+        <v>5.274814816710414e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01202133708507339</v>
+        <v>0.01202133708507639</v>
       </c>
       <c r="H10" t="n">
-        <v>1.276246312356512e-06</v>
+        <v>1.276246291459122e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4768655535134581</v>
+        <v>0.4768655535134355</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01500508180328185</v>
+        <v>0.01500508180312803</v>
       </c>
       <c r="K10" t="n">
-        <v>8.113142201635418</v>
+        <v>8.11314220163425</v>
       </c>
     </row>
     <row r="11">
@@ -818,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>8.113133295376661</v>
+        <v>8.11313329537693</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.274815211736379e-05</v>
+        <v>-5.274815161206213e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01202133708507298</v>
+        <v>0.01202133708507474</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.276246011702428e-06</v>
+        <v>-1.276246032599108e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4768655535130946</v>
+        <v>0.4768655535131607</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.01500508180210351</v>
+        <v>-0.01500508180225687</v>
       </c>
       <c r="K11" t="n">
-        <v>8.113142201630454</v>
+        <v>8.113142201630723</v>
       </c>
     </row>
     <row r="12">
@@ -853,25 +853,25 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>8.114175479580663</v>
+        <v>8.114175479580929</v>
       </c>
       <c r="F12" t="n">
-        <v>5.274815212167277e-05</v>
+        <v>5.274815160420837e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.012021337085073</v>
+        <v>-0.01202133708507473</v>
       </c>
       <c r="H12" t="n">
-        <v>1.27624601135778e-06</v>
+        <v>1.276246033172293e-06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4758775876426199</v>
+        <v>0.4758775876426864</v>
       </c>
       <c r="J12" t="n">
-        <v>0.04505488004389391</v>
+        <v>0.04505488004373993</v>
       </c>
       <c r="K12" t="n">
-        <v>8.114184384690539</v>
+        <v>8.114184384690805</v>
       </c>
     </row>
     <row r="13">
@@ -888,25 +888,25 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>8.114175479585626</v>
+        <v>8.114175479584461</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.27481476574951e-05</v>
+        <v>-5.274814817495947e-05</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.01202133708507339</v>
+        <v>-0.0120213370850764</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.276246312679776e-06</v>
+        <v>-1.276246290880136e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>0.475877587642983</v>
+        <v>0.4758775876429612</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.04505488004271615</v>
+        <v>-0.04505488004286866</v>
       </c>
       <c r="K13" t="n">
-        <v>8.1141843846955</v>
+        <v>8.114184384694337</v>
       </c>
     </row>
     <row r="14">
@@ -923,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>11.24253477912758</v>
+        <v>11.24253477912691</v>
       </c>
       <c r="F14" t="n">
-        <v>5.272740302799424e-05</v>
+        <v>5.272740356380378e-05</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01403178333646062</v>
+        <v>0.01403178333646527</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.886833036039658e-07</v>
+        <v>-2.886832883124274e-07</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2774101967681684</v>
+        <v>0.2774101967683359</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01500512856537014</v>
+        <v>0.01500512856519697</v>
       </c>
       <c r="K14" t="n">
-        <v>11.24254353576703</v>
+        <v>11.24254353576636</v>
       </c>
     </row>
     <row r="15">
@@ -958,25 +958,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>11.2425347791201</v>
+        <v>11.24253477912112</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.272740957680732e-05</v>
+        <v>-5.272740904099736e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01403178333646043</v>
+        <v>0.01403178333646289</v>
       </c>
       <c r="H15" t="n">
-        <v>2.886834930193329e-07</v>
+        <v>2.886835082336281e-07</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2774101967679769</v>
+        <v>0.2774101967680513</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.01500512856361739</v>
+        <v>-0.01500512856379087</v>
       </c>
       <c r="K15" t="n">
-        <v>11.24254353575955</v>
+        <v>11.24254353576057</v>
       </c>
     </row>
     <row r="16">
@@ -993,25 +993,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>11.24364880861739</v>
+        <v>11.24364880861841</v>
       </c>
       <c r="F16" t="n">
-        <v>5.272740958393851e-05</v>
+        <v>5.27274090296737e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.01403178333646046</v>
+        <v>-0.01403178333646289</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.886834933623841e-07</v>
+        <v>-2.886835081465285e-07</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2818139420127958</v>
+        <v>0.2818139420128695</v>
       </c>
       <c r="J16" t="n">
-        <v>0.04505493137084957</v>
+        <v>0.04505493137067544</v>
       </c>
       <c r="K16" t="n">
-        <v>11.24365756438923</v>
+        <v>11.24365756439025</v>
       </c>
     </row>
     <row r="17">
@@ -1028,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>11.24364880862486</v>
+        <v>11.2436488086242</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.272740302085454e-05</v>
+        <v>-5.272740357512158e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.01403178333646063</v>
+        <v>-0.01403178333646528</v>
       </c>
       <c r="H17" t="n">
-        <v>2.886833031477993e-07</v>
+        <v>2.88683288419905e-07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2818139420129872</v>
+        <v>0.2818139420131543</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.04505493136909523</v>
+        <v>-0.04505493136926936</v>
       </c>
       <c r="K17" t="n">
-        <v>11.2436575643967</v>
+        <v>11.24365756439603</v>
       </c>
     </row>
     <row r="18">
@@ -1063,25 +1063,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>12.7636275507655</v>
+        <v>12.76362755076675</v>
       </c>
       <c r="F18" t="n">
-        <v>5.273160743815383e-05</v>
+        <v>5.273160774713402e-05</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01458744045581826</v>
+        <v>0.01458744045582377</v>
       </c>
       <c r="H18" t="n">
-        <v>1.041020896839185e-07</v>
+        <v>1.041021125745989e-07</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1191579135705716</v>
+        <v>0.1191579135707582</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01500512783931789</v>
+        <v>0.01500512783927177</v>
       </c>
       <c r="K18" t="n">
-        <v>12.76363588680199</v>
+        <v>12.76363588680325</v>
       </c>
     </row>
     <row r="19">
@@ -1098,25 +1098,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>12.76362755075735</v>
+        <v>12.76362755075872</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.273161501681668e-05</v>
+        <v>-5.273161470783783e-05</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01458744045581829</v>
+        <v>0.01458744045582099</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.041020131429611e-07</v>
+        <v>-1.041019902353731e-07</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1191579135705384</v>
+        <v>0.1191579135705613</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.01500512783735091</v>
+        <v>-0.01500512783739848</v>
       </c>
       <c r="K19" t="n">
-        <v>12.76363588679385</v>
+        <v>12.76363588679521</v>
       </c>
     </row>
     <row r="20">
@@ -1133,25 +1133,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>12.76431736073221</v>
+        <v>12.76431736073357</v>
       </c>
       <c r="F20" t="n">
-        <v>5.273161502770671e-05</v>
+        <v>5.273161469785554e-05</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.01458744045581832</v>
+        <v>-0.01458744045582099</v>
       </c>
       <c r="H20" t="n">
-        <v>1.041020126456332e-07</v>
+        <v>1.041019900625209e-07</v>
       </c>
       <c r="I20" t="n">
-        <v>0.09905190241355175</v>
+        <v>0.09905190241357491</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04505493222254756</v>
+        <v>0.04505493222250071</v>
       </c>
       <c r="K20" t="n">
-        <v>12.7643256963182</v>
+        <v>12.76432569631957</v>
       </c>
     </row>
     <row r="21">
@@ -1168,25 +1168,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>12.76431736074036</v>
+        <v>12.76431736074161</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.273160742726827e-05</v>
+        <v>-5.273160775711663e-05</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.01458744045581826</v>
+        <v>-0.01458744045582378</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.041020899760041e-07</v>
+        <v>-1.041021128221863e-07</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09905190241358573</v>
+        <v>0.09905190241377351</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.04505493222058038</v>
+        <v>-0.04505493222062767</v>
       </c>
       <c r="K21" t="n">
-        <v>12.76432569632636</v>
+        <v>12.76432569632761</v>
       </c>
     </row>
   </sheetData>
@@ -1245,16 +1245,16 @@
         <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>12.76432569632636</v>
+        <v>12.76432569632761</v>
       </c>
       <c r="D2" t="n">
-        <v>12.76431736074036</v>
+        <v>12.76431736074161</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.273160742726827e-05</v>
+        <v>-5.273160775711663e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.01458744045581826</v>
+        <v>-0.01458744045582378</v>
       </c>
     </row>
     <row r="3">
@@ -1267,16 +1267,16 @@
         <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>12.76431736074036</v>
+        <v>12.76431736074161</v>
       </c>
       <c r="D3" t="n">
-        <v>12.76431736074036</v>
+        <v>12.76431736074161</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.273160742726827e-05</v>
+        <v>-5.273160775711663e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.01458744045581826</v>
+        <v>-0.01458744045582378</v>
       </c>
     </row>
     <row r="4">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>5.274815212167277e-05</v>
+        <v>-5.274815161206213e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>8.114175479580663</v>
+        <v>8.11313329537693</v>
       </c>
       <c r="E4" t="n">
-        <v>5.274815212167277e-05</v>
+        <v>-5.274815161206213e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.012021337085073</v>
+        <v>0.01202133708507474</v>
       </c>
     </row>
     <row r="5">
@@ -1308,19 +1308,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.01458744045581832</v>
+        <v>-0.01458744045582378</v>
       </c>
       <c r="D5" t="n">
-        <v>12.76431736073221</v>
+        <v>12.76431736074161</v>
       </c>
       <c r="E5" t="n">
-        <v>5.273161502770671e-05</v>
+        <v>-5.273160775711663e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01458744045581832</v>
+        <v>-0.01458744045582378</v>
       </c>
     </row>
   </sheetData>
@@ -1379,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-462.4872063002725</v>
+        <v>-462.4872063002059</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.008681138355291034</v>
+        <v>-0.008681138384937864</v>
       </c>
       <c r="D2" t="n">
-        <v>-1187.643359997</v>
+        <v>-1187.643359997215</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03034842954294979</v>
+        <v>0.03034842965933544</v>
       </c>
       <c r="F2" t="n">
-        <v>-1811.770631236171</v>
+        <v>-1811.770631235904</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.04262502787522724</v>
+        <v>-0.04262502787504397</v>
       </c>
     </row>
     <row r="3">
@@ -1402,22 +1402,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-462.4872063000618</v>
+        <v>-462.4872063000596</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00868113856954778</v>
+        <v>0.008681138539901042</v>
       </c>
       <c r="D3" t="n">
-        <v>-1187.643359996955</v>
+        <v>-1187.643359997083</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.03034843041376769</v>
+        <v>-0.0303484302973821</v>
       </c>
       <c r="F3" t="n">
-        <v>-1811.770631235287</v>
+        <v>-1811.770631235289</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04262502787392255</v>
+        <v>0.0426250278741061</v>
       </c>
     </row>
     <row r="4">
@@ -1425,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>-537.5127936996093</v>
+        <v>-537.5127936996073</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.008681138569743792</v>
+        <v>-0.008681138539563298</v>
       </c>
       <c r="D4" t="n">
-        <v>1187.643359996957</v>
+        <v>1187.643359997082</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03034843041456974</v>
+        <v>0.03034843029597107</v>
       </c>
       <c r="F4" t="n">
-        <v>-1887.082488781221</v>
+        <v>-1887.082488781223</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1280965491398132</v>
+        <v>-0.1280965491396296</v>
       </c>
     </row>
     <row r="5">
@@ -1448,22 +1448,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-537.51279369982</v>
+        <v>-537.5127936997534</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008681138355098365</v>
+        <v>0.008681138385276456</v>
       </c>
       <c r="D5" t="n">
-        <v>1187.643359997</v>
+        <v>1187.643359997217</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03034842954215432</v>
+        <v>-0.03034842966074816</v>
       </c>
       <c r="F5" t="n">
-        <v>-1887.082488782104</v>
+        <v>-1887.082488781838</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1280965491385087</v>
+        <v>0.1280965491386919</v>
       </c>
     </row>
   </sheetData>
@@ -1606,52 +1606,52 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007516730126563289</v>
+        <v>0.007516730126564649</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001252788354427215</v>
+        <v>0.001252788354427442</v>
       </c>
       <c r="H2" t="n">
-        <v>1187.643359997</v>
+        <v>1187.643359997215</v>
       </c>
       <c r="I2" t="n">
-        <v>250557.670885443</v>
+        <v>250557.6708854883</v>
       </c>
       <c r="J2" t="n">
-        <v>-1187.643359997</v>
+        <v>-1187.643359997215</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.008681138355291034</v>
+        <v>-0.008681138384937864</v>
       </c>
       <c r="L2" t="n">
-        <v>462.4872063002725</v>
+        <v>462.4872063002059</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04262502787522724</v>
+        <v>-0.04262502787504397</v>
       </c>
       <c r="N2" t="n">
-        <v>-1811.770631236171</v>
+        <v>-1811.770631235904</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.03034842954294979</v>
+        <v>-0.03034842965933544</v>
       </c>
       <c r="P2" t="n">
-        <v>1187.643359997</v>
+        <v>1187.643359997215</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.008681138355291034</v>
+        <v>0.008681138384937864</v>
       </c>
       <c r="R2" t="n">
-        <v>-462.4872063002725</v>
+        <v>-462.4872063002059</v>
       </c>
       <c r="S2" t="n">
-        <v>0.04262502787522724</v>
+        <v>0.04262502787504397</v>
       </c>
       <c r="T2" t="n">
-        <v>-963.1526065654646</v>
+        <v>-963.1526065653311</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.02173840058879641</v>
+        <v>-0.02173840065029174</v>
       </c>
     </row>
     <row r="3">
@@ -1673,52 +1673,52 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007516730126563006</v>
+        <v>0.007516730126563812</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001252788354427168</v>
+        <v>0.001252788354427302</v>
       </c>
       <c r="H3" t="n">
-        <v>1187.643359996955</v>
+        <v>1187.643359997082</v>
       </c>
       <c r="I3" t="n">
-        <v>250557.6708854335</v>
+        <v>250557.6708854604</v>
       </c>
       <c r="J3" t="n">
-        <v>-1187.643359996955</v>
+        <v>-1187.643359997083</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00868113856954778</v>
+        <v>0.008681138539901042</v>
       </c>
       <c r="L3" t="n">
-        <v>462.4872063000618</v>
+        <v>462.4872063000596</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04262502787392255</v>
+        <v>0.0426250278741061</v>
       </c>
       <c r="N3" t="n">
-        <v>-1811.770631235287</v>
+        <v>-1811.770631235289</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03034843041376769</v>
+        <v>0.0303484302973821</v>
       </c>
       <c r="P3" t="n">
-        <v>1187.643359996955</v>
+        <v>1187.643359997083</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.00868113856954778</v>
+        <v>-0.008681138539901042</v>
       </c>
       <c r="R3" t="n">
-        <v>-462.4872063000618</v>
+        <v>-462.4872063000596</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.04262502787392255</v>
+        <v>-0.0426250278741061</v>
       </c>
       <c r="T3" t="n">
-        <v>-963.1526065650828</v>
+        <v>-963.1526065650683</v>
       </c>
       <c r="U3" t="n">
-        <v>0.021738401003519</v>
+        <v>0.02173840094202415</v>
       </c>
     </row>
     <row r="4">
@@ -1740,52 +1740,52 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.007516730126563017</v>
+        <v>-0.007516730126563806</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.00125278835442717</v>
+        <v>-0.001252788354427301</v>
       </c>
       <c r="H4" t="n">
-        <v>-1187.643359996957</v>
+        <v>-1187.643359997081</v>
       </c>
       <c r="I4" t="n">
-        <v>-250557.6708854339</v>
+        <v>-250557.6708854602</v>
       </c>
       <c r="J4" t="n">
-        <v>1187.643359996957</v>
+        <v>1187.643359997082</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.008681138569743792</v>
+        <v>-0.008681138539563298</v>
       </c>
       <c r="L4" t="n">
-        <v>537.5127936996093</v>
+        <v>537.5127936996073</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1280965491398132</v>
+        <v>-0.1280965491396296</v>
       </c>
       <c r="N4" t="n">
-        <v>-1887.082488781221</v>
+        <v>-1887.082488781223</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.03034843041456974</v>
+        <v>-0.03034843029597107</v>
       </c>
       <c r="P4" t="n">
-        <v>-1187.643359996957</v>
+        <v>-1187.643359997082</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008681138569743792</v>
+        <v>0.008681138539563298</v>
       </c>
       <c r="R4" t="n">
-        <v>-387.5127936996093</v>
+        <v>-387.5127936996073</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1280965491398132</v>
+        <v>0.1280965491396296</v>
       </c>
       <c r="T4" t="n">
-        <v>-887.9942734164347</v>
+        <v>-887.9942734164206</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.02173840100389299</v>
+        <v>-0.02173840094140872</v>
       </c>
     </row>
     <row r="5">
@@ -1807,52 +1807,52 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.00751673012656329</v>
+        <v>-0.007516730126564661</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.001252788354427215</v>
+        <v>-0.001252788354427443</v>
       </c>
       <c r="H5" t="n">
-        <v>-1187.643359997</v>
+        <v>-1187.643359997216</v>
       </c>
       <c r="I5" t="n">
-        <v>-250557.670885443</v>
+        <v>-250557.6708854887</v>
       </c>
       <c r="J5" t="n">
-        <v>1187.643359997</v>
+        <v>1187.643359997217</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008681138355098365</v>
+        <v>0.008681138385276456</v>
       </c>
       <c r="L5" t="n">
-        <v>537.51279369982</v>
+        <v>537.5127936997534</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1280965491385087</v>
+        <v>0.1280965491386919</v>
       </c>
       <c r="N5" t="n">
-        <v>-1887.082488782104</v>
+        <v>-1887.082488781838</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03034842954215432</v>
+        <v>0.03034842966074816</v>
       </c>
       <c r="P5" t="n">
-        <v>-1187.643359997</v>
+        <v>-1187.643359997217</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.008681138355098365</v>
+        <v>-0.008681138385276456</v>
       </c>
       <c r="R5" t="n">
-        <v>-387.51279369982</v>
+        <v>-387.5127936997534</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1280965491385087</v>
+        <v>-0.1280965491386919</v>
       </c>
       <c r="T5" t="n">
-        <v>-887.9942734168162</v>
+        <v>-887.9942734166825</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02173840058843586</v>
+        <v>0.02173840065091057</v>
       </c>
     </row>
     <row r="6">
@@ -1874,52 +1874,52 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004504606958510098</v>
+        <v>0.004504606958511741</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0007507678264183497</v>
+        <v>0.0007507678264186235</v>
       </c>
       <c r="H6" t="n">
-        <v>711.7278994445956</v>
+        <v>711.7278994448551</v>
       </c>
       <c r="I6" t="n">
-        <v>150153.5652836699</v>
+        <v>150153.5652837247</v>
       </c>
       <c r="J6" t="n">
-        <v>-711.7278994445956</v>
+        <v>-711.7278994448552</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003335535281722257</v>
+        <v>0.00333553525708279</v>
       </c>
       <c r="L6" t="n">
-        <v>337.2538056231967</v>
+        <v>337.2538056231251</v>
       </c>
       <c r="M6" t="n">
-        <v>-8.174341103647093e-05</v>
+        <v>-8.17434107819523e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>-940.3329141341959</v>
+        <v>-940.3329141340305</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01525604259338728</v>
+        <v>0.01525604253144997</v>
       </c>
       <c r="P6" t="n">
-        <v>711.7278994445956</v>
+        <v>711.7278994448552</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.003335535281722257</v>
+        <v>-0.00333553525708279</v>
       </c>
       <c r="R6" t="n">
-        <v>-337.2538056231967</v>
+        <v>-337.2538056231251</v>
       </c>
       <c r="S6" t="n">
-        <v>8.174341103647093e-05</v>
+        <v>8.17434107819523e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>-1083.189919604984</v>
+        <v>-1083.189919604719</v>
       </c>
       <c r="U6" t="n">
-        <v>0.004757169096946262</v>
+        <v>0.004757169011046773</v>
       </c>
     </row>
     <row r="7">
@@ -1941,52 +1941,52 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004504606958509978</v>
+        <v>0.004504606958510925</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007507678264183296</v>
+        <v>0.0007507678264184874</v>
       </c>
       <c r="H7" t="n">
-        <v>711.7278994445765</v>
+        <v>711.7278994447261</v>
       </c>
       <c r="I7" t="n">
-        <v>150153.5652836659</v>
+        <v>150153.5652836975</v>
       </c>
       <c r="J7" t="n">
-        <v>-711.7278994445767</v>
+        <v>-711.7278994447263</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.003335535075520275</v>
+        <v>-0.003335535100160325</v>
       </c>
       <c r="L7" t="n">
-        <v>337.2538056229537</v>
+        <v>337.2538056229571</v>
       </c>
       <c r="M7" t="n">
-        <v>8.174340898744331e-05</v>
+        <v>8.174340924035906e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>-940.3329141334489</v>
+        <v>-940.3329141334998</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.01525604198034497</v>
+        <v>-0.0152560420422833</v>
       </c>
       <c r="P7" t="n">
-        <v>711.7278994445767</v>
+        <v>711.7278994447263</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003335535075520275</v>
+        <v>0.003335535100160325</v>
       </c>
       <c r="R7" t="n">
-        <v>-337.2538056229537</v>
+        <v>-337.2538056229571</v>
       </c>
       <c r="S7" t="n">
-        <v>-8.174340898744331e-05</v>
+        <v>-8.174340924035906e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>-1083.189919604273</v>
+        <v>-1083.189919604242</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.004757168472776685</v>
+        <v>-0.004757168558678665</v>
       </c>
     </row>
     <row r="8">
@@ -2008,52 +2008,52 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.004504606958509985</v>
+        <v>-0.004504606958510924</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0007507678264183309</v>
+        <v>-0.0007507678264184873</v>
       </c>
       <c r="H8" t="n">
-        <v>-711.7278994445777</v>
+        <v>-711.7278994447259</v>
       </c>
       <c r="I8" t="n">
-        <v>-150153.5652836662</v>
+        <v>-150153.5652836974</v>
       </c>
       <c r="J8" t="n">
-        <v>711.7278994445778</v>
+        <v>711.7278994447261</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003335535075336502</v>
+        <v>0.003335535100540082</v>
       </c>
       <c r="L8" t="n">
-        <v>412.7461943766295</v>
+        <v>412.7461943766323</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0001365709851156582</v>
+        <v>-0.0001365709848609731</v>
       </c>
       <c r="N8" t="n">
-        <v>-1015.843890303033</v>
+        <v>-1015.843890303083</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01525604197975264</v>
+        <v>0.01525604204344892</v>
       </c>
       <c r="P8" t="n">
-        <v>-711.7278994445778</v>
+        <v>-711.7278994447261</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.003335535075336502</v>
+        <v>-0.003335535100540082</v>
       </c>
       <c r="R8" t="n">
-        <v>-262.7461943766295</v>
+        <v>-262.7461943766323</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0001365709851156582</v>
+        <v>0.0001365709848609731</v>
       </c>
       <c r="T8" t="n">
-        <v>-1010.633275956742</v>
+        <v>-1010.633275956709</v>
       </c>
       <c r="U8" t="n">
-        <v>0.004757168472266371</v>
+        <v>0.004757168559791573</v>
       </c>
     </row>
     <row r="9">
@@ -2075,52 +2075,52 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.004504606958510099</v>
+        <v>-0.004504606958511742</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0007507678264183498</v>
+        <v>-0.0007507678264186236</v>
       </c>
       <c r="H9" t="n">
-        <v>-711.7278994445957</v>
+        <v>-711.7278994448552</v>
       </c>
       <c r="I9" t="n">
-        <v>-150153.56528367</v>
+        <v>-150153.5652837247</v>
       </c>
       <c r="J9" t="n">
-        <v>711.7278994445958</v>
+        <v>711.7278994448554</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.003335535281918336</v>
+        <v>-0.003335535256706077</v>
       </c>
       <c r="L9" t="n">
-        <v>412.7461943768724</v>
+        <v>412.7461943768008</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001365709830680184</v>
+        <v>0.0001365709833188455</v>
       </c>
       <c r="N9" t="n">
-        <v>-1015.843890303781</v>
+        <v>-1015.843890303616</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.01525604259399728</v>
+        <v>-0.01525604253028832</v>
       </c>
       <c r="P9" t="n">
-        <v>-711.7278994445958</v>
+        <v>-711.7278994448554</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003335535281918336</v>
+        <v>0.003335535256706077</v>
       </c>
       <c r="R9" t="n">
-        <v>-262.7461943768724</v>
+        <v>-262.7461943768008</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0001365709830680184</v>
+        <v>-0.0001365709833188455</v>
       </c>
       <c r="T9" t="n">
-        <v>-1010.633275957454</v>
+        <v>-1010.633275957188</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.00475716909751274</v>
+        <v>-0.004757169009948131</v>
       </c>
     </row>
     <row r="10">
@@ -2142,52 +2142,52 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002010446251387233</v>
+        <v>0.002010446251388883</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003350743752312055</v>
+        <v>0.0003350743752314805</v>
       </c>
       <c r="H10" t="n">
-        <v>317.6505077191828</v>
+        <v>317.6505077194435</v>
       </c>
       <c r="I10" t="n">
-        <v>67014.8750462411</v>
+        <v>67014.87504629609</v>
       </c>
       <c r="J10" t="n">
-        <v>-317.6505077191828</v>
+        <v>-317.6505077194436</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.000725679616803785</v>
+        <v>-0.0007256796201811321</v>
       </c>
       <c r="L10" t="n">
-        <v>213.7549774489315</v>
+        <v>213.7549774489485</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.330920974471073e-07</v>
+        <v>-1.330920423731063e-07</v>
       </c>
       <c r="N10" t="n">
-        <v>-493.6679683552808</v>
+        <v>-493.6679683554712</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.003335086766222121</v>
+        <v>-0.003335086749574341</v>
       </c>
       <c r="P10" t="n">
-        <v>317.6505077191828</v>
+        <v>317.6505077194436</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.000725679616803785</v>
+        <v>0.0007256796201811321</v>
       </c>
       <c r="R10" t="n">
-        <v>-213.7549774489315</v>
+        <v>-213.7549774489485</v>
       </c>
       <c r="S10" t="n">
-        <v>1.330920974471073e-07</v>
+        <v>1.330920423731063e-07</v>
       </c>
       <c r="T10" t="n">
-        <v>-788.861896338309</v>
+        <v>-788.8618963382187</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.00101899093460061</v>
+        <v>-0.001018990971512444</v>
       </c>
     </row>
     <row r="11">
@@ -2209,52 +2209,52 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00201044625138745</v>
+        <v>0.002010446251388151</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003350743752312416</v>
+        <v>0.0003350743752313584</v>
       </c>
       <c r="H11" t="n">
-        <v>317.6505077192171</v>
+        <v>317.6505077193278</v>
       </c>
       <c r="I11" t="n">
-        <v>67014.87504624833</v>
+        <v>67014.87504627169</v>
       </c>
       <c r="J11" t="n">
-        <v>-317.6505077192171</v>
+        <v>-317.6505077193278</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0007256797704882252</v>
+        <v>0.0007256797671678136</v>
       </c>
       <c r="L11" t="n">
-        <v>213.7549774487221</v>
+        <v>213.7549774488043</v>
       </c>
       <c r="M11" t="n">
-        <v>1.330904625743146e-07</v>
+        <v>1.330905198618226e-07</v>
       </c>
       <c r="N11" t="n">
-        <v>-493.6679683547802</v>
+        <v>-493.6679683550301</v>
       </c>
       <c r="O11" t="n">
-        <v>0.003335087144958782</v>
+        <v>0.003335087161719666</v>
       </c>
       <c r="P11" t="n">
-        <v>317.6505077192171</v>
+        <v>317.6505077193278</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.0007256797704882252</v>
+        <v>-0.0007256797671678136</v>
       </c>
       <c r="R11" t="n">
-        <v>-213.7549774487221</v>
+        <v>-213.7549774488043</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.330904625743146e-07</v>
+        <v>-1.330905198618226e-07</v>
       </c>
       <c r="T11" t="n">
-        <v>-788.8618963375543</v>
+        <v>-788.8618963377921</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001018991477970577</v>
+        <v>0.001018991441287212</v>
       </c>
     </row>
     <row r="12">
@@ -2276,52 +2276,52 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.002010446251387455</v>
+        <v>-0.002010446251388158</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0003350743752312425</v>
+        <v>-0.0003350743752313596</v>
       </c>
       <c r="H12" t="n">
-        <v>-317.6505077192179</v>
+        <v>-317.6505077193289</v>
       </c>
       <c r="I12" t="n">
-        <v>-67014.8750462485</v>
+        <v>-67014.87504627192</v>
       </c>
       <c r="J12" t="n">
-        <v>317.6505077192182</v>
+        <v>317.650507719329</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0007256797706754747</v>
+        <v>-0.0007256797668005119</v>
       </c>
       <c r="L12" t="n">
-        <v>286.2450225507185</v>
+        <v>286.245022550801</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.460844122613825e-07</v>
+        <v>-1.460843549183632e-07</v>
       </c>
       <c r="N12" t="n">
-        <v>-565.1279698860859</v>
+        <v>-565.1279698863391</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.003335087145519354</v>
+        <v>-0.003335087160977454</v>
       </c>
       <c r="P12" t="n">
-        <v>-317.6505077192182</v>
+        <v>-317.650507719329</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0007256797706754747</v>
+        <v>0.0007256797668005119</v>
       </c>
       <c r="R12" t="n">
-        <v>-136.2450225507185</v>
+        <v>-136.245022550801</v>
       </c>
       <c r="S12" t="n">
-        <v>1.460844122613825e-07</v>
+        <v>1.460843549183632e-07</v>
       </c>
       <c r="T12" t="n">
-        <v>-702.342165418225</v>
+        <v>-702.3421654184676</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.001018991478533501</v>
+        <v>-0.001018991439825603</v>
       </c>
     </row>
     <row r="13">
@@ -2343,52 +2343,52 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.002010446251387236</v>
+        <v>-0.002010446251388881</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0003350743752312061</v>
+        <v>-0.0003350743752314801</v>
       </c>
       <c r="H13" t="n">
-        <v>-317.6505077191833</v>
+        <v>-317.6505077194432</v>
       </c>
       <c r="I13" t="n">
-        <v>-67014.87504624121</v>
+        <v>-67014.87504629603</v>
       </c>
       <c r="J13" t="n">
-        <v>317.6505077191835</v>
+        <v>317.6505077194431</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0007256796166823266</v>
+        <v>0.000725679620527225</v>
       </c>
       <c r="L13" t="n">
-        <v>286.245022550927</v>
+        <v>286.2450225509428</v>
       </c>
       <c r="M13" t="n">
-        <v>1.460827712407298e-07</v>
+        <v>1.460828327748409e-07</v>
       </c>
       <c r="N13" t="n">
-        <v>-565.127969886584</v>
+        <v>-565.1279698867711</v>
       </c>
       <c r="O13" t="n">
-        <v>0.003335086765759374</v>
+        <v>0.003335086750263713</v>
       </c>
       <c r="P13" t="n">
-        <v>-317.6505077191835</v>
+        <v>-317.6505077194431</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.0007256796166823266</v>
+        <v>-0.000725679620527225</v>
       </c>
       <c r="R13" t="n">
-        <v>-136.245022550927</v>
+        <v>-136.2450225509428</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.460827712407298e-07</v>
+        <v>-1.460828327748409e-07</v>
       </c>
       <c r="T13" t="n">
-        <v>-702.3421654189774</v>
+        <v>-702.342165418886</v>
       </c>
       <c r="U13" t="n">
-        <v>0.001018990934334565</v>
+        <v>0.001018990972899647</v>
       </c>
     </row>
     <row r="14">
@@ -2410,52 +2410,52 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0005556571193576412</v>
+        <v>0.0005556571193584946</v>
       </c>
       <c r="G14" t="n">
-        <v>9.260951989294019e-05</v>
+        <v>9.260951989308244e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>87.79382485850731</v>
+        <v>87.79382485864215</v>
       </c>
       <c r="I14" t="n">
-        <v>18521.90397858804</v>
+        <v>18521.90397861649</v>
       </c>
       <c r="J14" t="n">
-        <v>-87.79382485850738</v>
+        <v>-87.79382485864198</v>
       </c>
       <c r="K14" t="n">
-        <v>0.000135553010461472</v>
+        <v>0.0001355530381578693</v>
       </c>
       <c r="L14" t="n">
-        <v>81.74248202001982</v>
+        <v>81.74248202023045</v>
       </c>
       <c r="M14" t="n">
-        <v>2.066456408766904e-09</v>
+        <v>2.066094795249995e-09</v>
       </c>
       <c r="N14" t="n">
-        <v>-128.1207564938366</v>
+        <v>-128.1207564944852</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0006973202224174468</v>
+        <v>0.000697320311130005</v>
       </c>
       <c r="P14" t="n">
-        <v>87.79382485850738</v>
+        <v>87.79382485864198</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.000135553010461472</v>
+        <v>-0.0001355530381578693</v>
       </c>
       <c r="R14" t="n">
-        <v>-81.74248202001982</v>
+        <v>-81.74248202023045</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.066456408766904e-09</v>
+        <v>-2.066094795249995e-09</v>
       </c>
       <c r="T14" t="n">
-        <v>-362.3341356262787</v>
+        <v>-362.3341356268993</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0001159978403513784</v>
+        <v>0.0001159979178172107</v>
       </c>
     </row>
     <row r="15">
@@ -2477,52 +2477,52 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0005556571193578615</v>
+        <v>0.0005556571193580991</v>
       </c>
       <c r="G15" t="n">
-        <v>9.260951989297692e-05</v>
+        <v>9.260951989301652e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>87.79382485854211</v>
+        <v>87.79382485857967</v>
       </c>
       <c r="I15" t="n">
-        <v>18521.90397859538</v>
+        <v>18521.9039786033</v>
       </c>
       <c r="J15" t="n">
-        <v>-87.79382485854194</v>
+        <v>-87.79382485857968</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0001355529532395382</v>
+        <v>-0.0001355529254980607</v>
       </c>
       <c r="L15" t="n">
-        <v>81.74248202002072</v>
+        <v>81.74248202003355</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.06706612937424e-09</v>
+        <v>-2.067424516305483e-09</v>
       </c>
       <c r="N15" t="n">
-        <v>-128.1207564939566</v>
+        <v>-128.1207564939577</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0006973201342787144</v>
+        <v>-0.0006973200453612369</v>
       </c>
       <c r="P15" t="n">
-        <v>87.79382485854194</v>
+        <v>87.79382485857968</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0001355529532395382</v>
+        <v>0.0001355529254980607</v>
       </c>
       <c r="R15" t="n">
-        <v>-81.74248202002072</v>
+        <v>-81.74248202003355</v>
       </c>
       <c r="S15" t="n">
-        <v>2.06706612937424e-09</v>
+        <v>2.067424516305483e-09</v>
       </c>
       <c r="T15" t="n">
-        <v>-362.3341356261658</v>
+        <v>-362.3341356262445</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0001159975851585185</v>
+        <v>-0.0001159975076271205</v>
       </c>
     </row>
     <row r="16">
@@ -2544,52 +2544,52 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0005556571193578649</v>
+        <v>-0.0005556571193581009</v>
       </c>
       <c r="G16" t="n">
-        <v>-9.260951989297748e-05</v>
+        <v>-9.260951989301681e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>-87.79382485854266</v>
+        <v>-87.79382485857994</v>
       </c>
       <c r="I16" t="n">
-        <v>-18521.9039785955</v>
+        <v>-18521.90397860336</v>
       </c>
       <c r="J16" t="n">
-        <v>87.79382485854239</v>
+        <v>87.79382485858014</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0001355529529342408</v>
+        <v>0.0001355529252306444</v>
       </c>
       <c r="L16" t="n">
-        <v>168.2575179794908</v>
+        <v>168.2575179795031</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.424063477723948e-09</v>
+        <v>-2.424425771252459e-09</v>
       </c>
       <c r="N16" t="n">
-        <v>-219.5286446350328</v>
+        <v>-219.528644635031</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0006973201332486564</v>
+        <v>0.0006973200443666297</v>
       </c>
       <c r="P16" t="n">
-        <v>-87.79382485854239</v>
+        <v>-87.79382485858014</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.0001355529529342408</v>
+        <v>-0.0001355529252306444</v>
       </c>
       <c r="R16" t="n">
-        <v>-18.25751797949079</v>
+        <v>-18.25751797950306</v>
       </c>
       <c r="S16" t="n">
-        <v>2.424063477723948e-09</v>
+        <v>2.424425771252459e-09</v>
       </c>
       <c r="T16" t="n">
-        <v>-340.0164632419128</v>
+        <v>-340.0164632419874</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0001159975843567848</v>
+        <v>0.0001159975070172403</v>
       </c>
     </row>
     <row r="17">
@@ -2611,52 +2611,52 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0005556571193576377</v>
+        <v>-0.0005556571193584964</v>
       </c>
       <c r="G17" t="n">
-        <v>-9.260951989293962e-05</v>
+        <v>-9.260951989308273e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>-87.79382485850675</v>
+        <v>-87.79382485864242</v>
       </c>
       <c r="I17" t="n">
-        <v>-18521.90397858792</v>
+        <v>-18521.90397861654</v>
       </c>
       <c r="J17" t="n">
-        <v>87.79382485850692</v>
+        <v>87.79382485864244</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0001355530108317436</v>
+        <v>-0.0001355530383835308</v>
       </c>
       <c r="L17" t="n">
-        <v>168.2575179794911</v>
+        <v>168.2575179797013</v>
       </c>
       <c r="M17" t="n">
-        <v>2.423457712286137e-09</v>
+        <v>2.42309672326968e-09</v>
       </c>
       <c r="N17" t="n">
-        <v>-219.528644634917</v>
+        <v>-219.528644635564</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.000697320223406836</v>
+        <v>-0.0006973203120697463</v>
       </c>
       <c r="P17" t="n">
-        <v>-87.79382485850692</v>
+        <v>-87.79382485864244</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0001355530108317436</v>
+        <v>0.0001355530383835308</v>
       </c>
       <c r="R17" t="n">
-        <v>-18.2575179794911</v>
+        <v>-18.25751797970133</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.423457712286137e-09</v>
+        <v>-2.42309672326968e-09</v>
       </c>
       <c r="T17" t="n">
-        <v>-340.0164632420323</v>
+        <v>-340.0164632426458</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0001159978415836149</v>
+        <v>-0.0001159979182314488</v>
       </c>
     </row>
     <row r="18">
@@ -2678,52 +2678,52 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0001052931328663778</v>
+        <v>-0.0001052931328663773</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.316164160829722e-05</v>
+        <v>-1.316164160829716e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>-12.47723624466577</v>
+        <v>-12.47723624466571</v>
       </c>
       <c r="I18" t="n">
-        <v>-2632.328321659445</v>
+        <v>-2632.328321659432</v>
       </c>
       <c r="J18" t="n">
-        <v>12.47723624466577</v>
+        <v>12.47723624466571</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.865352482534945e-12</v>
+        <v>1.13686837721616e-12</v>
       </c>
       <c r="L18" t="n">
-        <v>1.28306291372754e-10</v>
+        <v>9.748801765852022e-11</v>
       </c>
       <c r="M18" t="n">
-        <v>7.23199278240827e-13</v>
+        <v>5.082601006733967e-13</v>
       </c>
       <c r="N18" t="n">
-        <v>0.006457521373425529</v>
+        <v>0.006457521496698426</v>
       </c>
       <c r="O18" t="n">
-        <v>16.62376087106873</v>
+        <v>16.62376087108873</v>
       </c>
       <c r="P18" t="n">
-        <v>-12.47723624466577</v>
+        <v>-12.47723624466571</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.865352482534945e-12</v>
+        <v>-1.13686837721616e-12</v>
       </c>
       <c r="R18" t="n">
-        <v>-1.28306291372754e-10</v>
+        <v>-9.748801765852022e-11</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.23199278240827e-13</v>
+        <v>-5.082601006733967e-13</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.006457522399876302</v>
+        <v>-0.006457522276602568</v>
       </c>
       <c r="U18" t="n">
-        <v>-16.62376087109965</v>
+        <v>-16.62376087107964</v>
       </c>
     </row>
     <row r="19">
@@ -2757,40 +2757,40 @@
         <v>26420.5486660507</v>
       </c>
       <c r="J19" t="n">
-        <v>-125.233400677098</v>
+        <v>-125.2334006770398</v>
       </c>
       <c r="K19" t="n">
-        <v>12.48925291831083</v>
+        <v>12.48925291830579</v>
       </c>
       <c r="L19" t="n">
-        <v>-475.9154605522502</v>
+        <v>-475.9154605522591</v>
       </c>
       <c r="M19" t="n">
-        <v>2.48366232994117e-05</v>
+        <v>2.483662313930812e-05</v>
       </c>
       <c r="N19" t="n">
-        <v>1903.485520698533</v>
+        <v>1903.485520698568</v>
       </c>
       <c r="O19" t="n">
-        <v>16.66630415556484</v>
+        <v>16.66630415554469</v>
       </c>
       <c r="P19" t="n">
-        <v>125.233400677098</v>
+        <v>125.2334006770398</v>
       </c>
       <c r="Q19" t="n">
-        <v>-12.48925291831083</v>
+        <v>-12.48925291830579</v>
       </c>
       <c r="R19" t="n">
-        <v>475.9154605522502</v>
+        <v>475.9154605522591</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.48366232994117e-05</v>
+        <v>-2.483662313930812e-05</v>
       </c>
       <c r="T19" t="n">
-        <v>1903.838163719469</v>
+        <v>1903.838163719504</v>
       </c>
       <c r="U19" t="n">
-        <v>83.24771919092179</v>
+        <v>83.24771919090161</v>
       </c>
     </row>
     <row r="20">
@@ -2812,52 +2812,52 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001052931328663774</v>
+        <v>0.0001052931328663773</v>
       </c>
       <c r="G20" t="n">
-        <v>1.316164160829718e-05</v>
+        <v>1.316164160829716e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>12.47723624466572</v>
+        <v>12.4772362446657</v>
       </c>
       <c r="I20" t="n">
-        <v>2632.328321659435</v>
+        <v>2632.328321659431</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.47723624466572</v>
+        <v>-12.4772362446657</v>
       </c>
       <c r="K20" t="n">
-        <v>-100.000000000004</v>
+        <v>-99.99999999999892</v>
       </c>
       <c r="L20" t="n">
-        <v>1.285480819013252e-10</v>
+        <v>9.704281822564553e-11</v>
       </c>
       <c r="M20" t="n">
-        <v>7.238654120556021e-13</v>
+        <v>5.091482790930968e-13</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.006457522400840577</v>
+        <v>-0.006457522274820882</v>
       </c>
       <c r="O20" t="n">
-        <v>-83.37567916907628</v>
+        <v>-83.3756791690565</v>
       </c>
       <c r="P20" t="n">
-        <v>12.47723624466572</v>
+        <v>12.4772362446657</v>
       </c>
       <c r="Q20" t="n">
-        <v>-99.99999999999602</v>
+        <v>-100.0000000000011</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.285480819013252e-10</v>
+        <v>-9.704281822564553e-11</v>
       </c>
       <c r="S20" t="n">
-        <v>-7.238654120556021e-13</v>
+        <v>-5.091482790930968e-13</v>
       </c>
       <c r="T20" t="n">
-        <v>0.006457521372455919</v>
+        <v>0.00645752149847878</v>
       </c>
       <c r="U20" t="n">
-        <v>83.37567916904467</v>
+        <v>83.37567916906491</v>
       </c>
     </row>
     <row r="21">
@@ -2891,40 +2891,40 @@
         <v>26420.5486660618</v>
       </c>
       <c r="J21" t="n">
-        <v>-125.233400677098</v>
+        <v>-125.2334006771562</v>
       </c>
       <c r="K21" t="n">
-        <v>12.48925291830278</v>
+        <v>12.48925291830772</v>
       </c>
       <c r="L21" t="n">
-        <v>-475.9154605525324</v>
+        <v>-475.9154605524574</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.483662198250748e-05</v>
+        <v>-2.483662214261725e-05</v>
       </c>
       <c r="N21" t="n">
-        <v>1903.838163720598</v>
+        <v>1903.838163720297</v>
       </c>
       <c r="O21" t="n">
-        <v>83.24771919088963</v>
+        <v>83.24771919090941</v>
       </c>
       <c r="P21" t="n">
-        <v>125.233400677098</v>
+        <v>125.2334006771562</v>
       </c>
       <c r="Q21" t="n">
-        <v>-12.48925291830278</v>
+        <v>-12.48925291830772</v>
       </c>
       <c r="R21" t="n">
-        <v>475.9154605525324</v>
+        <v>475.9154605524574</v>
       </c>
       <c r="S21" t="n">
-        <v>2.483662198250748e-05</v>
+        <v>2.483662214261725e-05</v>
       </c>
       <c r="T21" t="n">
-        <v>1903.485520699661</v>
+        <v>1903.485520699361</v>
       </c>
       <c r="U21" t="n">
-        <v>16.6663041555326</v>
+        <v>16.66630415555239</v>
       </c>
     </row>
     <row r="22">
@@ -2946,52 +2946,52 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0001054962997791679</v>
+        <v>-0.0001054962997791663</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.318703747239599e-05</v>
+        <v>-1.318703747239578e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>-12.5013115238314</v>
+        <v>-12.5013115238312</v>
       </c>
       <c r="I22" t="n">
-        <v>-2637.407494479197</v>
+        <v>-2637.407494479156</v>
       </c>
       <c r="J22" t="n">
-        <v>12.5013115238314</v>
+        <v>12.5013115238312</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.592059900052845e-11</v>
+        <v>-4.433786671143025e-12</v>
       </c>
       <c r="L22" t="n">
-        <v>1.251894328219844e-10</v>
+        <v>1.079225597777622e-10</v>
       </c>
       <c r="M22" t="n">
-        <v>7.758238496080594e-13</v>
+        <v>5.864198016070077e-13</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.001416633740610715</v>
+        <v>-0.001416633671542655</v>
       </c>
       <c r="O22" t="n">
-        <v>16.65564080088552</v>
+        <v>16.65564080097101</v>
       </c>
       <c r="P22" t="n">
-        <v>-12.5013115238314</v>
+        <v>-12.5013115238312</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.592059900052845e-11</v>
+        <v>4.433786671143025e-12</v>
       </c>
       <c r="R22" t="n">
-        <v>-1.251894328219844e-10</v>
+        <v>-1.079225597777622e-10</v>
       </c>
       <c r="S22" t="n">
-        <v>-7.758238496080594e-13</v>
+        <v>-5.864198016070077e-13</v>
       </c>
       <c r="T22" t="n">
-        <v>0.001416632739095252</v>
+        <v>0.001416632808162177</v>
       </c>
       <c r="U22" t="n">
-        <v>-16.65564080109243</v>
+        <v>-16.65564080100648</v>
       </c>
     </row>
     <row r="23">
@@ -3013,52 +3013,52 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.001042184204001373</v>
+        <v>0.001042184203999597</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001302730255001716</v>
+        <v>0.0001302730254999496</v>
       </c>
       <c r="H23" t="n">
-        <v>123.4988281741627</v>
+        <v>123.4988281739522</v>
       </c>
       <c r="I23" t="n">
-        <v>26054.60510003432</v>
+        <v>26054.60509998991</v>
       </c>
       <c r="J23" t="n">
-        <v>-123.4988281741971</v>
+        <v>-123.4988281739643</v>
       </c>
       <c r="K23" t="n">
-        <v>12.49725030898538</v>
+        <v>12.49725030896388</v>
       </c>
       <c r="L23" t="n">
-        <v>-394.0773917252354</v>
+        <v>-394.0773917252902</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.448588741532367e-06</v>
+        <v>-5.448588832704337e-06</v>
       </c>
       <c r="N23" t="n">
-        <v>1576.857887959055</v>
+        <v>1576.857887959274</v>
       </c>
       <c r="O23" t="n">
-        <v>16.65572241141295</v>
+        <v>16.65572241132731</v>
       </c>
       <c r="P23" t="n">
-        <v>123.4988281741971</v>
+        <v>123.4988281739643</v>
       </c>
       <c r="Q23" t="n">
-        <v>-12.49725030898538</v>
+        <v>-12.49725030896388</v>
       </c>
       <c r="R23" t="n">
-        <v>394.0773917252354</v>
+        <v>394.0773917252902</v>
       </c>
       <c r="S23" t="n">
-        <v>5.448588741532367e-06</v>
+        <v>5.448588832704337e-06</v>
       </c>
       <c r="T23" t="n">
-        <v>1575.761245842828</v>
+        <v>1575.761245843047</v>
       </c>
       <c r="U23" t="n">
-        <v>83.32228006047011</v>
+        <v>83.32228006038376</v>
       </c>
     </row>
     <row r="24">
@@ -3080,7 +3080,7 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0001054962997791679</v>
+        <v>0.0001054962997791678</v>
       </c>
       <c r="G24" t="n">
         <v>1.318703747239598e-05</v>
@@ -3089,43 +3089,43 @@
         <v>12.50131152383139</v>
       </c>
       <c r="I24" t="n">
-        <v>2637.407494479197</v>
+        <v>2637.407494479196</v>
       </c>
       <c r="J24" t="n">
         <v>-12.50131152383139</v>
       </c>
       <c r="K24" t="n">
-        <v>-100.0000000000263</v>
+        <v>-100.0000000000048</v>
       </c>
       <c r="L24" t="n">
-        <v>1.254654333985444e-10</v>
+        <v>1.074449418325685e-10</v>
       </c>
       <c r="M24" t="n">
-        <v>7.751577157932843e-13</v>
+        <v>5.864198016070077e-13</v>
       </c>
       <c r="N24" t="n">
-        <v>0.001416632737978864</v>
+        <v>0.001416632810069984</v>
       </c>
       <c r="O24" t="n">
-        <v>-83.32241648536987</v>
+        <v>-83.32241648528483</v>
       </c>
       <c r="P24" t="n">
         <v>12.50131152383139</v>
       </c>
       <c r="Q24" t="n">
-        <v>-99.99999999997374</v>
+        <v>-99.99999999999523</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.254654333985444e-10</v>
+        <v>-1.074449418325685e-10</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.751577157932843e-13</v>
+        <v>-5.864198016070077e-13</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.00141663374170233</v>
+        <v>-0.001416633669628631</v>
       </c>
       <c r="U24" t="n">
-        <v>83.32241648516023</v>
+        <v>83.32241648524663</v>
       </c>
     </row>
     <row r="25">
@@ -3147,52 +3147,52 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.001042184204001373</v>
+        <v>0.001042184204003149</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001302730255001716</v>
+        <v>0.0001302730255003937</v>
       </c>
       <c r="H25" t="n">
-        <v>123.4988281741627</v>
+        <v>123.4988281743732</v>
       </c>
       <c r="I25" t="n">
-        <v>26054.60510003432</v>
+        <v>26054.60510007873</v>
       </c>
       <c r="J25" t="n">
-        <v>-123.4988281741971</v>
+        <v>-123.4988281744299</v>
       </c>
       <c r="K25" t="n">
-        <v>12.49725030893287</v>
+        <v>12.49725030895394</v>
       </c>
       <c r="L25" t="n">
-        <v>-394.0773917255378</v>
+        <v>-394.0773917255186</v>
       </c>
       <c r="M25" t="n">
-        <v>5.448590026519767e-06</v>
+        <v>5.448589935378031e-06</v>
       </c>
       <c r="N25" t="n">
-        <v>1575.761245844037</v>
+        <v>1575.761245843961</v>
       </c>
       <c r="O25" t="n">
-        <v>83.32228006026035</v>
+        <v>83.32228006034393</v>
       </c>
       <c r="P25" t="n">
-        <v>123.4988281741971</v>
+        <v>123.4988281744299</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.49725030893287</v>
+        <v>-12.49725030895394</v>
       </c>
       <c r="R25" t="n">
-        <v>394.0773917255378</v>
+        <v>394.0773917255186</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.448590026519767e-06</v>
+        <v>-5.448589935378031e-06</v>
       </c>
       <c r="T25" t="n">
-        <v>1576.857887960265</v>
+        <v>1576.857887960188</v>
       </c>
       <c r="U25" t="n">
-        <v>16.65572241120256</v>
+        <v>16.6557224112876</v>
       </c>
     </row>
     <row r="26">
@@ -3214,52 +3214,52 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0001054548126048016</v>
+        <v>-0.0001054548126048011</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.318185157560019e-05</v>
+        <v>-1.318185157560014e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>-12.49639529366899</v>
+        <v>-12.49639529366893</v>
       </c>
       <c r="I26" t="n">
-        <v>-2636.370315120039</v>
+        <v>-2636.370315120028</v>
       </c>
       <c r="J26" t="n">
-        <v>12.49639529366899</v>
+        <v>12.49639529366894</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.843059286940843e-11</v>
+        <v>-1.70530256582424e-11</v>
       </c>
       <c r="L26" t="n">
-        <v>7.886364625849396e-11</v>
+        <v>9.179013105153899e-11</v>
       </c>
       <c r="M26" t="n">
-        <v>4.087841176669826e-13</v>
+        <v>6.076250613773482e-13</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0003204382566711034</v>
+        <v>0.0003204382049224463</v>
       </c>
       <c r="O26" t="n">
-        <v>16.65569270639389</v>
+        <v>16.65569270651849</v>
       </c>
       <c r="P26" t="n">
-        <v>-12.49639529366899</v>
+        <v>-12.49639529366894</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.843059286940843e-11</v>
+        <v>1.70530256582424e-11</v>
       </c>
       <c r="R26" t="n">
-        <v>-7.886364625849396e-11</v>
+        <v>-9.179013105153899e-11</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.087841176669826e-13</v>
+        <v>-6.076250613773482e-13</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0003204388875802733</v>
+        <v>-0.0003204389392434948</v>
       </c>
       <c r="U26" t="n">
-        <v>-16.65569270678225</v>
+        <v>-16.65569270665674</v>
       </c>
     </row>
     <row r="27">
@@ -3296,37 +3296,37 @@
         <v>-132.0124954287894</v>
       </c>
       <c r="K27" t="n">
-        <v>12.49725652639148</v>
+        <v>12.49725652636022</v>
       </c>
       <c r="L27" t="n">
-        <v>-229.8566828605958</v>
+        <v>-229.856682860657</v>
       </c>
       <c r="M27" t="n">
-        <v>1.232456451699434e-06</v>
+        <v>1.232456515734565e-06</v>
       </c>
       <c r="N27" t="n">
-        <v>916.9826528315087</v>
+        <v>916.9826528317536</v>
       </c>
       <c r="O27" t="n">
-        <v>16.65569284193676</v>
+        <v>16.65569284181208</v>
       </c>
       <c r="P27" t="n">
         <v>132.0124954287894</v>
       </c>
       <c r="Q27" t="n">
-        <v>-12.49725652639148</v>
+        <v>-12.49725652636022</v>
       </c>
       <c r="R27" t="n">
-        <v>229.8566828605958</v>
+        <v>229.856682860657</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.232456451699434e-06</v>
+        <v>-1.232456515734565e-06</v>
       </c>
       <c r="T27" t="n">
-        <v>921.8708100532576</v>
+        <v>921.8708100535018</v>
       </c>
       <c r="U27" t="n">
-        <v>83.32235936919508</v>
+        <v>83.32235936906969</v>
       </c>
     </row>
     <row r="28">
@@ -3348,52 +3348,52 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>0.000105454812604793</v>
+        <v>0.0001054548126047953</v>
       </c>
       <c r="G28" t="n">
-        <v>1.318185157559913e-05</v>
+        <v>1.318185157559941e-05</v>
       </c>
       <c r="H28" t="n">
-        <v>12.49639529366798</v>
+        <v>12.49639529366824</v>
       </c>
       <c r="I28" t="n">
-        <v>2636.370315119826</v>
+        <v>2636.370315119882</v>
       </c>
       <c r="J28" t="n">
-        <v>-12.49639529366798</v>
+        <v>-12.49639529366824</v>
       </c>
       <c r="K28" t="n">
-        <v>-100.0000000000475</v>
+        <v>-100.0000000000168</v>
       </c>
       <c r="L28" t="n">
-        <v>7.919405605740729e-11</v>
+        <v>9.171041703837091e-11</v>
       </c>
       <c r="M28" t="n">
-        <v>4.084510507595951e-13</v>
+        <v>6.078471059822732e-13</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.0003204388888398558</v>
+        <v>-0.000320438938936185</v>
       </c>
       <c r="O28" t="n">
-        <v>-83.32235951285415</v>
+        <v>-83.32235951273137</v>
       </c>
       <c r="P28" t="n">
-        <v>12.49639529366798</v>
+        <v>12.49639529366824</v>
       </c>
       <c r="Q28" t="n">
-        <v>-99.99999999995248</v>
+        <v>-99.99999999998317</v>
       </c>
       <c r="R28" t="n">
-        <v>-7.919405605740729e-11</v>
+        <v>-9.171041703837091e-11</v>
       </c>
       <c r="S28" t="n">
-        <v>-4.084510507595951e-13</v>
+        <v>-6.078471059822732e-13</v>
       </c>
       <c r="T28" t="n">
-        <v>0.0003204382552865191</v>
+        <v>0.0003204382052528487</v>
       </c>
       <c r="U28" t="n">
-        <v>83.32235951247489</v>
+        <v>83.32235951259676</v>
       </c>
     </row>
     <row r="29">
@@ -3415,52 +3415,52 @@
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>0.001114029497285784</v>
+        <v>0.001114029497284008</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0001392536871607231</v>
+        <v>0.000139253687160501</v>
       </c>
       <c r="H29" t="n">
-        <v>132.0124954283655</v>
+        <v>132.012495428155</v>
       </c>
       <c r="I29" t="n">
-        <v>27850.73743214461</v>
+        <v>27850.73743210021</v>
       </c>
       <c r="J29" t="n">
-        <v>-132.0124954283237</v>
+        <v>-132.0124954280909</v>
       </c>
       <c r="K29" t="n">
-        <v>12.49725652629611</v>
+        <v>12.49725652632724</v>
       </c>
       <c r="L29" t="n">
-        <v>-229.8566828607552</v>
+        <v>-229.8566828608935</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.232455641335499e-06</v>
+        <v>-1.232455577255556e-06</v>
       </c>
       <c r="N29" t="n">
-        <v>921.870810053895</v>
+        <v>921.8708100544479</v>
       </c>
       <c r="O29" t="n">
-        <v>83.32235936881273</v>
+        <v>83.32235936893775</v>
       </c>
       <c r="P29" t="n">
-        <v>132.0124954283237</v>
+        <v>132.0124954280909</v>
       </c>
       <c r="Q29" t="n">
-        <v>-12.49725652629611</v>
+        <v>-12.49725652632724</v>
       </c>
       <c r="R29" t="n">
-        <v>229.8566828607552</v>
+        <v>229.8566828608935</v>
       </c>
       <c r="S29" t="n">
-        <v>1.232455641335499e-06</v>
+        <v>1.232455577255556e-06</v>
       </c>
       <c r="T29" t="n">
-        <v>916.9826528321462</v>
+        <v>916.9826528326996</v>
       </c>
       <c r="U29" t="n">
-        <v>16.65569284155616</v>
+        <v>16.65569284168014</v>
       </c>
     </row>
     <row r="30">
@@ -3482,52 +3482,52 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0001054632224549705</v>
+        <v>-0.0001054632224549718</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.318290280687131e-05</v>
+        <v>-1.318290280687148e-05</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.49739186091401</v>
+        <v>-12.49739186091416</v>
       </c>
       <c r="I30" t="n">
-        <v>-2636.580561374263</v>
+        <v>-2636.580561374296</v>
       </c>
       <c r="J30" t="n">
-        <v>12.49739186091401</v>
+        <v>12.49739186091416</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.91038304567337e-11</v>
+        <v>-5.616129783447832e-11</v>
       </c>
       <c r="L30" t="n">
-        <v>3.185670624457392e-11</v>
+        <v>5.1213033813724e-11</v>
       </c>
       <c r="M30" t="n">
-        <v>7.083222897108499e-14</v>
+        <v>4.203304371230843e-13</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.000115553404494969</v>
+        <v>-0.0001155534819119453</v>
       </c>
       <c r="O30" t="n">
-        <v>16.65569190043516</v>
+        <v>16.65569190032693</v>
       </c>
       <c r="P30" t="n">
-        <v>-12.49739186091401</v>
+        <v>-12.49739186091416</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.91038304567337e-11</v>
+        <v>5.616129783447832e-11</v>
       </c>
       <c r="R30" t="n">
-        <v>-3.185670624457392e-11</v>
+        <v>-5.1213033813724e-11</v>
       </c>
       <c r="S30" t="n">
-        <v>-7.083222897108499e-14</v>
+        <v>-4.203304371230843e-13</v>
       </c>
       <c r="T30" t="n">
-        <v>0.0001155531496422071</v>
+        <v>0.0001155530722067866</v>
       </c>
       <c r="U30" t="n">
-        <v>-16.65569190066799</v>
+        <v>-16.65569190077713</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>-81.74248202005401</v>
       </c>
       <c r="K31" t="n">
-        <v>12.49725630796159</v>
+        <v>12.49725630798878</v>
       </c>
       <c r="L31" t="n">
-        <v>-87.79382485851036</v>
+        <v>-87.79382485852895</v>
       </c>
       <c r="M31" t="n">
-        <v>-4.444355165871917e-07</v>
+        <v>-4.444354194820428e-07</v>
       </c>
       <c r="N31" t="n">
-        <v>362.3341356261689</v>
+        <v>362.3341356262432</v>
       </c>
       <c r="O31" t="n">
-        <v>16.65569189860274</v>
+        <v>16.65569189871105</v>
       </c>
       <c r="P31" t="n">
         <v>81.74248202005401</v>
       </c>
       <c r="Q31" t="n">
-        <v>-12.49725630796159</v>
+        <v>-12.49725630798878</v>
       </c>
       <c r="R31" t="n">
-        <v>87.79382485851036</v>
+        <v>87.79382485852895</v>
       </c>
       <c r="S31" t="n">
-        <v>4.444355165871917e-07</v>
+        <v>4.444354194820428e-07</v>
       </c>
       <c r="T31" t="n">
-        <v>340.0164632419138</v>
+        <v>340.0164632419883</v>
       </c>
       <c r="U31" t="n">
-        <v>83.32235856509004</v>
+        <v>83.32235856519915</v>
       </c>
     </row>
     <row r="32">
@@ -3616,52 +3616,52 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>0.000105463222454975</v>
+        <v>0.0001054632224549722</v>
       </c>
       <c r="G32" t="n">
-        <v>1.318290280687187e-05</v>
+        <v>1.318290280687152e-05</v>
       </c>
       <c r="H32" t="n">
-        <v>12.49739186091453</v>
+        <v>12.4973918609142</v>
       </c>
       <c r="I32" t="n">
-        <v>2636.580561374374</v>
+        <v>2636.580561374304</v>
       </c>
       <c r="J32" t="n">
-        <v>-12.49739186091453</v>
+        <v>-12.4973918609142</v>
       </c>
       <c r="K32" t="n">
-        <v>-100.0000000000293</v>
+        <v>-100.0000000000568</v>
       </c>
       <c r="L32" t="n">
-        <v>3.218251569913049e-11</v>
+        <v>5.138911518542955e-11</v>
       </c>
       <c r="M32" t="n">
-        <v>7.255307465925398e-14</v>
+        <v>4.23938661953116e-13</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0001155531482243991</v>
+        <v>0.0001155530715442055</v>
       </c>
       <c r="O32" t="n">
-        <v>-83.32235856751535</v>
+        <v>-83.32235856762449</v>
       </c>
       <c r="P32" t="n">
-        <v>12.49739186091453</v>
+        <v>12.4973918609142</v>
       </c>
       <c r="Q32" t="n">
-        <v>-99.99999999997067</v>
+        <v>-99.99999999994316</v>
       </c>
       <c r="R32" t="n">
-        <v>-3.218251569913049e-11</v>
+        <v>-5.138911518542955e-11</v>
       </c>
       <c r="S32" t="n">
-        <v>-7.255307465925398e-14</v>
+        <v>-4.23938661953116e-13</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.0001155534056854128</v>
+        <v>-0.0001155534826580151</v>
       </c>
       <c r="U32" t="n">
-        <v>83.32235856727888</v>
+        <v>83.32235856716974</v>
       </c>
     </row>
     <row r="33">
@@ -3683,52 +3683,52 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0006898099748582354</v>
+        <v>0.000689809974856459</v>
       </c>
       <c r="G33" t="n">
-        <v>8.622624685727942e-05</v>
+        <v>8.622624685705738e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>81.74248202070089</v>
+        <v>81.7424820204904</v>
       </c>
       <c r="I33" t="n">
-        <v>17245.24937145588</v>
+        <v>17245.24937141148</v>
       </c>
       <c r="J33" t="n">
-        <v>-81.7424820207525</v>
+        <v>-81.74248202051967</v>
       </c>
       <c r="K33" t="n">
-        <v>12.49725630790358</v>
+        <v>12.49725630787598</v>
       </c>
       <c r="L33" t="n">
-        <v>-87.79382485853831</v>
+        <v>-87.793824858693</v>
       </c>
       <c r="M33" t="n">
-        <v>4.444358450432963e-07</v>
+        <v>4.44435942673907e-07</v>
       </c>
       <c r="N33" t="n">
-        <v>340.0164632420261</v>
+        <v>340.0164632426455</v>
       </c>
       <c r="O33" t="n">
-        <v>83.32235856485785</v>
+        <v>83.32235856474811</v>
       </c>
       <c r="P33" t="n">
-        <v>81.7424820207525</v>
+        <v>81.74248202051967</v>
       </c>
       <c r="Q33" t="n">
-        <v>-12.49725630790358</v>
+        <v>-12.49725630787598</v>
       </c>
       <c r="R33" t="n">
-        <v>87.79382485853831</v>
+        <v>87.793824858693</v>
       </c>
       <c r="S33" t="n">
-        <v>-4.444358450432963e-07</v>
+        <v>-4.44435942673907e-07</v>
       </c>
       <c r="T33" t="n">
-        <v>362.3341356262804</v>
+        <v>362.3341356268984</v>
       </c>
       <c r="U33" t="n">
-        <v>16.65569189837078</v>
+        <v>16.65569189825973</v>
       </c>
     </row>
   </sheetData>
@@ -3991,16 +3991,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007516730126563289</v>
+        <v>0.007516730126564649</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001252788354427215</v>
+        <v>0.001252788354427442</v>
       </c>
       <c r="H2" t="n">
-        <v>1187.643359997</v>
+        <v>1187.643359997215</v>
       </c>
       <c r="I2" t="n">
-        <v>250557.670885443</v>
+        <v>250557.6708854883</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -4021,22 +4021,22 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.595119805279563</v>
+        <v>3.595119805279023</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.264656553662592e-05</v>
+        <v>5.264656576807992e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007516730126563289</v>
+        <v>0.007516730126564649</v>
       </c>
       <c r="S2" t="n">
-        <v>-5.817587131184721e-06</v>
+        <v>-5.81758716827277e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5733905572099365</v>
+        <v>0.5733905572098467</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01497636114535011</v>
+        <v>0.01497636114528572</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -4057,58 +4057,58 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007516730126563289</v>
+        <v>0.007516730126564649</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.264656553662592e-05</v>
+        <v>5.264656576807992e-05</v>
       </c>
       <c r="AD2" t="n">
-        <v>-3.595119805279563</v>
+        <v>-3.595119805279023</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.01497636114535011</v>
+        <v>0.01497636114528572</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5733905572099365</v>
+        <v>0.5733905572098467</v>
       </c>
       <c r="AG2" t="n">
-        <v>5.817587131184721e-06</v>
+        <v>5.81758716827277e-06</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1187.643359997</v>
+        <v>-1187.643359997215</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.008681138355291034</v>
+        <v>-0.008681138384937864</v>
       </c>
       <c r="AJ2" t="n">
-        <v>462.4872063002725</v>
+        <v>462.4872063002059</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.04262502787522724</v>
+        <v>-0.04262502787504397</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1811.770631236171</v>
+        <v>-1811.770631235904</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.03034842954294979</v>
+        <v>-0.03034842965933544</v>
       </c>
       <c r="AN2" t="n">
-        <v>1187.643359997</v>
+        <v>1187.643359997215</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.008681138355291034</v>
+        <v>0.008681138384937864</v>
       </c>
       <c r="AP2" t="n">
-        <v>-462.4872063002725</v>
+        <v>-462.4872063002059</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.04262502787522724</v>
+        <v>0.04262502787504397</v>
       </c>
       <c r="AR2" t="n">
-        <v>-963.1526065654646</v>
+        <v>-963.1526065653311</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.02173840058879641</v>
+        <v>-0.02173840065029174</v>
       </c>
     </row>
     <row r="3">
@@ -4130,16 +4130,16 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007516730126563006</v>
+        <v>0.007516730126563812</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001252788354427168</v>
+        <v>0.001252788354427302</v>
       </c>
       <c r="H3" t="n">
-        <v>1187.643359996955</v>
+        <v>1187.643359997082</v>
       </c>
       <c r="I3" t="n">
-        <v>250557.6708854335</v>
+        <v>250557.6708854604</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -4160,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.595119805277692</v>
+        <v>3.595119805277716</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.264656732975187e-05</v>
+        <v>-5.264656709829736e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007516730126563006</v>
+        <v>0.007516730126563812</v>
       </c>
       <c r="S3" t="n">
-        <v>5.817587439357226e-06</v>
+        <v>5.817587402268885e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5733905572095976</v>
+        <v>0.5733905572096085</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.01497636114489171</v>
+        <v>-0.0149763611449562</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -4196,58 +4196,58 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007516730126563006</v>
+        <v>0.007516730126563812</v>
       </c>
       <c r="AC3" t="n">
-        <v>-5.264656732975187e-05</v>
+        <v>-5.264656709829736e-05</v>
       </c>
       <c r="AD3" t="n">
-        <v>-3.595119805277692</v>
+        <v>-3.595119805277716</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.01497636114489171</v>
+        <v>-0.0149763611449562</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5733905572095976</v>
+        <v>0.5733905572096085</v>
       </c>
       <c r="AG3" t="n">
-        <v>-5.817587439357226e-06</v>
+        <v>-5.817587402268885e-06</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1187.643359996955</v>
+        <v>-1187.643359997083</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.00868113856954778</v>
+        <v>0.008681138539901042</v>
       </c>
       <c r="AJ3" t="n">
-        <v>462.4872063000618</v>
+        <v>462.4872063000596</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.04262502787392255</v>
+        <v>0.0426250278741061</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1811.770631235287</v>
+        <v>-1811.770631235289</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.03034843041376769</v>
+        <v>0.0303484302973821</v>
       </c>
       <c r="AN3" t="n">
-        <v>1187.643359996955</v>
+        <v>1187.643359997083</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.00868113856954778</v>
+        <v>-0.008681138539901042</v>
       </c>
       <c r="AP3" t="n">
-        <v>-462.4872063000618</v>
+        <v>-462.4872063000596</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.04262502787392255</v>
+        <v>-0.0426250278741061</v>
       </c>
       <c r="AR3" t="n">
-        <v>-963.1526065650828</v>
+        <v>-963.1526065650683</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.021738401003519</v>
+        <v>0.02173840094202415</v>
       </c>
     </row>
     <row r="4">
@@ -4269,16 +4269,16 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.007516730126563017</v>
+        <v>-0.007516730126563806</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.00125278835442717</v>
+        <v>-0.001252788354427301</v>
       </c>
       <c r="H4" t="n">
-        <v>-1187.643359996957</v>
+        <v>-1187.643359997081</v>
       </c>
       <c r="I4" t="n">
-        <v>-250557.6708854339</v>
+        <v>-250557.6708854602</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.596176627224334</v>
+        <v>3.596176627224358</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.264656733141418e-05</v>
+        <v>5.264656709531542e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.007516730126563017</v>
+        <v>-0.007516730126563806</v>
       </c>
       <c r="S4" t="n">
-        <v>-5.817587439646455e-06</v>
+        <v>-5.817587401731315e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5737082536248554</v>
+        <v>0.5737082536248662</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04500689564371815</v>
+        <v>0.04500689564365364</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -4335,58 +4335,58 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.007516730126563017</v>
+        <v>-0.007516730126563806</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.264656733141418e-05</v>
+        <v>5.264656709531542e-05</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3.596176627224334</v>
+        <v>-3.596176627224358</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.04500689564371815</v>
+        <v>0.04500689564365364</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5737082536248554</v>
+        <v>0.5737082536248662</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.817587439646455e-06</v>
+        <v>5.817587401731315e-06</v>
       </c>
       <c r="AH4" t="n">
-        <v>1187.643359996957</v>
+        <v>1187.643359997082</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.008681138569743792</v>
+        <v>-0.008681138539563298</v>
       </c>
       <c r="AJ4" t="n">
-        <v>537.5127936996093</v>
+        <v>537.5127936996073</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.1280965491398132</v>
+        <v>-0.1280965491396296</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1887.082488781221</v>
+        <v>-1887.082488781223</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.03034843041456974</v>
+        <v>-0.03034843029597107</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1187.643359996957</v>
+        <v>-1187.643359997082</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.008681138569743792</v>
+        <v>0.008681138539563298</v>
       </c>
       <c r="AP4" t="n">
-        <v>-387.5127936996093</v>
+        <v>-387.5127936996073</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.1280965491398132</v>
+        <v>0.1280965491396296</v>
       </c>
       <c r="AR4" t="n">
-        <v>-887.9942734164347</v>
+        <v>-887.9942734164206</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0.02173840100389299</v>
+        <v>-0.02173840094140872</v>
       </c>
     </row>
     <row r="5">
@@ -4408,16 +4408,16 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.00751673012656329</v>
+        <v>-0.007516730126564661</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.001252788354427215</v>
+        <v>-0.001252788354427443</v>
       </c>
       <c r="H5" t="n">
-        <v>-1187.643359997</v>
+        <v>-1187.643359997216</v>
       </c>
       <c r="I5" t="n">
-        <v>-250557.670885443</v>
+        <v>-250557.6708854887</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.596176627226205</v>
+        <v>3.596176627225665</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.264656553496323e-05</v>
+        <v>-5.264656577106183e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.00751673012656329</v>
+        <v>-0.007516730126564661</v>
       </c>
       <c r="S5" t="n">
-        <v>5.817587130890855e-06</v>
+        <v>5.817587168809183e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5737082536251945</v>
+        <v>0.5737082536251048</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.04500689564325982</v>
+        <v>-0.0450068956433242</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -4474,58 +4474,58 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.00751673012656329</v>
+        <v>-0.007516730126564661</v>
       </c>
       <c r="AC5" t="n">
-        <v>-5.264656553496323e-05</v>
+        <v>-5.264656577106183e-05</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3.596176627226205</v>
+        <v>-3.596176627225665</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.04500689564325982</v>
+        <v>-0.0450068956433242</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.5737082536251945</v>
+        <v>0.5737082536251048</v>
       </c>
       <c r="AG5" t="n">
-        <v>-5.817587130890855e-06</v>
+        <v>-5.817587168809183e-06</v>
       </c>
       <c r="AH5" t="n">
-        <v>1187.643359997</v>
+        <v>1187.643359997217</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.008681138355098365</v>
+        <v>0.008681138385276456</v>
       </c>
       <c r="AJ5" t="n">
-        <v>537.51279369982</v>
+        <v>537.5127936997534</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1280965491385087</v>
+        <v>0.1280965491386919</v>
       </c>
       <c r="AL5" t="n">
-        <v>-1887.082488782104</v>
+        <v>-1887.082488781838</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.03034842954215432</v>
+        <v>0.03034842966074816</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1187.643359997</v>
+        <v>-1187.643359997217</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.008681138355098365</v>
+        <v>-0.008681138385276456</v>
       </c>
       <c r="AP5" t="n">
-        <v>-387.51279369982</v>
+        <v>-387.5127936997534</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.1280965491385087</v>
+        <v>-0.1280965491386919</v>
       </c>
       <c r="AR5" t="n">
-        <v>-887.9942734168162</v>
+        <v>-887.9942734166825</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.02173840058843586</v>
+        <v>0.02173840065091057</v>
       </c>
     </row>
     <row r="6">
@@ -4547,124 +4547,124 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004504606958510098</v>
+        <v>0.004504606958511741</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0007507678264183497</v>
+        <v>0.0007507678264186235</v>
       </c>
       <c r="H6" t="n">
-        <v>711.7278994445956</v>
+        <v>711.7278994448551</v>
       </c>
       <c r="I6" t="n">
-        <v>150153.5652836699</v>
+        <v>150153.5652837247</v>
       </c>
       <c r="J6" t="n">
-        <v>3.595119805279563</v>
+        <v>3.595119805279023</v>
       </c>
       <c r="K6" t="n">
-        <v>5.264656553662592e-05</v>
+        <v>5.264656576807992e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007516730126563289</v>
+        <v>0.007516730126564649</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.817587131184721e-06</v>
+        <v>-5.81758716827277e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5733905572099365</v>
+        <v>0.5733905572098467</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01497636114535011</v>
+        <v>0.01497636114528572</v>
       </c>
       <c r="P6" t="n">
-        <v>8.113133295381624</v>
+        <v>8.113133295380457</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.27481476618041e-05</v>
+        <v>5.274814816710414e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01202133708507339</v>
+        <v>0.01202133708507639</v>
       </c>
       <c r="S6" t="n">
-        <v>1.276246312356512e-06</v>
+        <v>1.276246291459122e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4768655535134581</v>
+        <v>0.4768655535134355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01500508180328185</v>
+        <v>0.01500508180312803</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007516730126563289</v>
+        <v>0.007516730126564649</v>
       </c>
       <c r="W6" t="n">
-        <v>5.264656553662592e-05</v>
+        <v>5.264656576807992e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.595119805279563</v>
+        <v>-3.595119805279023</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01497636114535011</v>
+        <v>0.01497636114528572</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5733905572099365</v>
+        <v>0.5733905572098467</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.817587131184721e-06</v>
+        <v>5.81758716827277e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01202133708507339</v>
+        <v>0.01202133708507639</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.27481476618041e-05</v>
+        <v>5.274814816710414e-05</v>
       </c>
       <c r="AD6" t="n">
-        <v>-8.113133295381624</v>
+        <v>-8.113133295380457</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.01500508180328185</v>
+        <v>0.01500508180312803</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.4768655535134581</v>
+        <v>0.4768655535134355</v>
       </c>
       <c r="AG6" t="n">
-        <v>-1.276246312356512e-06</v>
+        <v>-1.276246291459122e-06</v>
       </c>
       <c r="AH6" t="n">
-        <v>-711.7278994445956</v>
+        <v>-711.7278994448552</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.003335535281722257</v>
+        <v>0.00333553525708279</v>
       </c>
       <c r="AJ6" t="n">
-        <v>337.2538056231967</v>
+        <v>337.2538056231251</v>
       </c>
       <c r="AK6" t="n">
-        <v>-8.174341103647093e-05</v>
+        <v>-8.17434107819523e-05</v>
       </c>
       <c r="AL6" t="n">
-        <v>-940.3329141341959</v>
+        <v>-940.3329141340305</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.01525604259338728</v>
+        <v>0.01525604253144997</v>
       </c>
       <c r="AN6" t="n">
-        <v>711.7278994445956</v>
+        <v>711.7278994448552</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.003335535281722257</v>
+        <v>-0.00333553525708279</v>
       </c>
       <c r="AP6" t="n">
-        <v>-337.2538056231967</v>
+        <v>-337.2538056231251</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.174341103647093e-05</v>
+        <v>8.17434107819523e-05</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1083.189919604984</v>
+        <v>-1083.189919604719</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.004757169096946262</v>
+        <v>0.004757169011046773</v>
       </c>
     </row>
     <row r="7">
@@ -4686,124 +4686,124 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004504606958509978</v>
+        <v>0.004504606958510925</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007507678264183296</v>
+        <v>0.0007507678264184874</v>
       </c>
       <c r="H7" t="n">
-        <v>711.7278994445765</v>
+        <v>711.7278994447261</v>
       </c>
       <c r="I7" t="n">
-        <v>150153.5652836659</v>
+        <v>150153.5652836975</v>
       </c>
       <c r="J7" t="n">
-        <v>3.595119805277692</v>
+        <v>3.595119805277716</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.264656732975187e-05</v>
+        <v>-5.264656709829736e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007516730126563006</v>
+        <v>0.007516730126563812</v>
       </c>
       <c r="M7" t="n">
-        <v>5.817587439357226e-06</v>
+        <v>5.817587402268885e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5733905572095976</v>
+        <v>0.5733905572096085</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.01497636114489171</v>
+        <v>-0.0149763611449562</v>
       </c>
       <c r="P7" t="n">
-        <v>8.113133295376661</v>
+        <v>8.11313329537693</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.274815211736379e-05</v>
+        <v>-5.274815161206213e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01202133708507298</v>
+        <v>0.01202133708507474</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.276246011702428e-06</v>
+        <v>-1.276246032599108e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4768655535130946</v>
+        <v>0.4768655535131607</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.01500508180210351</v>
+        <v>-0.01500508180225687</v>
       </c>
       <c r="V7" t="n">
-        <v>0.007516730126563006</v>
+        <v>0.007516730126563812</v>
       </c>
       <c r="W7" t="n">
-        <v>-5.264656732975187e-05</v>
+        <v>-5.264656709829736e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.595119805277692</v>
+        <v>-3.595119805277716</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.01497636114489171</v>
+        <v>-0.0149763611449562</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5733905572095976</v>
+        <v>0.5733905572096085</v>
       </c>
       <c r="AA7" t="n">
-        <v>-5.817587439357226e-06</v>
+        <v>-5.817587402268885e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01202133708507298</v>
+        <v>0.01202133708507474</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.274815211736379e-05</v>
+        <v>-5.274815161206213e-05</v>
       </c>
       <c r="AD7" t="n">
-        <v>-8.113133295376661</v>
+        <v>-8.11313329537693</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.01500508180210351</v>
+        <v>-0.01500508180225687</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.4768655535130946</v>
+        <v>0.4768655535131607</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.276246011702428e-06</v>
+        <v>1.276246032599108e-06</v>
       </c>
       <c r="AH7" t="n">
-        <v>-711.7278994445767</v>
+        <v>-711.7278994447263</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.003335535075520275</v>
+        <v>-0.003335535100160325</v>
       </c>
       <c r="AJ7" t="n">
-        <v>337.2538056229537</v>
+        <v>337.2538056229571</v>
       </c>
       <c r="AK7" t="n">
-        <v>8.174340898744331e-05</v>
+        <v>8.174340924035906e-05</v>
       </c>
       <c r="AL7" t="n">
-        <v>-940.3329141334489</v>
+        <v>-940.3329141334998</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.01525604198034497</v>
+        <v>-0.0152560420422833</v>
       </c>
       <c r="AN7" t="n">
-        <v>711.7278994445767</v>
+        <v>711.7278994447263</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.003335535075520275</v>
+        <v>0.003335535100160325</v>
       </c>
       <c r="AP7" t="n">
-        <v>-337.2538056229537</v>
+        <v>-337.2538056229571</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-8.174340898744331e-05</v>
+        <v>-8.174340924035906e-05</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1083.189919604273</v>
+        <v>-1083.189919604242</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.004757168472776685</v>
+        <v>-0.004757168558678665</v>
       </c>
     </row>
     <row r="8">
@@ -4825,124 +4825,124 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.004504606958509985</v>
+        <v>-0.004504606958510924</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0007507678264183309</v>
+        <v>-0.0007507678264184873</v>
       </c>
       <c r="H8" t="n">
-        <v>-711.7278994445777</v>
+        <v>-711.7278994447259</v>
       </c>
       <c r="I8" t="n">
-        <v>-150153.5652836662</v>
+        <v>-150153.5652836974</v>
       </c>
       <c r="J8" t="n">
-        <v>3.596176627224334</v>
+        <v>3.596176627224358</v>
       </c>
       <c r="K8" t="n">
-        <v>5.264656733141418e-05</v>
+        <v>5.264656709531542e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.007516730126563017</v>
+        <v>-0.007516730126563806</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.817587439646455e-06</v>
+        <v>-5.817587401731315e-06</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5737082536248554</v>
+        <v>0.5737082536248662</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04500689564371815</v>
+        <v>0.04500689564365364</v>
       </c>
       <c r="P8" t="n">
-        <v>8.114175479580663</v>
+        <v>8.114175479580929</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.274815212167277e-05</v>
+        <v>5.274815160420837e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.012021337085073</v>
+        <v>-0.01202133708507473</v>
       </c>
       <c r="S8" t="n">
-        <v>1.27624601135778e-06</v>
+        <v>1.276246033172293e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4758775876426199</v>
+        <v>0.4758775876426864</v>
       </c>
       <c r="U8" t="n">
-        <v>0.04505488004389391</v>
+        <v>0.04505488004373993</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.007516730126563017</v>
+        <v>-0.007516730126563806</v>
       </c>
       <c r="W8" t="n">
-        <v>5.264656733141418e-05</v>
+        <v>5.264656709531542e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.596176627224334</v>
+        <v>-3.596176627224358</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.04500689564371815</v>
+        <v>0.04500689564365364</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5737082536248554</v>
+        <v>0.5737082536248662</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.817587439646455e-06</v>
+        <v>5.817587401731315e-06</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.012021337085073</v>
+        <v>-0.01202133708507473</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.274815212167277e-05</v>
+        <v>5.274815160420837e-05</v>
       </c>
       <c r="AD8" t="n">
-        <v>-8.114175479580663</v>
+        <v>-8.114175479580929</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.04505488004389391</v>
+        <v>0.04505488004373993</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.4758775876426199</v>
+        <v>0.4758775876426864</v>
       </c>
       <c r="AG8" t="n">
-        <v>-1.27624601135778e-06</v>
+        <v>-1.276246033172293e-06</v>
       </c>
       <c r="AH8" t="n">
-        <v>711.7278994445778</v>
+        <v>711.7278994447261</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.003335535075336502</v>
+        <v>0.003335535100540082</v>
       </c>
       <c r="AJ8" t="n">
-        <v>412.7461943766295</v>
+        <v>412.7461943766323</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.0001365709851156582</v>
+        <v>-0.0001365709848609731</v>
       </c>
       <c r="AL8" t="n">
-        <v>-1015.843890303033</v>
+        <v>-1015.843890303083</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.01525604197975264</v>
+        <v>0.01525604204344892</v>
       </c>
       <c r="AN8" t="n">
-        <v>-711.7278994445778</v>
+        <v>-711.7278994447261</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.003335535075336502</v>
+        <v>-0.003335535100540082</v>
       </c>
       <c r="AP8" t="n">
-        <v>-262.7461943766295</v>
+        <v>-262.7461943766323</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0001365709851156582</v>
+        <v>0.0001365709848609731</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1010.633275956742</v>
+        <v>-1010.633275956709</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.004757168472266371</v>
+        <v>0.004757168559791573</v>
       </c>
     </row>
     <row r="9">
@@ -4964,124 +4964,124 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.004504606958510099</v>
+        <v>-0.004504606958511742</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0007507678264183498</v>
+        <v>-0.0007507678264186236</v>
       </c>
       <c r="H9" t="n">
-        <v>-711.7278994445957</v>
+        <v>-711.7278994448552</v>
       </c>
       <c r="I9" t="n">
-        <v>-150153.56528367</v>
+        <v>-150153.5652837247</v>
       </c>
       <c r="J9" t="n">
-        <v>3.596176627226205</v>
+        <v>3.596176627225665</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.264656553496323e-05</v>
+        <v>-5.264656577106183e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.00751673012656329</v>
+        <v>-0.007516730126564661</v>
       </c>
       <c r="M9" t="n">
-        <v>5.817587130890855e-06</v>
+        <v>5.817587168809183e-06</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5737082536251945</v>
+        <v>0.5737082536251048</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.04500689564325982</v>
+        <v>-0.0450068956433242</v>
       </c>
       <c r="P9" t="n">
-        <v>8.114175479585626</v>
+        <v>8.114175479584461</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.27481476574951e-05</v>
+        <v>-5.274814817495947e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.01202133708507339</v>
+        <v>-0.0120213370850764</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.276246312679776e-06</v>
+        <v>-1.276246290880136e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.475877587642983</v>
+        <v>0.4758775876429612</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.04505488004271615</v>
+        <v>-0.04505488004286866</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.00751673012656329</v>
+        <v>-0.007516730126564661</v>
       </c>
       <c r="W9" t="n">
-        <v>-5.264656553496323e-05</v>
+        <v>-5.264656577106183e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.596176627226205</v>
+        <v>-3.596176627225665</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.04500689564325982</v>
+        <v>-0.0450068956433242</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.5737082536251945</v>
+        <v>0.5737082536251048</v>
       </c>
       <c r="AA9" t="n">
-        <v>-5.817587130890855e-06</v>
+        <v>-5.817587168809183e-06</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.01202133708507339</v>
+        <v>-0.0120213370850764</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.27481476574951e-05</v>
+        <v>-5.274814817495947e-05</v>
       </c>
       <c r="AD9" t="n">
-        <v>-8.114175479585626</v>
+        <v>-8.114175479584461</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.04505488004271615</v>
+        <v>-0.04505488004286866</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.475877587642983</v>
+        <v>0.4758775876429612</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.276246312679776e-06</v>
+        <v>1.276246290880136e-06</v>
       </c>
       <c r="AH9" t="n">
-        <v>711.7278994445958</v>
+        <v>711.7278994448554</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.003335535281918336</v>
+        <v>-0.003335535256706077</v>
       </c>
       <c r="AJ9" t="n">
-        <v>412.7461943768724</v>
+        <v>412.7461943768008</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0001365709830680184</v>
+        <v>0.0001365709833188455</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1015.843890303781</v>
+        <v>-1015.843890303616</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.01525604259399728</v>
+        <v>-0.01525604253028832</v>
       </c>
       <c r="AN9" t="n">
-        <v>-711.7278994445958</v>
+        <v>-711.7278994448554</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.003335535281918336</v>
+        <v>0.003335535256706077</v>
       </c>
       <c r="AP9" t="n">
-        <v>-262.7461943768724</v>
+        <v>-262.7461943768008</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.0001365709830680184</v>
+        <v>-0.0001365709833188455</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1010.633275957454</v>
+        <v>-1010.633275957188</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0.00475716909751274</v>
+        <v>-0.004757169009948131</v>
       </c>
     </row>
     <row r="10">
@@ -5103,124 +5103,124 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002010446251387233</v>
+        <v>0.002010446251388883</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003350743752312055</v>
+        <v>0.0003350743752314805</v>
       </c>
       <c r="H10" t="n">
-        <v>317.6505077191828</v>
+        <v>317.6505077194435</v>
       </c>
       <c r="I10" t="n">
-        <v>67014.8750462411</v>
+        <v>67014.87504629609</v>
       </c>
       <c r="J10" t="n">
-        <v>8.113133295381624</v>
+        <v>8.113133295380457</v>
       </c>
       <c r="K10" t="n">
-        <v>5.27481476618041e-05</v>
+        <v>5.274814816710414e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01202133708507339</v>
+        <v>0.01202133708507639</v>
       </c>
       <c r="M10" t="n">
-        <v>1.276246312356512e-06</v>
+        <v>1.276246291459122e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4768655535134581</v>
+        <v>0.4768655535134355</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01500508180328185</v>
+        <v>0.01500508180312803</v>
       </c>
       <c r="P10" t="n">
-        <v>11.24253477912758</v>
+        <v>11.24253477912691</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.272740302799424e-05</v>
+        <v>5.272740356380378e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01403178333646062</v>
+        <v>0.01403178333646527</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.886833036039658e-07</v>
+        <v>-2.886832883124274e-07</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2774101967681684</v>
+        <v>0.2774101967683359</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01500512856537014</v>
+        <v>0.01500512856519697</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01202133708507339</v>
+        <v>0.01202133708507639</v>
       </c>
       <c r="W10" t="n">
-        <v>5.27481476618041e-05</v>
+        <v>5.274814816710414e-05</v>
       </c>
       <c r="X10" t="n">
-        <v>-8.113133295381624</v>
+        <v>-8.113133295380457</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01500508180328185</v>
+        <v>0.01500508180312803</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.4768655535134581</v>
+        <v>0.4768655535134355</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.276246312356512e-06</v>
+        <v>-1.276246291459122e-06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.01403178333646062</v>
+        <v>0.01403178333646527</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.272740302799424e-05</v>
+        <v>5.272740356380378e-05</v>
       </c>
       <c r="AD10" t="n">
-        <v>-11.24253477912758</v>
+        <v>-11.24253477912691</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.01500512856537014</v>
+        <v>0.01500512856519697</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2774101967681684</v>
+        <v>0.2774101967683359</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.886833036039658e-07</v>
+        <v>2.886832883124274e-07</v>
       </c>
       <c r="AH10" t="n">
-        <v>-317.6505077191828</v>
+        <v>-317.6505077194436</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.000725679616803785</v>
+        <v>-0.0007256796201811321</v>
       </c>
       <c r="AJ10" t="n">
-        <v>213.7549774489315</v>
+        <v>213.7549774489485</v>
       </c>
       <c r="AK10" t="n">
-        <v>-1.330920974471073e-07</v>
+        <v>-1.330920423731063e-07</v>
       </c>
       <c r="AL10" t="n">
-        <v>-493.6679683552808</v>
+        <v>-493.6679683554712</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.003335086766222121</v>
+        <v>-0.003335086749574341</v>
       </c>
       <c r="AN10" t="n">
-        <v>317.6505077191828</v>
+        <v>317.6505077194436</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.000725679616803785</v>
+        <v>0.0007256796201811321</v>
       </c>
       <c r="AP10" t="n">
-        <v>-213.7549774489315</v>
+        <v>-213.7549774489485</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.330920974471073e-07</v>
+        <v>1.330920423731063e-07</v>
       </c>
       <c r="AR10" t="n">
-        <v>-788.861896338309</v>
+        <v>-788.8618963382187</v>
       </c>
       <c r="AS10" t="n">
-        <v>-0.00101899093460061</v>
+        <v>-0.001018990971512444</v>
       </c>
     </row>
     <row r="11">
@@ -5242,124 +5242,124 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00201044625138745</v>
+        <v>0.002010446251388151</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003350743752312416</v>
+        <v>0.0003350743752313584</v>
       </c>
       <c r="H11" t="n">
-        <v>317.6505077192171</v>
+        <v>317.6505077193278</v>
       </c>
       <c r="I11" t="n">
-        <v>67014.87504624833</v>
+        <v>67014.87504627169</v>
       </c>
       <c r="J11" t="n">
-        <v>8.113133295376661</v>
+        <v>8.11313329537693</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.274815211736379e-05</v>
+        <v>-5.274815161206213e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01202133708507298</v>
+        <v>0.01202133708507474</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.276246011702428e-06</v>
+        <v>-1.276246032599108e-06</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4768655535130946</v>
+        <v>0.4768655535131607</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.01500508180210351</v>
+        <v>-0.01500508180225687</v>
       </c>
       <c r="P11" t="n">
-        <v>11.2425347791201</v>
+        <v>11.24253477912112</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.272740957680732e-05</v>
+        <v>-5.272740904099736e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01403178333646043</v>
+        <v>0.01403178333646289</v>
       </c>
       <c r="S11" t="n">
-        <v>2.886834930193329e-07</v>
+        <v>2.886835082336281e-07</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2774101967679769</v>
+        <v>0.2774101967680513</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.01500512856361739</v>
+        <v>-0.01500512856379087</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01202133708507298</v>
+        <v>0.01202133708507474</v>
       </c>
       <c r="W11" t="n">
-        <v>-5.274815211736379e-05</v>
+        <v>-5.274815161206213e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.113133295376661</v>
+        <v>-8.11313329537693</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.01500508180210351</v>
+        <v>-0.01500508180225687</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.4768655535130946</v>
+        <v>0.4768655535131607</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.276246011702428e-06</v>
+        <v>1.276246032599108e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01403178333646043</v>
+        <v>0.01403178333646289</v>
       </c>
       <c r="AC11" t="n">
-        <v>-5.272740957680732e-05</v>
+        <v>-5.272740904099736e-05</v>
       </c>
       <c r="AD11" t="n">
-        <v>-11.2425347791201</v>
+        <v>-11.24253477912112</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.01500512856361739</v>
+        <v>-0.01500512856379087</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.2774101967679769</v>
+        <v>0.2774101967680513</v>
       </c>
       <c r="AG11" t="n">
-        <v>-2.886834930193329e-07</v>
+        <v>-2.886835082336281e-07</v>
       </c>
       <c r="AH11" t="n">
-        <v>-317.6505077192171</v>
+        <v>-317.6505077193278</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0007256797704882252</v>
+        <v>0.0007256797671678136</v>
       </c>
       <c r="AJ11" t="n">
-        <v>213.7549774487221</v>
+        <v>213.7549774488043</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.330904625743146e-07</v>
+        <v>1.330905198618226e-07</v>
       </c>
       <c r="AL11" t="n">
-        <v>-493.6679683547802</v>
+        <v>-493.6679683550301</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.003335087144958782</v>
+        <v>0.003335087161719666</v>
       </c>
       <c r="AN11" t="n">
-        <v>317.6505077192171</v>
+        <v>317.6505077193278</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.0007256797704882252</v>
+        <v>-0.0007256797671678136</v>
       </c>
       <c r="AP11" t="n">
-        <v>-213.7549774487221</v>
+        <v>-213.7549774488043</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.330904625743146e-07</v>
+        <v>-1.330905198618226e-07</v>
       </c>
       <c r="AR11" t="n">
-        <v>-788.8618963375543</v>
+        <v>-788.8618963377921</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.001018991477970577</v>
+        <v>0.001018991441287212</v>
       </c>
     </row>
     <row r="12">
@@ -5381,124 +5381,124 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.002010446251387455</v>
+        <v>-0.002010446251388158</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0003350743752312425</v>
+        <v>-0.0003350743752313596</v>
       </c>
       <c r="H12" t="n">
-        <v>-317.6505077192179</v>
+        <v>-317.6505077193289</v>
       </c>
       <c r="I12" t="n">
-        <v>-67014.8750462485</v>
+        <v>-67014.87504627192</v>
       </c>
       <c r="J12" t="n">
-        <v>8.114175479580663</v>
+        <v>8.114175479580929</v>
       </c>
       <c r="K12" t="n">
-        <v>5.274815212167277e-05</v>
+        <v>5.274815160420837e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.012021337085073</v>
+        <v>-0.01202133708507473</v>
       </c>
       <c r="M12" t="n">
-        <v>1.27624601135778e-06</v>
+        <v>1.276246033172293e-06</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4758775876426199</v>
+        <v>0.4758775876426864</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04505488004389391</v>
+        <v>0.04505488004373993</v>
       </c>
       <c r="P12" t="n">
-        <v>11.24364880861739</v>
+        <v>11.24364880861841</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.272740958393851e-05</v>
+        <v>5.27274090296737e-05</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.01403178333646046</v>
+        <v>-0.01403178333646289</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.886834933623841e-07</v>
+        <v>-2.886835081465285e-07</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2818139420127958</v>
+        <v>0.2818139420128695</v>
       </c>
       <c r="U12" t="n">
-        <v>0.04505493137084957</v>
+        <v>0.04505493137067544</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.012021337085073</v>
+        <v>-0.01202133708507473</v>
       </c>
       <c r="W12" t="n">
-        <v>5.274815212167277e-05</v>
+        <v>5.274815160420837e-05</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.114175479580663</v>
+        <v>-8.114175479580929</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.04505488004389391</v>
+        <v>0.04505488004373993</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.4758775876426199</v>
+        <v>0.4758775876426864</v>
       </c>
       <c r="AA12" t="n">
-        <v>-1.27624601135778e-06</v>
+        <v>-1.276246033172293e-06</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.01403178333646046</v>
+        <v>-0.01403178333646289</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.272740958393851e-05</v>
+        <v>5.27274090296737e-05</v>
       </c>
       <c r="AD12" t="n">
-        <v>-11.24364880861739</v>
+        <v>-11.24364880861841</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.04505493137084957</v>
+        <v>0.04505493137067544</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2818139420127958</v>
+        <v>0.2818139420128695</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.886834933623841e-07</v>
+        <v>2.886835081465285e-07</v>
       </c>
       <c r="AH12" t="n">
-        <v>317.6505077192182</v>
+        <v>317.650507719329</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.0007256797706754747</v>
+        <v>-0.0007256797668005119</v>
       </c>
       <c r="AJ12" t="n">
-        <v>286.2450225507185</v>
+        <v>286.245022550801</v>
       </c>
       <c r="AK12" t="n">
-        <v>-1.460844122613825e-07</v>
+        <v>-1.460843549183632e-07</v>
       </c>
       <c r="AL12" t="n">
-        <v>-565.1279698860859</v>
+        <v>-565.1279698863391</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.003335087145519354</v>
+        <v>-0.003335087160977454</v>
       </c>
       <c r="AN12" t="n">
-        <v>-317.6505077192182</v>
+        <v>-317.650507719329</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0007256797706754747</v>
+        <v>0.0007256797668005119</v>
       </c>
       <c r="AP12" t="n">
-        <v>-136.2450225507185</v>
+        <v>-136.245022550801</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.460844122613825e-07</v>
+        <v>1.460843549183632e-07</v>
       </c>
       <c r="AR12" t="n">
-        <v>-702.342165418225</v>
+        <v>-702.3421654184676</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0.001018991478533501</v>
+        <v>-0.001018991439825603</v>
       </c>
     </row>
     <row r="13">
@@ -5520,124 +5520,124 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.002010446251387236</v>
+        <v>-0.002010446251388881</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0003350743752312061</v>
+        <v>-0.0003350743752314801</v>
       </c>
       <c r="H13" t="n">
-        <v>-317.6505077191833</v>
+        <v>-317.6505077194432</v>
       </c>
       <c r="I13" t="n">
-        <v>-67014.87504624121</v>
+        <v>-67014.87504629603</v>
       </c>
       <c r="J13" t="n">
-        <v>8.114175479585626</v>
+        <v>8.114175479584461</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.27481476574951e-05</v>
+        <v>-5.274814817495947e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.01202133708507339</v>
+        <v>-0.0120213370850764</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.276246312679776e-06</v>
+        <v>-1.276246290880136e-06</v>
       </c>
       <c r="N13" t="n">
-        <v>0.475877587642983</v>
+        <v>0.4758775876429612</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.04505488004271615</v>
+        <v>-0.04505488004286866</v>
       </c>
       <c r="P13" t="n">
-        <v>11.24364880862486</v>
+        <v>11.2436488086242</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.272740302085454e-05</v>
+        <v>-5.272740357512158e-05</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.01403178333646063</v>
+        <v>-0.01403178333646528</v>
       </c>
       <c r="S13" t="n">
-        <v>2.886833031477993e-07</v>
+        <v>2.88683288419905e-07</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2818139420129872</v>
+        <v>0.2818139420131543</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.04505493136909523</v>
+        <v>-0.04505493136926936</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.01202133708507339</v>
+        <v>-0.0120213370850764</v>
       </c>
       <c r="W13" t="n">
-        <v>-5.27481476574951e-05</v>
+        <v>-5.274814817495947e-05</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.114175479585626</v>
+        <v>-8.114175479584461</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.04505488004271615</v>
+        <v>-0.04505488004286866</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.475877587642983</v>
+        <v>0.4758775876429612</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.276246312679776e-06</v>
+        <v>1.276246290880136e-06</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.01403178333646063</v>
+        <v>-0.01403178333646528</v>
       </c>
       <c r="AC13" t="n">
-        <v>-5.272740302085454e-05</v>
+        <v>-5.272740357512158e-05</v>
       </c>
       <c r="AD13" t="n">
-        <v>-11.24364880862486</v>
+        <v>-11.2436488086242</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.04505493136909523</v>
+        <v>-0.04505493136926936</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.2818139420129872</v>
+        <v>0.2818139420131543</v>
       </c>
       <c r="AG13" t="n">
-        <v>-2.886833031477993e-07</v>
+        <v>-2.88683288419905e-07</v>
       </c>
       <c r="AH13" t="n">
-        <v>317.6505077191835</v>
+        <v>317.6505077194431</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0007256796166823266</v>
+        <v>0.000725679620527225</v>
       </c>
       <c r="AJ13" t="n">
-        <v>286.245022550927</v>
+        <v>286.2450225509428</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.460827712407298e-07</v>
+        <v>1.460828327748409e-07</v>
       </c>
       <c r="AL13" t="n">
-        <v>-565.127969886584</v>
+        <v>-565.1279698867711</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.003335086765759374</v>
+        <v>0.003335086750263713</v>
       </c>
       <c r="AN13" t="n">
-        <v>-317.6505077191835</v>
+        <v>-317.6505077194431</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.0007256796166823266</v>
+        <v>-0.000725679620527225</v>
       </c>
       <c r="AP13" t="n">
-        <v>-136.245022550927</v>
+        <v>-136.2450225509428</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-1.460827712407298e-07</v>
+        <v>-1.460828327748409e-07</v>
       </c>
       <c r="AR13" t="n">
-        <v>-702.3421654189774</v>
+        <v>-702.342165418886</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.001018990934334565</v>
+        <v>0.001018990972899647</v>
       </c>
     </row>
     <row r="14">
@@ -5659,124 +5659,124 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0005556571193576412</v>
+        <v>0.0005556571193584946</v>
       </c>
       <c r="G14" t="n">
-        <v>9.260951989294019e-05</v>
+        <v>9.260951989308244e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>87.79382485850731</v>
+        <v>87.79382485864215</v>
       </c>
       <c r="I14" t="n">
-        <v>18521.90397858804</v>
+        <v>18521.90397861649</v>
       </c>
       <c r="J14" t="n">
-        <v>11.24253477912758</v>
+        <v>11.24253477912691</v>
       </c>
       <c r="K14" t="n">
-        <v>5.272740302799424e-05</v>
+        <v>5.272740356380378e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01403178333646062</v>
+        <v>0.01403178333646527</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.886833036039658e-07</v>
+        <v>-2.886832883124274e-07</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2774101967681684</v>
+        <v>0.2774101967683359</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01500512856537014</v>
+        <v>0.01500512856519697</v>
       </c>
       <c r="P14" t="n">
-        <v>12.7636275507655</v>
+        <v>12.76362755076675</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.273160743815383e-05</v>
+        <v>5.273160774713402e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01458744045581826</v>
+        <v>0.01458744045582377</v>
       </c>
       <c r="S14" t="n">
-        <v>1.041020896839185e-07</v>
+        <v>1.041021125745989e-07</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1191579135705716</v>
+        <v>0.1191579135707582</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01500512783931789</v>
+        <v>0.01500512783927177</v>
       </c>
       <c r="V14" t="n">
-        <v>0.01403178333646062</v>
+        <v>0.01403178333646527</v>
       </c>
       <c r="W14" t="n">
-        <v>5.272740302799424e-05</v>
+        <v>5.272740356380378e-05</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.24253477912758</v>
+        <v>-11.24253477912691</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.01500512856537014</v>
+        <v>0.01500512856519697</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.2774101967681684</v>
+        <v>0.2774101967683359</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.886833036039658e-07</v>
+        <v>2.886832883124274e-07</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.01458744045581826</v>
+        <v>0.01458744045582377</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.273160743815383e-05</v>
+        <v>5.273160774713402e-05</v>
       </c>
       <c r="AD14" t="n">
-        <v>-12.7636275507655</v>
+        <v>-12.76362755076675</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.01500512783931789</v>
+        <v>0.01500512783927177</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1191579135705716</v>
+        <v>0.1191579135707582</v>
       </c>
       <c r="AG14" t="n">
-        <v>-1.041020896839185e-07</v>
+        <v>-1.041021125745989e-07</v>
       </c>
       <c r="AH14" t="n">
-        <v>-87.79382485850738</v>
+        <v>-87.79382485864198</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.000135553010461472</v>
+        <v>0.0001355530381578693</v>
       </c>
       <c r="AJ14" t="n">
-        <v>81.74248202001982</v>
+        <v>81.74248202023045</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.066456408766904e-09</v>
+        <v>2.066094795249995e-09</v>
       </c>
       <c r="AL14" t="n">
-        <v>-128.1207564938366</v>
+        <v>-128.1207564944852</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0006973202224174468</v>
+        <v>0.000697320311130005</v>
       </c>
       <c r="AN14" t="n">
-        <v>87.79382485850738</v>
+        <v>87.79382485864198</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.000135553010461472</v>
+        <v>-0.0001355530381578693</v>
       </c>
       <c r="AP14" t="n">
-        <v>-81.74248202001982</v>
+        <v>-81.74248202023045</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-2.066456408766904e-09</v>
+        <v>-2.066094795249995e-09</v>
       </c>
       <c r="AR14" t="n">
-        <v>-362.3341356262787</v>
+        <v>-362.3341356268993</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0001159978403513784</v>
+        <v>0.0001159979178172107</v>
       </c>
     </row>
     <row r="15">
@@ -5798,124 +5798,124 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0005556571193578615</v>
+        <v>0.0005556571193580991</v>
       </c>
       <c r="G15" t="n">
-        <v>9.260951989297692e-05</v>
+        <v>9.260951989301652e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>87.79382485854211</v>
+        <v>87.79382485857967</v>
       </c>
       <c r="I15" t="n">
-        <v>18521.90397859538</v>
+        <v>18521.9039786033</v>
       </c>
       <c r="J15" t="n">
-        <v>11.2425347791201</v>
+        <v>11.24253477912112</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.272740957680732e-05</v>
+        <v>-5.272740904099736e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01403178333646043</v>
+        <v>0.01403178333646289</v>
       </c>
       <c r="M15" t="n">
-        <v>2.886834930193329e-07</v>
+        <v>2.886835082336281e-07</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2774101967679769</v>
+        <v>0.2774101967680513</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.01500512856361739</v>
+        <v>-0.01500512856379087</v>
       </c>
       <c r="P15" t="n">
-        <v>12.76362755075735</v>
+        <v>12.76362755075872</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.273161501681668e-05</v>
+        <v>-5.273161470783783e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>0.01458744045581829</v>
+        <v>0.01458744045582099</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.041020131429611e-07</v>
+        <v>-1.041019902353731e-07</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1191579135705384</v>
+        <v>0.1191579135705613</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.01500512783735091</v>
+        <v>-0.01500512783739848</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01403178333646043</v>
+        <v>0.01403178333646289</v>
       </c>
       <c r="W15" t="n">
-        <v>-5.272740957680732e-05</v>
+        <v>-5.272740904099736e-05</v>
       </c>
       <c r="X15" t="n">
-        <v>-11.2425347791201</v>
+        <v>-11.24253477912112</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.01500512856361739</v>
+        <v>-0.01500512856379087</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.2774101967679769</v>
+        <v>0.2774101967680513</v>
       </c>
       <c r="AA15" t="n">
-        <v>-2.886834930193329e-07</v>
+        <v>-2.886835082336281e-07</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.01458744045581829</v>
+        <v>0.01458744045582099</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.273161501681668e-05</v>
+        <v>-5.273161470783783e-05</v>
       </c>
       <c r="AD15" t="n">
-        <v>-12.76362755075735</v>
+        <v>-12.76362755075872</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.01500512783735091</v>
+        <v>-0.01500512783739848</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1191579135705384</v>
+        <v>0.1191579135705613</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.041020131429611e-07</v>
+        <v>1.041019902353731e-07</v>
       </c>
       <c r="AH15" t="n">
-        <v>-87.79382485854194</v>
+        <v>-87.79382485857968</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.0001355529532395382</v>
+        <v>-0.0001355529254980607</v>
       </c>
       <c r="AJ15" t="n">
-        <v>81.74248202002072</v>
+        <v>81.74248202003355</v>
       </c>
       <c r="AK15" t="n">
-        <v>-2.06706612937424e-09</v>
+        <v>-2.067424516305483e-09</v>
       </c>
       <c r="AL15" t="n">
-        <v>-128.1207564939566</v>
+        <v>-128.1207564939577</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0.0006973201342787144</v>
+        <v>-0.0006973200453612369</v>
       </c>
       <c r="AN15" t="n">
-        <v>87.79382485854194</v>
+        <v>87.79382485857968</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0001355529532395382</v>
+        <v>0.0001355529254980607</v>
       </c>
       <c r="AP15" t="n">
-        <v>-81.74248202002072</v>
+        <v>-81.74248202003355</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.06706612937424e-09</v>
+        <v>2.067424516305483e-09</v>
       </c>
       <c r="AR15" t="n">
-        <v>-362.3341356261658</v>
+        <v>-362.3341356262445</v>
       </c>
       <c r="AS15" t="n">
-        <v>-0.0001159975851585185</v>
+        <v>-0.0001159975076271205</v>
       </c>
     </row>
     <row r="16">
@@ -5937,124 +5937,124 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0005556571193578649</v>
+        <v>-0.0005556571193581009</v>
       </c>
       <c r="G16" t="n">
-        <v>-9.260951989297748e-05</v>
+        <v>-9.260951989301681e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>-87.79382485854266</v>
+        <v>-87.79382485857994</v>
       </c>
       <c r="I16" t="n">
-        <v>-18521.9039785955</v>
+        <v>-18521.90397860336</v>
       </c>
       <c r="J16" t="n">
-        <v>11.24364880861739</v>
+        <v>11.24364880861841</v>
       </c>
       <c r="K16" t="n">
-        <v>5.272740958393851e-05</v>
+        <v>5.27274090296737e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.01403178333646046</v>
+        <v>-0.01403178333646289</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.886834933623841e-07</v>
+        <v>-2.886835081465285e-07</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2818139420127958</v>
+        <v>0.2818139420128695</v>
       </c>
       <c r="O16" t="n">
-        <v>0.04505493137084957</v>
+        <v>0.04505493137067544</v>
       </c>
       <c r="P16" t="n">
-        <v>12.76431736073221</v>
+        <v>12.76431736073357</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.273161502770671e-05</v>
+        <v>5.273161469785554e-05</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.01458744045581832</v>
+        <v>-0.01458744045582099</v>
       </c>
       <c r="S16" t="n">
-        <v>1.041020126456332e-07</v>
+        <v>1.041019900625209e-07</v>
       </c>
       <c r="T16" t="n">
-        <v>0.09905190241355175</v>
+        <v>0.09905190241357491</v>
       </c>
       <c r="U16" t="n">
-        <v>0.04505493222254756</v>
+        <v>0.04505493222250071</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.01403178333646046</v>
+        <v>-0.01403178333646289</v>
       </c>
       <c r="W16" t="n">
-        <v>5.272740958393851e-05</v>
+        <v>5.27274090296737e-05</v>
       </c>
       <c r="X16" t="n">
-        <v>-11.24364880861739</v>
+        <v>-11.24364880861841</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.04505493137084957</v>
+        <v>0.04505493137067544</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.2818139420127958</v>
+        <v>0.2818139420128695</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.886834933623841e-07</v>
+        <v>2.886835081465285e-07</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.01458744045581832</v>
+        <v>-0.01458744045582099</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.273161502770671e-05</v>
+        <v>5.273161469785554e-05</v>
       </c>
       <c r="AD16" t="n">
-        <v>-12.76431736073221</v>
+        <v>-12.76431736073357</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.04505493222254756</v>
+        <v>0.04505493222250071</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.09905190241355175</v>
+        <v>0.09905190241357491</v>
       </c>
       <c r="AG16" t="n">
-        <v>-1.041020126456332e-07</v>
+        <v>-1.041019900625209e-07</v>
       </c>
       <c r="AH16" t="n">
-        <v>87.79382485854239</v>
+        <v>87.79382485858014</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0001355529529342408</v>
+        <v>0.0001355529252306444</v>
       </c>
       <c r="AJ16" t="n">
-        <v>168.2575179794908</v>
+        <v>168.2575179795031</v>
       </c>
       <c r="AK16" t="n">
-        <v>-2.424063477723948e-09</v>
+        <v>-2.424425771252459e-09</v>
       </c>
       <c r="AL16" t="n">
-        <v>-219.5286446350328</v>
+        <v>-219.528644635031</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.0006973201332486564</v>
+        <v>0.0006973200443666297</v>
       </c>
       <c r="AN16" t="n">
-        <v>-87.79382485854239</v>
+        <v>-87.79382485858014</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.0001355529529342408</v>
+        <v>-0.0001355529252306444</v>
       </c>
       <c r="AP16" t="n">
-        <v>-18.25751797949079</v>
+        <v>-18.25751797950306</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.424063477723948e-09</v>
+        <v>2.424425771252459e-09</v>
       </c>
       <c r="AR16" t="n">
-        <v>-340.0164632419128</v>
+        <v>-340.0164632419874</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.0001159975843567848</v>
+        <v>0.0001159975070172403</v>
       </c>
     </row>
     <row r="17">
@@ -6076,124 +6076,124 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0005556571193576377</v>
+        <v>-0.0005556571193584964</v>
       </c>
       <c r="G17" t="n">
-        <v>-9.260951989293962e-05</v>
+        <v>-9.260951989308273e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>-87.79382485850675</v>
+        <v>-87.79382485864242</v>
       </c>
       <c r="I17" t="n">
-        <v>-18521.90397858792</v>
+        <v>-18521.90397861654</v>
       </c>
       <c r="J17" t="n">
-        <v>11.24364880862486</v>
+        <v>11.2436488086242</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.272740302085454e-05</v>
+        <v>-5.272740357512158e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.01403178333646063</v>
+        <v>-0.01403178333646528</v>
       </c>
       <c r="M17" t="n">
-        <v>2.886833031477993e-07</v>
+        <v>2.88683288419905e-07</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2818139420129872</v>
+        <v>0.2818139420131543</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.04505493136909523</v>
+        <v>-0.04505493136926936</v>
       </c>
       <c r="P17" t="n">
-        <v>12.76431736074036</v>
+        <v>12.76431736074161</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.273160742726827e-05</v>
+        <v>-5.273160775711663e-05</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.01458744045581826</v>
+        <v>-0.01458744045582378</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.041020899760041e-07</v>
+        <v>-1.041021128221863e-07</v>
       </c>
       <c r="T17" t="n">
-        <v>0.09905190241358573</v>
+        <v>0.09905190241377351</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.04505493222058038</v>
+        <v>-0.04505493222062767</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.01403178333646063</v>
+        <v>-0.01403178333646528</v>
       </c>
       <c r="W17" t="n">
-        <v>-5.272740302085454e-05</v>
+        <v>-5.272740357512158e-05</v>
       </c>
       <c r="X17" t="n">
-        <v>-11.24364880862486</v>
+        <v>-11.2436488086242</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.04505493136909523</v>
+        <v>-0.04505493136926936</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.2818139420129872</v>
+        <v>0.2818139420131543</v>
       </c>
       <c r="AA17" t="n">
-        <v>-2.886833031477993e-07</v>
+        <v>-2.88683288419905e-07</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.01458744045581826</v>
+        <v>-0.01458744045582378</v>
       </c>
       <c r="AC17" t="n">
-        <v>-5.273160742726827e-05</v>
+        <v>-5.273160775711663e-05</v>
       </c>
       <c r="AD17" t="n">
-        <v>-12.76431736074036</v>
+        <v>-12.76431736074161</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.04505493222058038</v>
+        <v>-0.04505493222062767</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.09905190241358573</v>
+        <v>0.09905190241377351</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.041020899760041e-07</v>
+        <v>1.041021128221863e-07</v>
       </c>
       <c r="AH17" t="n">
-        <v>87.79382485850692</v>
+        <v>87.79382485864244</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.0001355530108317436</v>
+        <v>-0.0001355530383835308</v>
       </c>
       <c r="AJ17" t="n">
-        <v>168.2575179794911</v>
+        <v>168.2575179797013</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.423457712286137e-09</v>
+        <v>2.42309672326968e-09</v>
       </c>
       <c r="AL17" t="n">
-        <v>-219.528644634917</v>
+        <v>-219.528644635564</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.000697320223406836</v>
+        <v>-0.0006973203120697463</v>
       </c>
       <c r="AN17" t="n">
-        <v>-87.79382485850692</v>
+        <v>-87.79382485864244</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.0001355530108317436</v>
+        <v>0.0001355530383835308</v>
       </c>
       <c r="AP17" t="n">
-        <v>-18.2575179794911</v>
+        <v>-18.25751797970133</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-2.423457712286137e-09</v>
+        <v>-2.42309672326968e-09</v>
       </c>
       <c r="AR17" t="n">
-        <v>-340.0164632420323</v>
+        <v>-340.0164632426458</v>
       </c>
       <c r="AS17" t="n">
-        <v>-0.0001159978415836149</v>
+        <v>-0.0001159979182314488</v>
       </c>
     </row>
     <row r="18">
@@ -6215,124 +6215,124 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0001052931328663778</v>
+        <v>-0.0001052931328663773</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.316164160829722e-05</v>
+        <v>-1.316164160829716e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>-12.47723624466577</v>
+        <v>-12.47723624466571</v>
       </c>
       <c r="I18" t="n">
-        <v>-2632.328321659445</v>
+        <v>-2632.328321659432</v>
       </c>
       <c r="J18" t="n">
-        <v>3.595119805279563</v>
+        <v>3.595119805279023</v>
       </c>
       <c r="K18" t="n">
-        <v>5.264656553662592e-05</v>
+        <v>5.264656576807992e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.007516730126563289</v>
+        <v>0.007516730126564649</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.817587131184721e-06</v>
+        <v>-5.81758716827277e-06</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5733905572099365</v>
+        <v>0.5733905572098467</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01497636114535011</v>
+        <v>0.01497636114528572</v>
       </c>
       <c r="P18" t="n">
-        <v>3.595119805277692</v>
+        <v>3.595119805277716</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.264656732975187e-05</v>
+        <v>-5.264656709829736e-05</v>
       </c>
       <c r="R18" t="n">
-        <v>0.007516730126563006</v>
+        <v>0.007516730126563812</v>
       </c>
       <c r="S18" t="n">
-        <v>5.817587439357226e-06</v>
+        <v>5.817587402268885e-06</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5733905572095976</v>
+        <v>0.5733905572096085</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.01497636114489171</v>
+        <v>-0.0149763611449562</v>
       </c>
       <c r="V18" t="n">
-        <v>5.264656553662592e-05</v>
+        <v>5.264656576807992e-05</v>
       </c>
       <c r="W18" t="n">
-        <v>-3.595119805279563</v>
+        <v>-3.595119805279023</v>
       </c>
       <c r="X18" t="n">
-        <v>0.007516730126563289</v>
+        <v>0.007516730126564649</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.5733905572099365</v>
+        <v>0.5733905572098467</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.817587131184721e-06</v>
+        <v>5.81758716827277e-06</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.01497636114535011</v>
+        <v>0.01497636114528572</v>
       </c>
       <c r="AB18" t="n">
-        <v>-5.264656732975187e-05</v>
+        <v>-5.264656709829736e-05</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.595119805277692</v>
+        <v>-3.595119805277716</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.007516730126563006</v>
+        <v>0.007516730126563812</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.5733905572095976</v>
+        <v>0.5733905572096085</v>
       </c>
       <c r="AF18" t="n">
-        <v>-5.817587439357226e-06</v>
+        <v>-5.817587402268885e-06</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.01497636114489171</v>
+        <v>-0.0149763611449562</v>
       </c>
       <c r="AH18" t="n">
-        <v>12.47723624466577</v>
+        <v>12.47723624466571</v>
       </c>
       <c r="AI18" t="n">
-        <v>-3.865352482534945e-12</v>
+        <v>1.13686837721616e-12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.28306291372754e-10</v>
+        <v>9.748801765852022e-11</v>
       </c>
       <c r="AK18" t="n">
-        <v>7.23199278240827e-13</v>
+        <v>5.082601006733967e-13</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.006457521373425529</v>
+        <v>0.006457521496698426</v>
       </c>
       <c r="AM18" t="n">
-        <v>16.62376087106873</v>
+        <v>16.62376087108873</v>
       </c>
       <c r="AN18" t="n">
-        <v>-12.47723624466577</v>
+        <v>-12.47723624466571</v>
       </c>
       <c r="AO18" t="n">
-        <v>3.865352482534945e-12</v>
+        <v>-1.13686837721616e-12</v>
       </c>
       <c r="AP18" t="n">
-        <v>-1.28306291372754e-10</v>
+        <v>-9.748801765852022e-11</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-7.23199278240827e-13</v>
+        <v>-5.082601006733967e-13</v>
       </c>
       <c r="AR18" t="n">
-        <v>-0.006457522399876302</v>
+        <v>-0.006457522276602568</v>
       </c>
       <c r="AS18" t="n">
-        <v>-16.62376087109965</v>
+        <v>-16.62376087107964</v>
       </c>
     </row>
     <row r="19">
@@ -6366,112 +6366,112 @@
         <v>26420.5486660507</v>
       </c>
       <c r="J19" t="n">
-        <v>3.595119805277692</v>
+        <v>3.595119805277716</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.264656732975187e-05</v>
+        <v>-5.264656709829736e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.007516730126563006</v>
+        <v>0.007516730126563812</v>
       </c>
       <c r="M19" t="n">
-        <v>5.817587439357226e-06</v>
+        <v>5.817587402268885e-06</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5733905572095976</v>
+        <v>0.5733905572096085</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.01497636114489171</v>
+        <v>-0.0149763611449562</v>
       </c>
       <c r="P19" t="n">
-        <v>3.596176627224334</v>
+        <v>3.596176627224358</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.264656733141418e-05</v>
+        <v>5.264656709531542e-05</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.007516730126563017</v>
+        <v>-0.007516730126563806</v>
       </c>
       <c r="S19" t="n">
-        <v>-5.817587439646455e-06</v>
+        <v>-5.817587401731315e-06</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5737082536248554</v>
+        <v>0.5737082536248662</v>
       </c>
       <c r="U19" t="n">
-        <v>0.04500689564371815</v>
+        <v>0.04500689564365364</v>
       </c>
       <c r="V19" t="n">
-        <v>3.595119805277692</v>
+        <v>3.595119805277716</v>
       </c>
       <c r="W19" t="n">
-        <v>-5.264656732975187e-05</v>
+        <v>-5.264656709829736e-05</v>
       </c>
       <c r="X19" t="n">
-        <v>0.007516730126563006</v>
+        <v>0.007516730126563812</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.817587439357226e-06</v>
+        <v>5.817587402268885e-06</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.5733905572095976</v>
+        <v>0.5733905572096085</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.01497636114489171</v>
+        <v>-0.0149763611449562</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.596176627224334</v>
+        <v>3.596176627224358</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.264656733141418e-05</v>
+        <v>5.264656709531542e-05</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.007516730126563017</v>
+        <v>-0.007516730126563806</v>
       </c>
       <c r="AE19" t="n">
-        <v>-5.817587439646455e-06</v>
+        <v>-5.817587401731315e-06</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.5737082536248554</v>
+        <v>0.5737082536248662</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.04500689564371815</v>
+        <v>0.04500689564365364</v>
       </c>
       <c r="AH19" t="n">
-        <v>-125.233400677098</v>
+        <v>-125.2334006770398</v>
       </c>
       <c r="AI19" t="n">
-        <v>12.48925291831083</v>
+        <v>12.48925291830579</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-475.9154605522502</v>
+        <v>-475.9154605522591</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.48366232994117e-05</v>
+        <v>2.483662313930812e-05</v>
       </c>
       <c r="AL19" t="n">
-        <v>1903.485520698533</v>
+        <v>1903.485520698568</v>
       </c>
       <c r="AM19" t="n">
-        <v>16.66630415556484</v>
+        <v>16.66630415554469</v>
       </c>
       <c r="AN19" t="n">
-        <v>125.233400677098</v>
+        <v>125.2334006770398</v>
       </c>
       <c r="AO19" t="n">
-        <v>-12.48925291831083</v>
+        <v>-12.48925291830579</v>
       </c>
       <c r="AP19" t="n">
-        <v>475.9154605522502</v>
+        <v>475.9154605522591</v>
       </c>
       <c r="AQ19" t="n">
-        <v>-2.48366232994117e-05</v>
+        <v>-2.483662313930812e-05</v>
       </c>
       <c r="AR19" t="n">
-        <v>1903.838163719469</v>
+        <v>1903.838163719504</v>
       </c>
       <c r="AS19" t="n">
-        <v>83.24771919092179</v>
+        <v>83.24771919090161</v>
       </c>
     </row>
     <row r="20">
@@ -6493,124 +6493,124 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001052931328663774</v>
+        <v>0.0001052931328663773</v>
       </c>
       <c r="G20" t="n">
-        <v>1.316164160829718e-05</v>
+        <v>1.316164160829716e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>12.47723624466572</v>
+        <v>12.4772362446657</v>
       </c>
       <c r="I20" t="n">
-        <v>2632.328321659435</v>
+        <v>2632.328321659431</v>
       </c>
       <c r="J20" t="n">
-        <v>3.596176627224334</v>
+        <v>3.596176627224358</v>
       </c>
       <c r="K20" t="n">
-        <v>5.264656733141418e-05</v>
+        <v>5.264656709531542e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.007516730126563017</v>
+        <v>-0.007516730126563806</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.817587439646455e-06</v>
+        <v>-5.817587401731315e-06</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5737082536248554</v>
+        <v>0.5737082536248662</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04500689564371815</v>
+        <v>0.04500689564365364</v>
       </c>
       <c r="P20" t="n">
-        <v>3.596176627226205</v>
+        <v>3.596176627225665</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.264656553496323e-05</v>
+        <v>-5.264656577106183e-05</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.00751673012656329</v>
+        <v>-0.007516730126564661</v>
       </c>
       <c r="S20" t="n">
-        <v>5.817587130890855e-06</v>
+        <v>5.817587168809183e-06</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5737082536251945</v>
+        <v>0.5737082536251048</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.04500689564325982</v>
+        <v>-0.0450068956433242</v>
       </c>
       <c r="V20" t="n">
-        <v>-5.264656733141418e-05</v>
+        <v>-5.264656709531542e-05</v>
       </c>
       <c r="W20" t="n">
-        <v>3.596176627224334</v>
+        <v>3.596176627224358</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.007516730126563017</v>
+        <v>-0.007516730126563806</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.5737082536248554</v>
+        <v>-0.5737082536248662</v>
       </c>
       <c r="Z20" t="n">
-        <v>-5.817587439646455e-06</v>
+        <v>-5.817587401731315e-06</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.04500689564371815</v>
+        <v>0.04500689564365364</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.264656553496323e-05</v>
+        <v>5.264656577106183e-05</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.596176627226205</v>
+        <v>3.596176627225665</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.00751673012656329</v>
+        <v>-0.007516730126564661</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.5737082536251945</v>
+        <v>-0.5737082536251048</v>
       </c>
       <c r="AF20" t="n">
-        <v>5.817587130890855e-06</v>
+        <v>5.817587168809183e-06</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.04500689564325982</v>
+        <v>-0.0450068956433242</v>
       </c>
       <c r="AH20" t="n">
-        <v>-12.47723624466572</v>
+        <v>-12.4772362446657</v>
       </c>
       <c r="AI20" t="n">
-        <v>-100.000000000004</v>
+        <v>-99.99999999999892</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.285480819013252e-10</v>
+        <v>9.704281822564553e-11</v>
       </c>
       <c r="AK20" t="n">
-        <v>7.238654120556021e-13</v>
+        <v>5.091482790930968e-13</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.006457522400840577</v>
+        <v>-0.006457522274820882</v>
       </c>
       <c r="AM20" t="n">
-        <v>-83.37567916907628</v>
+        <v>-83.3756791690565</v>
       </c>
       <c r="AN20" t="n">
-        <v>12.47723624466572</v>
+        <v>12.4772362446657</v>
       </c>
       <c r="AO20" t="n">
-        <v>-99.99999999999602</v>
+        <v>-100.0000000000011</v>
       </c>
       <c r="AP20" t="n">
-        <v>-1.285480819013252e-10</v>
+        <v>-9.704281822564553e-11</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-7.238654120556021e-13</v>
+        <v>-5.091482790930968e-13</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.006457521372455919</v>
+        <v>0.00645752149847878</v>
       </c>
       <c r="AS20" t="n">
-        <v>83.37567916904467</v>
+        <v>83.37567916906491</v>
       </c>
     </row>
     <row r="21">
@@ -6644,112 +6644,112 @@
         <v>26420.5486660618</v>
       </c>
       <c r="J21" t="n">
-        <v>3.596176627226205</v>
+        <v>3.596176627225665</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.264656553496323e-05</v>
+        <v>-5.264656577106183e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.00751673012656329</v>
+        <v>-0.007516730126564661</v>
       </c>
       <c r="M21" t="n">
-        <v>5.817587130890855e-06</v>
+        <v>5.817587168809183e-06</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5737082536251945</v>
+        <v>0.5737082536251048</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.04500689564325982</v>
+        <v>-0.0450068956433242</v>
       </c>
       <c r="P21" t="n">
-        <v>3.595119805279563</v>
+        <v>3.595119805279023</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.264656553662592e-05</v>
+        <v>5.264656576807992e-05</v>
       </c>
       <c r="R21" t="n">
-        <v>0.007516730126563289</v>
+        <v>0.007516730126564649</v>
       </c>
       <c r="S21" t="n">
-        <v>-5.817587131184721e-06</v>
+        <v>-5.81758716827277e-06</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5733905572099365</v>
+        <v>0.5733905572098467</v>
       </c>
       <c r="U21" t="n">
-        <v>0.01497636114535011</v>
+        <v>0.01497636114528572</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.596176627226205</v>
+        <v>-3.596176627225665</v>
       </c>
       <c r="W21" t="n">
-        <v>-5.264656553496323e-05</v>
+        <v>-5.264656577106183e-05</v>
       </c>
       <c r="X21" t="n">
-        <v>0.00751673012656329</v>
+        <v>0.007516730126564661</v>
       </c>
       <c r="Y21" t="n">
-        <v>-5.817587130890855e-06</v>
+        <v>-5.817587168809183e-06</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.5737082536251945</v>
+        <v>0.5737082536251048</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.04500689564325982</v>
+        <v>0.0450068956433242</v>
       </c>
       <c r="AB21" t="n">
-        <v>-3.595119805279563</v>
+        <v>-3.595119805279023</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.264656553662592e-05</v>
+        <v>5.264656576807992e-05</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.007516730126563289</v>
+        <v>-0.007516730126564649</v>
       </c>
       <c r="AE21" t="n">
-        <v>5.817587131184721e-06</v>
+        <v>5.81758716827277e-06</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.5733905572099365</v>
+        <v>0.5733905572098467</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.01497636114535011</v>
+        <v>-0.01497636114528572</v>
       </c>
       <c r="AH21" t="n">
-        <v>-125.233400677098</v>
+        <v>-125.2334006771562</v>
       </c>
       <c r="AI21" t="n">
-        <v>12.48925291830278</v>
+        <v>12.48925291830772</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-475.9154605525324</v>
+        <v>-475.9154605524574</v>
       </c>
       <c r="AK21" t="n">
-        <v>-2.483662198250748e-05</v>
+        <v>-2.483662214261725e-05</v>
       </c>
       <c r="AL21" t="n">
-        <v>1903.838163720598</v>
+        <v>1903.838163720297</v>
       </c>
       <c r="AM21" t="n">
-        <v>83.24771919088963</v>
+        <v>83.24771919090941</v>
       </c>
       <c r="AN21" t="n">
-        <v>125.233400677098</v>
+        <v>125.2334006771562</v>
       </c>
       <c r="AO21" t="n">
-        <v>-12.48925291830278</v>
+        <v>-12.48925291830772</v>
       </c>
       <c r="AP21" t="n">
-        <v>475.9154605525324</v>
+        <v>475.9154605524574</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.483662198250748e-05</v>
+        <v>2.483662214261725e-05</v>
       </c>
       <c r="AR21" t="n">
-        <v>1903.485520699661</v>
+        <v>1903.485520699361</v>
       </c>
       <c r="AS21" t="n">
-        <v>16.6663041555326</v>
+        <v>16.66630415555239</v>
       </c>
     </row>
     <row r="22">
@@ -6771,124 +6771,124 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0001054962997791679</v>
+        <v>-0.0001054962997791663</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.318703747239599e-05</v>
+        <v>-1.318703747239578e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>-12.5013115238314</v>
+        <v>-12.5013115238312</v>
       </c>
       <c r="I22" t="n">
-        <v>-2637.407494479197</v>
+        <v>-2637.407494479156</v>
       </c>
       <c r="J22" t="n">
-        <v>8.113133295381624</v>
+        <v>8.113133295380457</v>
       </c>
       <c r="K22" t="n">
-        <v>5.27481476618041e-05</v>
+        <v>5.274814816710414e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01202133708507339</v>
+        <v>0.01202133708507639</v>
       </c>
       <c r="M22" t="n">
-        <v>1.276246312356512e-06</v>
+        <v>1.276246291459122e-06</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4768655535134581</v>
+        <v>0.4768655535134355</v>
       </c>
       <c r="O22" t="n">
-        <v>0.01500508180328185</v>
+        <v>0.01500508180312803</v>
       </c>
       <c r="P22" t="n">
-        <v>8.113133295376661</v>
+        <v>8.11313329537693</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.274815211736379e-05</v>
+        <v>-5.274815161206213e-05</v>
       </c>
       <c r="R22" t="n">
-        <v>0.01202133708507298</v>
+        <v>0.01202133708507474</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.276246011702428e-06</v>
+        <v>-1.276246032599108e-06</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4768655535130946</v>
+        <v>0.4768655535131607</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.01500508180210351</v>
+        <v>-0.01500508180225687</v>
       </c>
       <c r="V22" t="n">
-        <v>5.27481476618041e-05</v>
+        <v>5.274814816710414e-05</v>
       </c>
       <c r="W22" t="n">
-        <v>-8.113133295381624</v>
+        <v>-8.113133295380457</v>
       </c>
       <c r="X22" t="n">
-        <v>0.01202133708507339</v>
+        <v>0.01202133708507639</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.4768655535134581</v>
+        <v>0.4768655535134355</v>
       </c>
       <c r="Z22" t="n">
-        <v>-1.276246312356512e-06</v>
+        <v>-1.276246291459122e-06</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.01500508180328185</v>
+        <v>0.01500508180312803</v>
       </c>
       <c r="AB22" t="n">
-        <v>-5.274815211736379e-05</v>
+        <v>-5.274815161206213e-05</v>
       </c>
       <c r="AC22" t="n">
-        <v>-8.113133295376661</v>
+        <v>-8.11313329537693</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.01202133708507298</v>
+        <v>0.01202133708507474</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.4768655535130946</v>
+        <v>0.4768655535131607</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.276246011702428e-06</v>
+        <v>1.276246032599108e-06</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.01500508180210351</v>
+        <v>-0.01500508180225687</v>
       </c>
       <c r="AH22" t="n">
-        <v>12.5013115238314</v>
+        <v>12.5013115238312</v>
       </c>
       <c r="AI22" t="n">
-        <v>-2.592059900052845e-11</v>
+        <v>-4.433786671143025e-12</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.251894328219844e-10</v>
+        <v>1.079225597777622e-10</v>
       </c>
       <c r="AK22" t="n">
-        <v>7.758238496080594e-13</v>
+        <v>5.864198016070077e-13</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.001416633740610715</v>
+        <v>-0.001416633671542655</v>
       </c>
       <c r="AM22" t="n">
-        <v>16.65564080088552</v>
+        <v>16.65564080097101</v>
       </c>
       <c r="AN22" t="n">
-        <v>-12.5013115238314</v>
+        <v>-12.5013115238312</v>
       </c>
       <c r="AO22" t="n">
-        <v>2.592059900052845e-11</v>
+        <v>4.433786671143025e-12</v>
       </c>
       <c r="AP22" t="n">
-        <v>-1.251894328219844e-10</v>
+        <v>-1.079225597777622e-10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>-7.758238496080594e-13</v>
+        <v>-5.864198016070077e-13</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.001416632739095252</v>
+        <v>0.001416632808162177</v>
       </c>
       <c r="AS22" t="n">
-        <v>-16.65564080109243</v>
+        <v>-16.65564080100648</v>
       </c>
     </row>
     <row r="23">
@@ -6910,124 +6910,124 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.001042184204001373</v>
+        <v>0.001042184203999597</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001302730255001716</v>
+        <v>0.0001302730254999496</v>
       </c>
       <c r="H23" t="n">
-        <v>123.4988281741627</v>
+        <v>123.4988281739522</v>
       </c>
       <c r="I23" t="n">
-        <v>26054.60510003432</v>
+        <v>26054.60509998991</v>
       </c>
       <c r="J23" t="n">
-        <v>8.113133295376661</v>
+        <v>8.11313329537693</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.274815211736379e-05</v>
+        <v>-5.274815161206213e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.01202133708507298</v>
+        <v>0.01202133708507474</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.276246011702428e-06</v>
+        <v>-1.276246032599108e-06</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4768655535130946</v>
+        <v>0.4768655535131607</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.01500508180210351</v>
+        <v>-0.01500508180225687</v>
       </c>
       <c r="P23" t="n">
-        <v>8.114175479580663</v>
+        <v>8.114175479580929</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.274815212167277e-05</v>
+        <v>5.274815160420837e-05</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.012021337085073</v>
+        <v>-0.01202133708507473</v>
       </c>
       <c r="S23" t="n">
-        <v>1.27624601135778e-06</v>
+        <v>1.276246033172293e-06</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4758775876426199</v>
+        <v>0.4758775876426864</v>
       </c>
       <c r="U23" t="n">
-        <v>0.04505488004389391</v>
+        <v>0.04505488004373993</v>
       </c>
       <c r="V23" t="n">
-        <v>8.113133295376661</v>
+        <v>8.11313329537693</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.274815211736379e-05</v>
+        <v>-5.274815161206213e-05</v>
       </c>
       <c r="X23" t="n">
-        <v>0.01202133708507298</v>
+        <v>0.01202133708507474</v>
       </c>
       <c r="Y23" t="n">
-        <v>-1.276246011702428e-06</v>
+        <v>-1.276246032599108e-06</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.4768655535130946</v>
+        <v>0.4768655535131607</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.01500508180210351</v>
+        <v>-0.01500508180225687</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.114175479580663</v>
+        <v>8.114175479580929</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.274815212167277e-05</v>
+        <v>5.274815160420837e-05</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.012021337085073</v>
+        <v>-0.01202133708507473</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.27624601135778e-06</v>
+        <v>1.276246033172293e-06</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.4758775876426199</v>
+        <v>0.4758775876426864</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.04505488004389391</v>
+        <v>0.04505488004373993</v>
       </c>
       <c r="AH23" t="n">
-        <v>-123.4988281741971</v>
+        <v>-123.4988281739643</v>
       </c>
       <c r="AI23" t="n">
-        <v>12.49725030898538</v>
+        <v>12.49725030896388</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-394.0773917252354</v>
+        <v>-394.0773917252902</v>
       </c>
       <c r="AK23" t="n">
-        <v>-5.448588741532367e-06</v>
+        <v>-5.448588832704337e-06</v>
       </c>
       <c r="AL23" t="n">
-        <v>1576.857887959055</v>
+        <v>1576.857887959274</v>
       </c>
       <c r="AM23" t="n">
-        <v>16.65572241141295</v>
+        <v>16.65572241132731</v>
       </c>
       <c r="AN23" t="n">
-        <v>123.4988281741971</v>
+        <v>123.4988281739643</v>
       </c>
       <c r="AO23" t="n">
-        <v>-12.49725030898538</v>
+        <v>-12.49725030896388</v>
       </c>
       <c r="AP23" t="n">
-        <v>394.0773917252354</v>
+        <v>394.0773917252902</v>
       </c>
       <c r="AQ23" t="n">
-        <v>5.448588741532367e-06</v>
+        <v>5.448588832704337e-06</v>
       </c>
       <c r="AR23" t="n">
-        <v>1575.761245842828</v>
+        <v>1575.761245843047</v>
       </c>
       <c r="AS23" t="n">
-        <v>83.32228006047011</v>
+        <v>83.32228006038376</v>
       </c>
     </row>
     <row r="24">
@@ -7049,7 +7049,7 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0001054962997791679</v>
+        <v>0.0001054962997791678</v>
       </c>
       <c r="G24" t="n">
         <v>1.318703747239598e-05</v>
@@ -7058,115 +7058,115 @@
         <v>12.50131152383139</v>
       </c>
       <c r="I24" t="n">
-        <v>2637.407494479197</v>
+        <v>2637.407494479196</v>
       </c>
       <c r="J24" t="n">
-        <v>8.114175479580663</v>
+        <v>8.114175479580929</v>
       </c>
       <c r="K24" t="n">
-        <v>5.274815212167277e-05</v>
+        <v>5.274815160420837e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.012021337085073</v>
+        <v>-0.01202133708507473</v>
       </c>
       <c r="M24" t="n">
-        <v>1.27624601135778e-06</v>
+        <v>1.276246033172293e-06</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4758775876426199</v>
+        <v>0.4758775876426864</v>
       </c>
       <c r="O24" t="n">
-        <v>0.04505488004389391</v>
+        <v>0.04505488004373993</v>
       </c>
       <c r="P24" t="n">
-        <v>8.114175479585626</v>
+        <v>8.114175479584461</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.27481476574951e-05</v>
+        <v>-5.274814817495947e-05</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.01202133708507339</v>
+        <v>-0.0120213370850764</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.276246312679776e-06</v>
+        <v>-1.276246290880136e-06</v>
       </c>
       <c r="T24" t="n">
-        <v>0.475877587642983</v>
+        <v>0.4758775876429612</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.04505488004271615</v>
+        <v>-0.04505488004286866</v>
       </c>
       <c r="V24" t="n">
-        <v>-5.274815212167277e-05</v>
+        <v>-5.274815160420837e-05</v>
       </c>
       <c r="W24" t="n">
-        <v>8.114175479580663</v>
+        <v>8.114175479580929</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.012021337085073</v>
+        <v>-0.01202133708507473</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.4758775876426199</v>
+        <v>-0.4758775876426864</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.27624601135778e-06</v>
+        <v>1.276246033172293e-06</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.04505488004389391</v>
+        <v>0.04505488004373993</v>
       </c>
       <c r="AB24" t="n">
-        <v>5.27481476574951e-05</v>
+        <v>5.274814817495947e-05</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.114175479585626</v>
+        <v>8.114175479584461</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.01202133708507339</v>
+        <v>-0.0120213370850764</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.475877587642983</v>
+        <v>-0.4758775876429612</v>
       </c>
       <c r="AF24" t="n">
-        <v>-1.276246312679776e-06</v>
+        <v>-1.276246290880136e-06</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.04505488004271615</v>
+        <v>-0.04505488004286866</v>
       </c>
       <c r="AH24" t="n">
         <v>-12.50131152383139</v>
       </c>
       <c r="AI24" t="n">
-        <v>-100.0000000000263</v>
+        <v>-100.0000000000048</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.254654333985444e-10</v>
+        <v>1.074449418325685e-10</v>
       </c>
       <c r="AK24" t="n">
-        <v>7.751577157932843e-13</v>
+        <v>5.864198016070077e-13</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.001416632737978864</v>
+        <v>0.001416632810069984</v>
       </c>
       <c r="AM24" t="n">
-        <v>-83.32241648536987</v>
+        <v>-83.32241648528483</v>
       </c>
       <c r="AN24" t="n">
         <v>12.50131152383139</v>
       </c>
       <c r="AO24" t="n">
-        <v>-99.99999999997374</v>
+        <v>-99.99999999999523</v>
       </c>
       <c r="AP24" t="n">
-        <v>-1.254654333985444e-10</v>
+        <v>-1.074449418325685e-10</v>
       </c>
       <c r="AQ24" t="n">
-        <v>-7.751577157932843e-13</v>
+        <v>-5.864198016070077e-13</v>
       </c>
       <c r="AR24" t="n">
-        <v>-0.00141663374170233</v>
+        <v>-0.001416633669628631</v>
       </c>
       <c r="AS24" t="n">
-        <v>83.32241648516023</v>
+        <v>83.32241648524663</v>
       </c>
     </row>
     <row r="25">
@@ -7188,124 +7188,124 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.001042184204001373</v>
+        <v>0.001042184204003149</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001302730255001716</v>
+        <v>0.0001302730255003937</v>
       </c>
       <c r="H25" t="n">
-        <v>123.4988281741627</v>
+        <v>123.4988281743732</v>
       </c>
       <c r="I25" t="n">
-        <v>26054.60510003432</v>
+        <v>26054.60510007873</v>
       </c>
       <c r="J25" t="n">
-        <v>8.114175479585626</v>
+        <v>8.114175479584461</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.27481476574951e-05</v>
+        <v>-5.274814817495947e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.01202133708507339</v>
+        <v>-0.0120213370850764</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.276246312679776e-06</v>
+        <v>-1.276246290880136e-06</v>
       </c>
       <c r="N25" t="n">
-        <v>0.475877587642983</v>
+        <v>0.4758775876429612</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.04505488004271615</v>
+        <v>-0.04505488004286866</v>
       </c>
       <c r="P25" t="n">
-        <v>8.113133295381624</v>
+        <v>8.113133295380457</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.27481476618041e-05</v>
+        <v>5.274814816710414e-05</v>
       </c>
       <c r="R25" t="n">
-        <v>0.01202133708507339</v>
+        <v>0.01202133708507639</v>
       </c>
       <c r="S25" t="n">
-        <v>1.276246312356512e-06</v>
+        <v>1.276246291459122e-06</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4768655535134581</v>
+        <v>0.4768655535134355</v>
       </c>
       <c r="U25" t="n">
-        <v>0.01500508180328185</v>
+        <v>0.01500508180312803</v>
       </c>
       <c r="V25" t="n">
-        <v>-8.114175479585626</v>
+        <v>-8.114175479584461</v>
       </c>
       <c r="W25" t="n">
-        <v>-5.27481476574951e-05</v>
+        <v>-5.274814817495947e-05</v>
       </c>
       <c r="X25" t="n">
-        <v>0.01202133708507339</v>
+        <v>0.0120213370850764</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.276246312679776e-06</v>
+        <v>1.276246290880136e-06</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.475877587642983</v>
+        <v>0.4758775876429612</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.04505488004271615</v>
+        <v>0.04505488004286866</v>
       </c>
       <c r="AB25" t="n">
-        <v>-8.113133295381624</v>
+        <v>-8.113133295380457</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.27481476618041e-05</v>
+        <v>5.274814816710414e-05</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.01202133708507339</v>
+        <v>-0.01202133708507639</v>
       </c>
       <c r="AE25" t="n">
-        <v>-1.276246312356512e-06</v>
+        <v>-1.276246291459122e-06</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.4768655535134581</v>
+        <v>0.4768655535134355</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.01500508180328185</v>
+        <v>-0.01500508180312803</v>
       </c>
       <c r="AH25" t="n">
-        <v>-123.4988281741971</v>
+        <v>-123.4988281744299</v>
       </c>
       <c r="AI25" t="n">
-        <v>12.49725030893287</v>
+        <v>12.49725030895394</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-394.0773917255378</v>
+        <v>-394.0773917255186</v>
       </c>
       <c r="AK25" t="n">
-        <v>5.448590026519767e-06</v>
+        <v>5.448589935378031e-06</v>
       </c>
       <c r="AL25" t="n">
-        <v>1575.761245844037</v>
+        <v>1575.761245843961</v>
       </c>
       <c r="AM25" t="n">
-        <v>83.32228006026035</v>
+        <v>83.32228006034393</v>
       </c>
       <c r="AN25" t="n">
-        <v>123.4988281741971</v>
+        <v>123.4988281744299</v>
       </c>
       <c r="AO25" t="n">
-        <v>-12.49725030893287</v>
+        <v>-12.49725030895394</v>
       </c>
       <c r="AP25" t="n">
-        <v>394.0773917255378</v>
+        <v>394.0773917255186</v>
       </c>
       <c r="AQ25" t="n">
-        <v>-5.448590026519767e-06</v>
+        <v>-5.448589935378031e-06</v>
       </c>
       <c r="AR25" t="n">
-        <v>1576.857887960265</v>
+        <v>1576.857887960188</v>
       </c>
       <c r="AS25" t="n">
-        <v>16.65572241120256</v>
+        <v>16.6557224112876</v>
       </c>
     </row>
     <row r="26">
@@ -7327,124 +7327,124 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0001054548126048016</v>
+        <v>-0.0001054548126048011</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.318185157560019e-05</v>
+        <v>-1.318185157560014e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>-12.49639529366899</v>
+        <v>-12.49639529366893</v>
       </c>
       <c r="I26" t="n">
-        <v>-2636.370315120039</v>
+        <v>-2636.370315120028</v>
       </c>
       <c r="J26" t="n">
-        <v>11.24253477912758</v>
+        <v>11.24253477912691</v>
       </c>
       <c r="K26" t="n">
-        <v>5.272740302799424e-05</v>
+        <v>5.272740356380378e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01403178333646062</v>
+        <v>0.01403178333646527</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.886833036039658e-07</v>
+        <v>-2.886832883124274e-07</v>
       </c>
       <c r="N26" t="n">
-        <v>0.2774101967681684</v>
+        <v>0.2774101967683359</v>
       </c>
       <c r="O26" t="n">
-        <v>0.01500512856537014</v>
+        <v>0.01500512856519697</v>
       </c>
       <c r="P26" t="n">
-        <v>11.2425347791201</v>
+        <v>11.24253477912112</v>
       </c>
       <c r="Q26" t="n">
-        <v>-5.272740957680732e-05</v>
+        <v>-5.272740904099736e-05</v>
       </c>
       <c r="R26" t="n">
-        <v>0.01403178333646043</v>
+        <v>0.01403178333646289</v>
       </c>
       <c r="S26" t="n">
-        <v>2.886834930193329e-07</v>
+        <v>2.886835082336281e-07</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2774101967679769</v>
+        <v>0.2774101967680513</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.01500512856361739</v>
+        <v>-0.01500512856379087</v>
       </c>
       <c r="V26" t="n">
-        <v>5.272740302799424e-05</v>
+        <v>5.272740356380378e-05</v>
       </c>
       <c r="W26" t="n">
-        <v>-11.24253477912758</v>
+        <v>-11.24253477912691</v>
       </c>
       <c r="X26" t="n">
-        <v>0.01403178333646062</v>
+        <v>0.01403178333646527</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.2774101967681684</v>
+        <v>0.2774101967683359</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.886833036039658e-07</v>
+        <v>2.886832883124274e-07</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01500512856537014</v>
+        <v>0.01500512856519697</v>
       </c>
       <c r="AB26" t="n">
-        <v>-5.272740957680732e-05</v>
+        <v>-5.272740904099736e-05</v>
       </c>
       <c r="AC26" t="n">
-        <v>-11.2425347791201</v>
+        <v>-11.24253477912112</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.01403178333646043</v>
+        <v>0.01403178333646289</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.2774101967679769</v>
+        <v>0.2774101967680513</v>
       </c>
       <c r="AF26" t="n">
-        <v>-2.886834930193329e-07</v>
+        <v>-2.886835082336281e-07</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.01500512856361739</v>
+        <v>-0.01500512856379087</v>
       </c>
       <c r="AH26" t="n">
-        <v>12.49639529366899</v>
+        <v>12.49639529366894</v>
       </c>
       <c r="AI26" t="n">
-        <v>-4.843059286940843e-11</v>
+        <v>-1.70530256582424e-11</v>
       </c>
       <c r="AJ26" t="n">
-        <v>7.886364625849396e-11</v>
+        <v>9.179013105153899e-11</v>
       </c>
       <c r="AK26" t="n">
-        <v>4.087841176669826e-13</v>
+        <v>6.076250613773482e-13</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.0003204382566711034</v>
+        <v>0.0003204382049224463</v>
       </c>
       <c r="AM26" t="n">
-        <v>16.65569270639389</v>
+        <v>16.65569270651849</v>
       </c>
       <c r="AN26" t="n">
-        <v>-12.49639529366899</v>
+        <v>-12.49639529366894</v>
       </c>
       <c r="AO26" t="n">
-        <v>4.843059286940843e-11</v>
+        <v>1.70530256582424e-11</v>
       </c>
       <c r="AP26" t="n">
-        <v>-7.886364625849396e-11</v>
+        <v>-9.179013105153899e-11</v>
       </c>
       <c r="AQ26" t="n">
-        <v>-4.087841176669826e-13</v>
+        <v>-6.076250613773482e-13</v>
       </c>
       <c r="AR26" t="n">
-        <v>-0.0003204388875802733</v>
+        <v>-0.0003204389392434948</v>
       </c>
       <c r="AS26" t="n">
-        <v>-16.65569270678225</v>
+        <v>-16.65569270665674</v>
       </c>
     </row>
     <row r="27">
@@ -7478,112 +7478,112 @@
         <v>27850.73743223343</v>
       </c>
       <c r="J27" t="n">
-        <v>11.2425347791201</v>
+        <v>11.24253477912112</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.272740957680732e-05</v>
+        <v>-5.272740904099736e-05</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01403178333646043</v>
+        <v>0.01403178333646289</v>
       </c>
       <c r="M27" t="n">
-        <v>2.886834930193329e-07</v>
+        <v>2.886835082336281e-07</v>
       </c>
       <c r="N27" t="n">
-        <v>0.2774101967679769</v>
+        <v>0.2774101967680513</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.01500512856361739</v>
+        <v>-0.01500512856379087</v>
       </c>
       <c r="P27" t="n">
-        <v>11.24364880861739</v>
+        <v>11.24364880861841</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.272740958393851e-05</v>
+        <v>5.27274090296737e-05</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.01403178333646046</v>
+        <v>-0.01403178333646289</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.886834933623841e-07</v>
+        <v>-2.886835081465285e-07</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2818139420127958</v>
+        <v>0.2818139420128695</v>
       </c>
       <c r="U27" t="n">
-        <v>0.04505493137084957</v>
+        <v>0.04505493137067544</v>
       </c>
       <c r="V27" t="n">
-        <v>11.2425347791201</v>
+        <v>11.24253477912112</v>
       </c>
       <c r="W27" t="n">
-        <v>-5.272740957680732e-05</v>
+        <v>-5.272740904099736e-05</v>
       </c>
       <c r="X27" t="n">
-        <v>0.01403178333646043</v>
+        <v>0.01403178333646289</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.886834930193329e-07</v>
+        <v>2.886835082336281e-07</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.2774101967679769</v>
+        <v>0.2774101967680513</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.01500512856361739</v>
+        <v>-0.01500512856379087</v>
       </c>
       <c r="AB27" t="n">
-        <v>11.24364880861739</v>
+        <v>11.24364880861841</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.272740958393851e-05</v>
+        <v>5.27274090296737e-05</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.01403178333646046</v>
+        <v>-0.01403178333646289</v>
       </c>
       <c r="AE27" t="n">
-        <v>-2.886834933623841e-07</v>
+        <v>-2.886835081465285e-07</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.2818139420127958</v>
+        <v>0.2818139420128695</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.04505493137084957</v>
+        <v>0.04505493137067544</v>
       </c>
       <c r="AH27" t="n">
         <v>-132.0124954287894</v>
       </c>
       <c r="AI27" t="n">
-        <v>12.49725652639148</v>
+        <v>12.49725652636022</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-229.8566828605958</v>
+        <v>-229.856682860657</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.232456451699434e-06</v>
+        <v>1.232456515734565e-06</v>
       </c>
       <c r="AL27" t="n">
-        <v>916.9826528315087</v>
+        <v>916.9826528317536</v>
       </c>
       <c r="AM27" t="n">
-        <v>16.65569284193676</v>
+        <v>16.65569284181208</v>
       </c>
       <c r="AN27" t="n">
         <v>132.0124954287894</v>
       </c>
       <c r="AO27" t="n">
-        <v>-12.49725652639148</v>
+        <v>-12.49725652636022</v>
       </c>
       <c r="AP27" t="n">
-        <v>229.8566828605958</v>
+        <v>229.856682860657</v>
       </c>
       <c r="AQ27" t="n">
-        <v>-1.232456451699434e-06</v>
+        <v>-1.232456515734565e-06</v>
       </c>
       <c r="AR27" t="n">
-        <v>921.8708100532576</v>
+        <v>921.8708100535018</v>
       </c>
       <c r="AS27" t="n">
-        <v>83.32235936919508</v>
+        <v>83.32235936906969</v>
       </c>
     </row>
     <row r="28">
@@ -7605,124 +7605,124 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>0.000105454812604793</v>
+        <v>0.0001054548126047953</v>
       </c>
       <c r="G28" t="n">
-        <v>1.318185157559913e-05</v>
+        <v>1.318185157559941e-05</v>
       </c>
       <c r="H28" t="n">
-        <v>12.49639529366798</v>
+        <v>12.49639529366824</v>
       </c>
       <c r="I28" t="n">
-        <v>2636.370315119826</v>
+        <v>2636.370315119882</v>
       </c>
       <c r="J28" t="n">
-        <v>11.24364880861739</v>
+        <v>11.24364880861841</v>
       </c>
       <c r="K28" t="n">
-        <v>5.272740958393851e-05</v>
+        <v>5.27274090296737e-05</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.01403178333646046</v>
+        <v>-0.01403178333646289</v>
       </c>
       <c r="M28" t="n">
-        <v>-2.886834933623841e-07</v>
+        <v>-2.886835081465285e-07</v>
       </c>
       <c r="N28" t="n">
-        <v>0.2818139420127958</v>
+        <v>0.2818139420128695</v>
       </c>
       <c r="O28" t="n">
-        <v>0.04505493137084957</v>
+        <v>0.04505493137067544</v>
       </c>
       <c r="P28" t="n">
-        <v>11.24364880862486</v>
+        <v>11.2436488086242</v>
       </c>
       <c r="Q28" t="n">
-        <v>-5.272740302085454e-05</v>
+        <v>-5.272740357512158e-05</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.01403178333646063</v>
+        <v>-0.01403178333646528</v>
       </c>
       <c r="S28" t="n">
-        <v>2.886833031477993e-07</v>
+        <v>2.88683288419905e-07</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2818139420129872</v>
+        <v>0.2818139420131543</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.04505493136909523</v>
+        <v>-0.04505493136926936</v>
       </c>
       <c r="V28" t="n">
-        <v>-5.272740958393851e-05</v>
+        <v>-5.27274090296737e-05</v>
       </c>
       <c r="W28" t="n">
-        <v>11.24364880861739</v>
+        <v>11.24364880861841</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.01403178333646046</v>
+        <v>-0.01403178333646289</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.2818139420127958</v>
+        <v>-0.2818139420128695</v>
       </c>
       <c r="Z28" t="n">
-        <v>-2.886834933623841e-07</v>
+        <v>-2.886835081465285e-07</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.04505493137084957</v>
+        <v>0.04505493137067544</v>
       </c>
       <c r="AB28" t="n">
-        <v>5.272740302085454e-05</v>
+        <v>5.272740357512158e-05</v>
       </c>
       <c r="AC28" t="n">
-        <v>11.24364880862486</v>
+        <v>11.2436488086242</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.01403178333646063</v>
+        <v>-0.01403178333646528</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.2818139420129872</v>
+        <v>-0.2818139420131543</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.886833031477993e-07</v>
+        <v>2.88683288419905e-07</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.04505493136909523</v>
+        <v>-0.04505493136926936</v>
       </c>
       <c r="AH28" t="n">
-        <v>-12.49639529366798</v>
+        <v>-12.49639529366824</v>
       </c>
       <c r="AI28" t="n">
-        <v>-100.0000000000475</v>
+        <v>-100.0000000000168</v>
       </c>
       <c r="AJ28" t="n">
-        <v>7.919405605740729e-11</v>
+        <v>9.171041703837091e-11</v>
       </c>
       <c r="AK28" t="n">
-        <v>4.084510507595951e-13</v>
+        <v>6.078471059822732e-13</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.0003204388888398558</v>
+        <v>-0.000320438938936185</v>
       </c>
       <c r="AM28" t="n">
-        <v>-83.32235951285415</v>
+        <v>-83.32235951273137</v>
       </c>
       <c r="AN28" t="n">
-        <v>12.49639529366798</v>
+        <v>12.49639529366824</v>
       </c>
       <c r="AO28" t="n">
-        <v>-99.99999999995248</v>
+        <v>-99.99999999998317</v>
       </c>
       <c r="AP28" t="n">
-        <v>-7.919405605740729e-11</v>
+        <v>-9.171041703837091e-11</v>
       </c>
       <c r="AQ28" t="n">
-        <v>-4.084510507595951e-13</v>
+        <v>-6.078471059822732e-13</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.0003204382552865191</v>
+        <v>0.0003204382052528487</v>
       </c>
       <c r="AS28" t="n">
-        <v>83.32235951247489</v>
+        <v>83.32235951259676</v>
       </c>
     </row>
     <row r="29">
@@ -7744,124 +7744,124 @@
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>0.001114029497285784</v>
+        <v>0.001114029497284008</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0001392536871607231</v>
+        <v>0.000139253687160501</v>
       </c>
       <c r="H29" t="n">
-        <v>132.0124954283655</v>
+        <v>132.012495428155</v>
       </c>
       <c r="I29" t="n">
-        <v>27850.73743214461</v>
+        <v>27850.73743210021</v>
       </c>
       <c r="J29" t="n">
-        <v>11.24364880862486</v>
+        <v>11.2436488086242</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.272740302085454e-05</v>
+        <v>-5.272740357512158e-05</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.01403178333646063</v>
+        <v>-0.01403178333646528</v>
       </c>
       <c r="M29" t="n">
-        <v>2.886833031477993e-07</v>
+        <v>2.88683288419905e-07</v>
       </c>
       <c r="N29" t="n">
-        <v>0.2818139420129872</v>
+        <v>0.2818139420131543</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.04505493136909523</v>
+        <v>-0.04505493136926936</v>
       </c>
       <c r="P29" t="n">
-        <v>11.24253477912758</v>
+        <v>11.24253477912691</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.272740302799424e-05</v>
+        <v>5.272740356380378e-05</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01403178333646062</v>
+        <v>0.01403178333646527</v>
       </c>
       <c r="S29" t="n">
-        <v>-2.886833036039658e-07</v>
+        <v>-2.886832883124274e-07</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2774101967681684</v>
+        <v>0.2774101967683359</v>
       </c>
       <c r="U29" t="n">
-        <v>0.01500512856537014</v>
+        <v>0.01500512856519697</v>
       </c>
       <c r="V29" t="n">
-        <v>-11.24364880862486</v>
+        <v>-11.2436488086242</v>
       </c>
       <c r="W29" t="n">
-        <v>-5.272740302085454e-05</v>
+        <v>-5.272740357512158e-05</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01403178333646063</v>
+        <v>0.01403178333646528</v>
       </c>
       <c r="Y29" t="n">
-        <v>-2.886833031477993e-07</v>
+        <v>-2.88683288419905e-07</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.2818139420129872</v>
+        <v>0.2818139420131543</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.04505493136909523</v>
+        <v>0.04505493136926936</v>
       </c>
       <c r="AB29" t="n">
-        <v>-11.24253477912758</v>
+        <v>-11.24253477912691</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.272740302799424e-05</v>
+        <v>5.272740356380378e-05</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.01403178333646062</v>
+        <v>-0.01403178333646527</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.886833036039658e-07</v>
+        <v>2.886832883124274e-07</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.2774101967681684</v>
+        <v>0.2774101967683359</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.01500512856537014</v>
+        <v>-0.01500512856519697</v>
       </c>
       <c r="AH29" t="n">
-        <v>-132.0124954283237</v>
+        <v>-132.0124954280909</v>
       </c>
       <c r="AI29" t="n">
-        <v>12.49725652629611</v>
+        <v>12.49725652632724</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-229.8566828607552</v>
+        <v>-229.8566828608935</v>
       </c>
       <c r="AK29" t="n">
-        <v>-1.232455641335499e-06</v>
+        <v>-1.232455577255556e-06</v>
       </c>
       <c r="AL29" t="n">
-        <v>921.870810053895</v>
+        <v>921.8708100544479</v>
       </c>
       <c r="AM29" t="n">
-        <v>83.32235936881273</v>
+        <v>83.32235936893775</v>
       </c>
       <c r="AN29" t="n">
-        <v>132.0124954283237</v>
+        <v>132.0124954280909</v>
       </c>
       <c r="AO29" t="n">
-        <v>-12.49725652629611</v>
+        <v>-12.49725652632724</v>
       </c>
       <c r="AP29" t="n">
-        <v>229.8566828607552</v>
+        <v>229.8566828608935</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.232455641335499e-06</v>
+        <v>1.232455577255556e-06</v>
       </c>
       <c r="AR29" t="n">
-        <v>916.9826528321462</v>
+        <v>916.9826528326996</v>
       </c>
       <c r="AS29" t="n">
-        <v>16.65569284155616</v>
+        <v>16.65569284168014</v>
       </c>
     </row>
     <row r="30">
@@ -7883,124 +7883,124 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0001054632224549705</v>
+        <v>-0.0001054632224549718</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.318290280687131e-05</v>
+        <v>-1.318290280687148e-05</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.49739186091401</v>
+        <v>-12.49739186091416</v>
       </c>
       <c r="I30" t="n">
-        <v>-2636.580561374263</v>
+        <v>-2636.580561374296</v>
       </c>
       <c r="J30" t="n">
-        <v>12.7636275507655</v>
+        <v>12.76362755076675</v>
       </c>
       <c r="K30" t="n">
-        <v>5.273160743815383e-05</v>
+        <v>5.273160774713402e-05</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01458744045581826</v>
+        <v>0.01458744045582377</v>
       </c>
       <c r="M30" t="n">
-        <v>1.041020896839185e-07</v>
+        <v>1.041021125745989e-07</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1191579135705716</v>
+        <v>0.1191579135707582</v>
       </c>
       <c r="O30" t="n">
-        <v>0.01500512783931789</v>
+        <v>0.01500512783927177</v>
       </c>
       <c r="P30" t="n">
-        <v>12.76362755075735</v>
+        <v>12.76362755075872</v>
       </c>
       <c r="Q30" t="n">
-        <v>-5.273161501681668e-05</v>
+        <v>-5.273161470783783e-05</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01458744045581829</v>
+        <v>0.01458744045582099</v>
       </c>
       <c r="S30" t="n">
-        <v>-1.041020131429611e-07</v>
+        <v>-1.041019902353731e-07</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1191579135705384</v>
+        <v>0.1191579135705613</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.01500512783735091</v>
+        <v>-0.01500512783739848</v>
       </c>
       <c r="V30" t="n">
-        <v>5.273160743815383e-05</v>
+        <v>5.273160774713402e-05</v>
       </c>
       <c r="W30" t="n">
-        <v>-12.7636275507655</v>
+        <v>-12.76362755076675</v>
       </c>
       <c r="X30" t="n">
-        <v>0.01458744045581826</v>
+        <v>0.01458744045582377</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.1191579135705716</v>
+        <v>0.1191579135707582</v>
       </c>
       <c r="Z30" t="n">
-        <v>-1.041020896839185e-07</v>
+        <v>-1.041021125745989e-07</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.01500512783931789</v>
+        <v>0.01500512783927177</v>
       </c>
       <c r="AB30" t="n">
-        <v>-5.273161501681668e-05</v>
+        <v>-5.273161470783783e-05</v>
       </c>
       <c r="AC30" t="n">
-        <v>-12.76362755075735</v>
+        <v>-12.76362755075872</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.01458744045581829</v>
+        <v>0.01458744045582099</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.1191579135705384</v>
+        <v>0.1191579135705613</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.041020131429611e-07</v>
+        <v>1.041019902353731e-07</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.01500512783735091</v>
+        <v>-0.01500512783739848</v>
       </c>
       <c r="AH30" t="n">
-        <v>12.49739186091401</v>
+        <v>12.49739186091416</v>
       </c>
       <c r="AI30" t="n">
-        <v>-2.91038304567337e-11</v>
+        <v>-5.616129783447832e-11</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.185670624457392e-11</v>
+        <v>5.1213033813724e-11</v>
       </c>
       <c r="AK30" t="n">
-        <v>7.083222897108499e-14</v>
+        <v>4.203304371230843e-13</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.000115553404494969</v>
+        <v>-0.0001155534819119453</v>
       </c>
       <c r="AM30" t="n">
-        <v>16.65569190043516</v>
+        <v>16.65569190032693</v>
       </c>
       <c r="AN30" t="n">
-        <v>-12.49739186091401</v>
+        <v>-12.49739186091416</v>
       </c>
       <c r="AO30" t="n">
-        <v>2.91038304567337e-11</v>
+        <v>5.616129783447832e-11</v>
       </c>
       <c r="AP30" t="n">
-        <v>-3.185670624457392e-11</v>
+        <v>-5.1213033813724e-11</v>
       </c>
       <c r="AQ30" t="n">
-        <v>-7.083222897108499e-14</v>
+        <v>-4.203304371230843e-13</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.0001155531496422071</v>
+        <v>0.0001155530722067866</v>
       </c>
       <c r="AS30" t="n">
-        <v>-16.65569190066799</v>
+        <v>-16.65569190077713</v>
       </c>
     </row>
     <row r="31">
@@ -8034,112 +8034,112 @@
         <v>17245.24937132265</v>
       </c>
       <c r="J31" t="n">
-        <v>12.76362755075735</v>
+        <v>12.76362755075872</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.273161501681668e-05</v>
+        <v>-5.273161470783783e-05</v>
       </c>
       <c r="L31" t="n">
-        <v>0.01458744045581829</v>
+        <v>0.01458744045582099</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.041020131429611e-07</v>
+        <v>-1.041019902353731e-07</v>
       </c>
       <c r="N31" t="n">
-        <v>0.1191579135705384</v>
+        <v>0.1191579135705613</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.01500512783735091</v>
+        <v>-0.01500512783739848</v>
       </c>
       <c r="P31" t="n">
-        <v>12.76431736073221</v>
+        <v>12.76431736073357</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.273161502770671e-05</v>
+        <v>5.273161469785554e-05</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.01458744045581832</v>
+        <v>-0.01458744045582099</v>
       </c>
       <c r="S31" t="n">
-        <v>1.041020126456332e-07</v>
+        <v>1.041019900625209e-07</v>
       </c>
       <c r="T31" t="n">
-        <v>0.09905190241355175</v>
+        <v>0.09905190241357491</v>
       </c>
       <c r="U31" t="n">
-        <v>0.04505493222254756</v>
+        <v>0.04505493222250071</v>
       </c>
       <c r="V31" t="n">
-        <v>12.76362755075735</v>
+        <v>12.76362755075872</v>
       </c>
       <c r="W31" t="n">
-        <v>-5.273161501681668e-05</v>
+        <v>-5.273161470783783e-05</v>
       </c>
       <c r="X31" t="n">
-        <v>0.01458744045581829</v>
+        <v>0.01458744045582099</v>
       </c>
       <c r="Y31" t="n">
-        <v>-1.041020131429611e-07</v>
+        <v>-1.041019902353731e-07</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.1191579135705384</v>
+        <v>0.1191579135705613</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.01500512783735091</v>
+        <v>-0.01500512783739848</v>
       </c>
       <c r="AB31" t="n">
-        <v>12.76431736073221</v>
+        <v>12.76431736073357</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.273161502770671e-05</v>
+        <v>5.273161469785554e-05</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.01458744045581832</v>
+        <v>-0.01458744045582099</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.041020126456332e-07</v>
+        <v>1.041019900625209e-07</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.09905190241355175</v>
+        <v>0.09905190241357491</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.04505493222254756</v>
+        <v>0.04505493222250071</v>
       </c>
       <c r="AH31" t="n">
         <v>-81.74248202005401</v>
       </c>
       <c r="AI31" t="n">
-        <v>12.49725630796159</v>
+        <v>12.49725630798878</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-87.79382485851036</v>
+        <v>-87.79382485852895</v>
       </c>
       <c r="AK31" t="n">
-        <v>-4.444355165871917e-07</v>
+        <v>-4.444354194820428e-07</v>
       </c>
       <c r="AL31" t="n">
-        <v>362.3341356261689</v>
+        <v>362.3341356262432</v>
       </c>
       <c r="AM31" t="n">
-        <v>16.65569189860274</v>
+        <v>16.65569189871105</v>
       </c>
       <c r="AN31" t="n">
         <v>81.74248202005401</v>
       </c>
       <c r="AO31" t="n">
-        <v>-12.49725630796159</v>
+        <v>-12.49725630798878</v>
       </c>
       <c r="AP31" t="n">
-        <v>87.79382485851036</v>
+        <v>87.79382485852895</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4.444355165871917e-07</v>
+        <v>4.444354194820428e-07</v>
       </c>
       <c r="AR31" t="n">
-        <v>340.0164632419138</v>
+        <v>340.0164632419883</v>
       </c>
       <c r="AS31" t="n">
-        <v>83.32235856509004</v>
+        <v>83.32235856519915</v>
       </c>
     </row>
     <row r="32">
@@ -8161,124 +8161,124 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>0.000105463222454975</v>
+        <v>0.0001054632224549722</v>
       </c>
       <c r="G32" t="n">
-        <v>1.318290280687187e-05</v>
+        <v>1.318290280687152e-05</v>
       </c>
       <c r="H32" t="n">
-        <v>12.49739186091453</v>
+        <v>12.4973918609142</v>
       </c>
       <c r="I32" t="n">
-        <v>2636.580561374374</v>
+        <v>2636.580561374304</v>
       </c>
       <c r="J32" t="n">
-        <v>12.76431736073221</v>
+        <v>12.76431736073357</v>
       </c>
       <c r="K32" t="n">
-        <v>5.273161502770671e-05</v>
+        <v>5.273161469785554e-05</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.01458744045581832</v>
+        <v>-0.01458744045582099</v>
       </c>
       <c r="M32" t="n">
-        <v>1.041020126456332e-07</v>
+        <v>1.041019900625209e-07</v>
       </c>
       <c r="N32" t="n">
-        <v>0.09905190241355175</v>
+        <v>0.09905190241357491</v>
       </c>
       <c r="O32" t="n">
-        <v>0.04505493222254756</v>
+        <v>0.04505493222250071</v>
       </c>
       <c r="P32" t="n">
-        <v>12.76431736074036</v>
+        <v>12.76431736074161</v>
       </c>
       <c r="Q32" t="n">
-        <v>-5.273160742726827e-05</v>
+        <v>-5.273160775711663e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.01458744045581826</v>
+        <v>-0.01458744045582378</v>
       </c>
       <c r="S32" t="n">
-        <v>-1.041020899760041e-07</v>
+        <v>-1.041021128221863e-07</v>
       </c>
       <c r="T32" t="n">
-        <v>0.09905190241358573</v>
+        <v>0.09905190241377351</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.04505493222058038</v>
+        <v>-0.04505493222062767</v>
       </c>
       <c r="V32" t="n">
-        <v>-5.273161502770671e-05</v>
+        <v>-5.273161469785554e-05</v>
       </c>
       <c r="W32" t="n">
-        <v>12.76431736073221</v>
+        <v>12.76431736073357</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.01458744045581832</v>
+        <v>-0.01458744045582099</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.09905190241355175</v>
+        <v>-0.09905190241357491</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.041020126456332e-07</v>
+        <v>1.041019900625209e-07</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.04505493222254756</v>
+        <v>0.04505493222250071</v>
       </c>
       <c r="AB32" t="n">
-        <v>5.273160742726827e-05</v>
+        <v>5.273160775711663e-05</v>
       </c>
       <c r="AC32" t="n">
-        <v>12.76431736074036</v>
+        <v>12.76431736074161</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.01458744045581826</v>
+        <v>-0.01458744045582378</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.09905190241358573</v>
+        <v>-0.09905190241377351</v>
       </c>
       <c r="AF32" t="n">
-        <v>-1.041020899760041e-07</v>
+        <v>-1.041021128221863e-07</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.04505493222058038</v>
+        <v>-0.04505493222062767</v>
       </c>
       <c r="AH32" t="n">
-        <v>-12.49739186091453</v>
+        <v>-12.4973918609142</v>
       </c>
       <c r="AI32" t="n">
-        <v>-100.0000000000293</v>
+        <v>-100.0000000000568</v>
       </c>
       <c r="AJ32" t="n">
-        <v>3.218251569913049e-11</v>
+        <v>5.138911518542955e-11</v>
       </c>
       <c r="AK32" t="n">
-        <v>7.255307465925398e-14</v>
+        <v>4.23938661953116e-13</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.0001155531482243991</v>
+        <v>0.0001155530715442055</v>
       </c>
       <c r="AM32" t="n">
-        <v>-83.32235856751535</v>
+        <v>-83.32235856762449</v>
       </c>
       <c r="AN32" t="n">
-        <v>12.49739186091453</v>
+        <v>12.4973918609142</v>
       </c>
       <c r="AO32" t="n">
-        <v>-99.99999999997067</v>
+        <v>-99.99999999994316</v>
       </c>
       <c r="AP32" t="n">
-        <v>-3.218251569913049e-11</v>
+        <v>-5.138911518542955e-11</v>
       </c>
       <c r="AQ32" t="n">
-        <v>-7.255307465925398e-14</v>
+        <v>-4.23938661953116e-13</v>
       </c>
       <c r="AR32" t="n">
-        <v>-0.0001155534056854128</v>
+        <v>-0.0001155534826580151</v>
       </c>
       <c r="AS32" t="n">
-        <v>83.32235856727888</v>
+        <v>83.32235856716974</v>
       </c>
     </row>
     <row r="33">
@@ -8300,124 +8300,124 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0006898099748582354</v>
+        <v>0.000689809974856459</v>
       </c>
       <c r="G33" t="n">
-        <v>8.622624685727942e-05</v>
+        <v>8.622624685705738e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>81.74248202070089</v>
+        <v>81.7424820204904</v>
       </c>
       <c r="I33" t="n">
-        <v>17245.24937145588</v>
+        <v>17245.24937141148</v>
       </c>
       <c r="J33" t="n">
-        <v>12.76431736074036</v>
+        <v>12.76431736074161</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.273160742726827e-05</v>
+        <v>-5.273160775711663e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.01458744045581826</v>
+        <v>-0.01458744045582378</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.041020899760041e-07</v>
+        <v>-1.041021128221863e-07</v>
       </c>
       <c r="N33" t="n">
-        <v>0.09905190241358573</v>
+        <v>0.09905190241377351</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.04505493222058038</v>
+        <v>-0.04505493222062767</v>
       </c>
       <c r="P33" t="n">
-        <v>12.7636275507655</v>
+        <v>12.76362755076675</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.273160743815383e-05</v>
+        <v>5.273160774713402e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>0.01458744045581826</v>
+        <v>0.01458744045582377</v>
       </c>
       <c r="S33" t="n">
-        <v>1.041020896839185e-07</v>
+        <v>1.041021125745989e-07</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1191579135705716</v>
+        <v>0.1191579135707582</v>
       </c>
       <c r="U33" t="n">
-        <v>0.01500512783931789</v>
+        <v>0.01500512783927177</v>
       </c>
       <c r="V33" t="n">
-        <v>-12.76431736074036</v>
+        <v>-12.76431736074161</v>
       </c>
       <c r="W33" t="n">
-        <v>-5.273160742726827e-05</v>
+        <v>-5.273160775711663e-05</v>
       </c>
       <c r="X33" t="n">
-        <v>0.01458744045581826</v>
+        <v>0.01458744045582378</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.041020899760041e-07</v>
+        <v>1.041021128221863e-07</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.09905190241358573</v>
+        <v>0.09905190241377351</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.04505493222058038</v>
+        <v>0.04505493222062767</v>
       </c>
       <c r="AB33" t="n">
-        <v>-12.7636275507655</v>
+        <v>-12.76362755076675</v>
       </c>
       <c r="AC33" t="n">
-        <v>5.273160743815383e-05</v>
+        <v>5.273160774713402e-05</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.01458744045581826</v>
+        <v>-0.01458744045582377</v>
       </c>
       <c r="AE33" t="n">
-        <v>-1.041020896839185e-07</v>
+        <v>-1.041021125745989e-07</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.1191579135705716</v>
+        <v>0.1191579135707582</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.01500512783931789</v>
+        <v>-0.01500512783927177</v>
       </c>
       <c r="AH33" t="n">
-        <v>-81.7424820207525</v>
+        <v>-81.74248202051967</v>
       </c>
       <c r="AI33" t="n">
-        <v>12.49725630790358</v>
+        <v>12.49725630787598</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-87.79382485853831</v>
+        <v>-87.793824858693</v>
       </c>
       <c r="AK33" t="n">
-        <v>4.444358450432963e-07</v>
+        <v>4.44435942673907e-07</v>
       </c>
       <c r="AL33" t="n">
-        <v>340.0164632420261</v>
+        <v>340.0164632426455</v>
       </c>
       <c r="AM33" t="n">
-        <v>83.32235856485785</v>
+        <v>83.32235856474811</v>
       </c>
       <c r="AN33" t="n">
-        <v>81.7424820207525</v>
+        <v>81.74248202051967</v>
       </c>
       <c r="AO33" t="n">
-        <v>-12.49725630790358</v>
+        <v>-12.49725630787598</v>
       </c>
       <c r="AP33" t="n">
-        <v>87.79382485853831</v>
+        <v>87.793824858693</v>
       </c>
       <c r="AQ33" t="n">
-        <v>-4.444358450432963e-07</v>
+        <v>-4.44435942673907e-07</v>
       </c>
       <c r="AR33" t="n">
-        <v>362.3341356262804</v>
+        <v>362.3341356268984</v>
       </c>
       <c r="AS33" t="n">
-        <v>16.65569189837078</v>
+        <v>16.65569189825973</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/validation_frame_member_loads.xlsx
+++ b/outputs/validation_frame_member_loads.xlsx
@@ -643,25 +643,25 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>3.595119805279023</v>
+        <v>3.595119805279563</v>
       </c>
       <c r="F6" t="n">
-        <v>5.264656576807992e-05</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007516730126564649</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="H6" t="n">
-        <v>-5.81758716827277e-06</v>
+        <v>-5.817587131184721e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5733905572098467</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01497636114528572</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="K6" t="n">
-        <v>3.595127663701657</v>
+        <v>3.595127663702197</v>
       </c>
     </row>
     <row r="7">
@@ -678,25 +678,25 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>3.595119805277716</v>
+        <v>3.595119805277692</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.264656709829736e-05</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007516730126563812</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="H7" t="n">
-        <v>5.817587402268885e-06</v>
+        <v>5.817587439357226e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5733905572096085</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0149763611449562</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="K7" t="n">
-        <v>3.59512766370035</v>
+        <v>3.595127663700326</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +713,25 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>3.596176627224358</v>
+        <v>3.596176627224334</v>
       </c>
       <c r="F8" t="n">
-        <v>5.264656709531542e-05</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.007516730126563806</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.817587401731315e-06</v>
+        <v>-5.817587439646455e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5737082536248662</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04500689564365364</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="K8" t="n">
-        <v>3.596184483337613</v>
+        <v>3.596184483337589</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +748,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>3.596176627225665</v>
+        <v>3.596176627226205</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.264656577106183e-05</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.007516730126564661</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="H9" t="n">
-        <v>5.817587168809183e-06</v>
+        <v>5.817587130890855e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5737082536251048</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0450068956433242</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="K9" t="n">
-        <v>3.59618448333892</v>
+        <v>3.59618448333946</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>8.113133295380457</v>
+        <v>8.113133295381624</v>
       </c>
       <c r="F10" t="n">
-        <v>5.274814816710414e-05</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01202133708507639</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="H10" t="n">
-        <v>1.276246291459122e-06</v>
+        <v>1.276246312356512e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4768655535134355</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01500508180312803</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="K10" t="n">
-        <v>8.11314220163425</v>
+        <v>8.113142201635418</v>
       </c>
     </row>
     <row r="11">
@@ -818,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>8.11313329537693</v>
+        <v>8.113133295376661</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.274815161206213e-05</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01202133708507474</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.276246032599108e-06</v>
+        <v>-1.276246011702428e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4768655535131607</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.01500508180225687</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="K11" t="n">
-        <v>8.113142201630723</v>
+        <v>8.113142201630454</v>
       </c>
     </row>
     <row r="12">
@@ -853,25 +853,25 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>8.114175479580929</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="F12" t="n">
-        <v>5.274815160420837e-05</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01202133708507473</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="H12" t="n">
-        <v>1.276246033172293e-06</v>
+        <v>1.27624601135778e-06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4758775876426864</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="J12" t="n">
-        <v>0.04505488004373993</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="K12" t="n">
-        <v>8.114184384690805</v>
+        <v>8.114184384690539</v>
       </c>
     </row>
     <row r="13">
@@ -888,25 +888,25 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>8.114175479584461</v>
+        <v>8.114175479585626</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.274814817495947e-05</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0120213370850764</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.276246290880136e-06</v>
+        <v>-1.276246312679776e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4758775876429612</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.04505488004286866</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="K13" t="n">
-        <v>8.114184384694337</v>
+        <v>8.1141843846955</v>
       </c>
     </row>
     <row r="14">
@@ -923,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>11.24253477912691</v>
+        <v>11.24253477912758</v>
       </c>
       <c r="F14" t="n">
-        <v>5.272740356380378e-05</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01403178333646527</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.886832883124274e-07</v>
+        <v>-2.886833036039658e-07</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2774101967683359</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01500512856519697</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="K14" t="n">
-        <v>11.24254353576636</v>
+        <v>11.24254353576703</v>
       </c>
     </row>
     <row r="15">
@@ -958,25 +958,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>11.24253477912112</v>
+        <v>11.2425347791201</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.272740904099736e-05</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01403178333646289</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="H15" t="n">
-        <v>2.886835082336281e-07</v>
+        <v>2.886834930193329e-07</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2774101967680513</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.01500512856379087</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="K15" t="n">
-        <v>11.24254353576057</v>
+        <v>11.24254353575955</v>
       </c>
     </row>
     <row r="16">
@@ -993,25 +993,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>11.24364880861841</v>
+        <v>11.24364880861739</v>
       </c>
       <c r="F16" t="n">
-        <v>5.27274090296737e-05</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.01403178333646289</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.886835081465285e-07</v>
+        <v>-2.886834933623841e-07</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2818139420128695</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="J16" t="n">
-        <v>0.04505493137067544</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="K16" t="n">
-        <v>11.24365756439025</v>
+        <v>11.24365756438923</v>
       </c>
     </row>
     <row r="17">
@@ -1028,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>11.2436488086242</v>
+        <v>11.24364880862486</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.272740357512158e-05</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.01403178333646528</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="H17" t="n">
-        <v>2.88683288419905e-07</v>
+        <v>2.886833031477993e-07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2818139420131543</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.04505493136926936</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="K17" t="n">
-        <v>11.24365756439603</v>
+        <v>11.2436575643967</v>
       </c>
     </row>
     <row r="18">
@@ -1063,25 +1063,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>12.76362755076675</v>
+        <v>12.7636275507655</v>
       </c>
       <c r="F18" t="n">
-        <v>5.273160774713402e-05</v>
+        <v>5.273160743815383e-05</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01458744045582377</v>
+        <v>0.01458744045581826</v>
       </c>
       <c r="H18" t="n">
-        <v>1.041021125745989e-07</v>
+        <v>1.041020896839185e-07</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1191579135707582</v>
+        <v>0.1191579135705716</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01500512783927177</v>
+        <v>0.01500512783931789</v>
       </c>
       <c r="K18" t="n">
-        <v>12.76363588680325</v>
+        <v>12.76363588680199</v>
       </c>
     </row>
     <row r="19">
@@ -1098,25 +1098,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>12.76362755075872</v>
+        <v>12.76362755075735</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.273161470783783e-05</v>
+        <v>-5.273161501681668e-05</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01458744045582099</v>
+        <v>0.01458744045581829</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.041019902353731e-07</v>
+        <v>-1.041020131429611e-07</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1191579135705613</v>
+        <v>0.1191579135705384</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.01500512783739848</v>
+        <v>-0.01500512783735091</v>
       </c>
       <c r="K19" t="n">
-        <v>12.76363588679521</v>
+        <v>12.76363588679385</v>
       </c>
     </row>
     <row r="20">
@@ -1133,25 +1133,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>12.76431736073357</v>
+        <v>12.76431736073221</v>
       </c>
       <c r="F20" t="n">
-        <v>5.273161469785554e-05</v>
+        <v>5.273161502770671e-05</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.01458744045582099</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="H20" t="n">
-        <v>1.041019900625209e-07</v>
+        <v>1.041020126456332e-07</v>
       </c>
       <c r="I20" t="n">
-        <v>0.09905190241357491</v>
+        <v>0.09905190241355175</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04505493222250071</v>
+        <v>0.04505493222254756</v>
       </c>
       <c r="K20" t="n">
-        <v>12.76432569631957</v>
+        <v>12.7643256963182</v>
       </c>
     </row>
     <row r="21">
@@ -1168,25 +1168,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>12.76431736074161</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.273160775711663e-05</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.01458744045582378</v>
+        <v>-0.01458744045581826</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.041021128221863e-07</v>
+        <v>-1.041020899760041e-07</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09905190241377351</v>
+        <v>0.09905190241358573</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.04505493222062767</v>
+        <v>-0.04505493222058038</v>
       </c>
       <c r="K21" t="n">
-        <v>12.76432569632761</v>
+        <v>12.76432569632636</v>
       </c>
     </row>
   </sheetData>
@@ -1245,16 +1245,16 @@
         <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>12.76432569632761</v>
+        <v>12.76432569632636</v>
       </c>
       <c r="D2" t="n">
-        <v>12.76431736074161</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.273160775711663e-05</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.01458744045582378</v>
+        <v>-0.01458744045581826</v>
       </c>
     </row>
     <row r="3">
@@ -1267,16 +1267,16 @@
         <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>12.76431736074161</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="D3" t="n">
-        <v>12.76431736074161</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.273160775711663e-05</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.01458744045582378</v>
+        <v>-0.01458744045581826</v>
       </c>
     </row>
     <row r="4">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>-5.274815161206213e-05</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>8.11313329537693</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.274815161206213e-05</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01202133708507474</v>
+        <v>-0.012021337085073</v>
       </c>
     </row>
     <row r="5">
@@ -1308,19 +1308,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.01458744045582378</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="D5" t="n">
-        <v>12.76431736074161</v>
+        <v>12.76431736073221</v>
       </c>
       <c r="E5" t="n">
-        <v>-5.273160775711663e-05</v>
+        <v>5.273161502770671e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01458744045582378</v>
+        <v>-0.01458744045581832</v>
       </c>
     </row>
   </sheetData>
@@ -1379,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-462.4872063002059</v>
+        <v>-462.4872063002725</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.008681138384937864</v>
+        <v>-0.008681138355291034</v>
       </c>
       <c r="D2" t="n">
-        <v>-1187.643359997215</v>
+        <v>-1187.643359997</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03034842965933544</v>
+        <v>0.03034842954294979</v>
       </c>
       <c r="F2" t="n">
-        <v>-1811.770631235904</v>
+        <v>-1811.770631236171</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.04262502787504397</v>
+        <v>-0.04262502787522724</v>
       </c>
     </row>
     <row r="3">
@@ -1402,22 +1402,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-462.4872063000596</v>
+        <v>-462.4872063000618</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008681138539901042</v>
+        <v>0.00868113856954778</v>
       </c>
       <c r="D3" t="n">
-        <v>-1187.643359997083</v>
+        <v>-1187.643359996955</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0303484302973821</v>
+        <v>-0.03034843041376769</v>
       </c>
       <c r="F3" t="n">
-        <v>-1811.770631235289</v>
+        <v>-1811.770631235287</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0426250278741061</v>
+        <v>0.04262502787392255</v>
       </c>
     </row>
     <row r="4">
@@ -1425,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>-537.5127936996073</v>
+        <v>-537.5127936996093</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.008681138539563298</v>
+        <v>-0.008681138569743792</v>
       </c>
       <c r="D4" t="n">
-        <v>1187.643359997082</v>
+        <v>1187.643359996957</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03034843029597107</v>
+        <v>0.03034843041456974</v>
       </c>
       <c r="F4" t="n">
-        <v>-1887.082488781223</v>
+        <v>-1887.082488781221</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1280965491396296</v>
+        <v>-0.1280965491398132</v>
       </c>
     </row>
     <row r="5">
@@ -1448,22 +1448,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-537.5127936997534</v>
+        <v>-537.51279369982</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008681138385276456</v>
+        <v>0.008681138355098365</v>
       </c>
       <c r="D5" t="n">
-        <v>1187.643359997217</v>
+        <v>1187.643359997</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03034842966074816</v>
+        <v>-0.03034842954215432</v>
       </c>
       <c r="F5" t="n">
-        <v>-1887.082488781838</v>
+        <v>-1887.082488782104</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1280965491386919</v>
+        <v>0.1280965491385087</v>
       </c>
     </row>
   </sheetData>
@@ -1606,52 +1606,52 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007516730126564649</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001252788354427442</v>
+        <v>0.001252788354427215</v>
       </c>
       <c r="H2" t="n">
-        <v>1187.643359997215</v>
+        <v>1187.643359997</v>
       </c>
       <c r="I2" t="n">
-        <v>250557.6708854883</v>
+        <v>250557.670885443</v>
       </c>
       <c r="J2" t="n">
-        <v>-1187.643359997215</v>
+        <v>-1187.643359997</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.008681138384937864</v>
+        <v>-0.008681138355291034</v>
       </c>
       <c r="L2" t="n">
-        <v>462.4872063002059</v>
+        <v>462.4872063002725</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04262502787504397</v>
+        <v>-0.04262502787522724</v>
       </c>
       <c r="N2" t="n">
-        <v>-1811.770631235904</v>
+        <v>-1811.770631236171</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.03034842965933544</v>
+        <v>-0.03034842954294979</v>
       </c>
       <c r="P2" t="n">
-        <v>1187.643359997215</v>
+        <v>1187.643359997</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.008681138384937864</v>
+        <v>0.008681138355291034</v>
       </c>
       <c r="R2" t="n">
-        <v>-462.4872063002059</v>
+        <v>-462.4872063002725</v>
       </c>
       <c r="S2" t="n">
-        <v>0.04262502787504397</v>
+        <v>0.04262502787522724</v>
       </c>
       <c r="T2" t="n">
-        <v>-963.1526065653311</v>
+        <v>-963.1526065654646</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.02173840065029174</v>
+        <v>-0.02173840058879641</v>
       </c>
     </row>
     <row r="3">
@@ -1673,52 +1673,52 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007516730126563812</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001252788354427302</v>
+        <v>0.001252788354427168</v>
       </c>
       <c r="H3" t="n">
-        <v>1187.643359997082</v>
+        <v>1187.643359996955</v>
       </c>
       <c r="I3" t="n">
-        <v>250557.6708854604</v>
+        <v>250557.6708854335</v>
       </c>
       <c r="J3" t="n">
-        <v>-1187.643359997083</v>
+        <v>-1187.643359996955</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008681138539901042</v>
+        <v>0.00868113856954778</v>
       </c>
       <c r="L3" t="n">
-        <v>462.4872063000596</v>
+        <v>462.4872063000618</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0426250278741061</v>
+        <v>0.04262502787392255</v>
       </c>
       <c r="N3" t="n">
-        <v>-1811.770631235289</v>
+        <v>-1811.770631235287</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0303484302973821</v>
+        <v>0.03034843041376769</v>
       </c>
       <c r="P3" t="n">
-        <v>1187.643359997083</v>
+        <v>1187.643359996955</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.008681138539901042</v>
+        <v>-0.00868113856954778</v>
       </c>
       <c r="R3" t="n">
-        <v>-462.4872063000596</v>
+        <v>-462.4872063000618</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0426250278741061</v>
+        <v>-0.04262502787392255</v>
       </c>
       <c r="T3" t="n">
-        <v>-963.1526065650683</v>
+        <v>-963.1526065650828</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02173840094202415</v>
+        <v>0.021738401003519</v>
       </c>
     </row>
     <row r="4">
@@ -1740,52 +1740,52 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.007516730126563806</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001252788354427301</v>
+        <v>-0.00125278835442717</v>
       </c>
       <c r="H4" t="n">
-        <v>-1187.643359997081</v>
+        <v>-1187.643359996957</v>
       </c>
       <c r="I4" t="n">
-        <v>-250557.6708854602</v>
+        <v>-250557.6708854339</v>
       </c>
       <c r="J4" t="n">
-        <v>1187.643359997082</v>
+        <v>1187.643359996957</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.008681138539563298</v>
+        <v>-0.008681138569743792</v>
       </c>
       <c r="L4" t="n">
-        <v>537.5127936996073</v>
+        <v>537.5127936996093</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1280965491396296</v>
+        <v>-0.1280965491398132</v>
       </c>
       <c r="N4" t="n">
-        <v>-1887.082488781223</v>
+        <v>-1887.082488781221</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.03034843029597107</v>
+        <v>-0.03034843041456974</v>
       </c>
       <c r="P4" t="n">
-        <v>-1187.643359997082</v>
+        <v>-1187.643359996957</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008681138539563298</v>
+        <v>0.008681138569743792</v>
       </c>
       <c r="R4" t="n">
-        <v>-387.5127936996073</v>
+        <v>-387.5127936996093</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1280965491396296</v>
+        <v>0.1280965491398132</v>
       </c>
       <c r="T4" t="n">
-        <v>-887.9942734164206</v>
+        <v>-887.9942734164347</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.02173840094140872</v>
+        <v>-0.02173840100389299</v>
       </c>
     </row>
     <row r="5">
@@ -1807,52 +1807,52 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.007516730126564661</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.001252788354427443</v>
+        <v>-0.001252788354427215</v>
       </c>
       <c r="H5" t="n">
-        <v>-1187.643359997216</v>
+        <v>-1187.643359997</v>
       </c>
       <c r="I5" t="n">
-        <v>-250557.6708854887</v>
+        <v>-250557.670885443</v>
       </c>
       <c r="J5" t="n">
-        <v>1187.643359997217</v>
+        <v>1187.643359997</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008681138385276456</v>
+        <v>0.008681138355098365</v>
       </c>
       <c r="L5" t="n">
-        <v>537.5127936997534</v>
+        <v>537.51279369982</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1280965491386919</v>
+        <v>0.1280965491385087</v>
       </c>
       <c r="N5" t="n">
-        <v>-1887.082488781838</v>
+        <v>-1887.082488782104</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03034842966074816</v>
+        <v>0.03034842954215432</v>
       </c>
       <c r="P5" t="n">
-        <v>-1187.643359997217</v>
+        <v>-1187.643359997</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.008681138385276456</v>
+        <v>-0.008681138355098365</v>
       </c>
       <c r="R5" t="n">
-        <v>-387.5127936997534</v>
+        <v>-387.51279369982</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1280965491386919</v>
+        <v>-0.1280965491385087</v>
       </c>
       <c r="T5" t="n">
-        <v>-887.9942734166825</v>
+        <v>-887.9942734168162</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02173840065091057</v>
+        <v>0.02173840058843586</v>
       </c>
     </row>
     <row r="6">
@@ -1874,52 +1874,52 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004504606958511741</v>
+        <v>0.004504606958510098</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0007507678264186235</v>
+        <v>0.0007507678264183497</v>
       </c>
       <c r="H6" t="n">
-        <v>711.7278994448551</v>
+        <v>711.7278994445956</v>
       </c>
       <c r="I6" t="n">
-        <v>150153.5652837247</v>
+        <v>150153.5652836699</v>
       </c>
       <c r="J6" t="n">
-        <v>-711.7278994448552</v>
+        <v>-711.7278994445956</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00333553525708279</v>
+        <v>0.003335535281722257</v>
       </c>
       <c r="L6" t="n">
-        <v>337.2538056231251</v>
+        <v>337.2538056231967</v>
       </c>
       <c r="M6" t="n">
-        <v>-8.17434107819523e-05</v>
+        <v>-8.174341103647093e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>-940.3329141340305</v>
+        <v>-940.3329141341959</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01525604253144997</v>
+        <v>0.01525604259338728</v>
       </c>
       <c r="P6" t="n">
-        <v>711.7278994448552</v>
+        <v>711.7278994445956</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.00333553525708279</v>
+        <v>-0.003335535281722257</v>
       </c>
       <c r="R6" t="n">
-        <v>-337.2538056231251</v>
+        <v>-337.2538056231967</v>
       </c>
       <c r="S6" t="n">
-        <v>8.17434107819523e-05</v>
+        <v>8.174341103647093e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>-1083.189919604719</v>
+        <v>-1083.189919604984</v>
       </c>
       <c r="U6" t="n">
-        <v>0.004757169011046773</v>
+        <v>0.004757169096946262</v>
       </c>
     </row>
     <row r="7">
@@ -1941,52 +1941,52 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004504606958510925</v>
+        <v>0.004504606958509978</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007507678264184874</v>
+        <v>0.0007507678264183296</v>
       </c>
       <c r="H7" t="n">
-        <v>711.7278994447261</v>
+        <v>711.7278994445765</v>
       </c>
       <c r="I7" t="n">
-        <v>150153.5652836975</v>
+        <v>150153.5652836659</v>
       </c>
       <c r="J7" t="n">
-        <v>-711.7278994447263</v>
+        <v>-711.7278994445767</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.003335535100160325</v>
+        <v>-0.003335535075520275</v>
       </c>
       <c r="L7" t="n">
-        <v>337.2538056229571</v>
+        <v>337.2538056229537</v>
       </c>
       <c r="M7" t="n">
-        <v>8.174340924035906e-05</v>
+        <v>8.174340898744331e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>-940.3329141334998</v>
+        <v>-940.3329141334489</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0152560420422833</v>
+        <v>-0.01525604198034497</v>
       </c>
       <c r="P7" t="n">
-        <v>711.7278994447263</v>
+        <v>711.7278994445767</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003335535100160325</v>
+        <v>0.003335535075520275</v>
       </c>
       <c r="R7" t="n">
-        <v>-337.2538056229571</v>
+        <v>-337.2538056229537</v>
       </c>
       <c r="S7" t="n">
-        <v>-8.174340924035906e-05</v>
+        <v>-8.174340898744331e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>-1083.189919604242</v>
+        <v>-1083.189919604273</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.004757168558678665</v>
+        <v>-0.004757168472776685</v>
       </c>
     </row>
     <row r="8">
@@ -2008,52 +2008,52 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.004504606958510924</v>
+        <v>-0.004504606958509985</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0007507678264184873</v>
+        <v>-0.0007507678264183309</v>
       </c>
       <c r="H8" t="n">
-        <v>-711.7278994447259</v>
+        <v>-711.7278994445777</v>
       </c>
       <c r="I8" t="n">
-        <v>-150153.5652836974</v>
+        <v>-150153.5652836662</v>
       </c>
       <c r="J8" t="n">
-        <v>711.7278994447261</v>
+        <v>711.7278994445778</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003335535100540082</v>
+        <v>0.003335535075336502</v>
       </c>
       <c r="L8" t="n">
-        <v>412.7461943766323</v>
+        <v>412.7461943766295</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0001365709848609731</v>
+        <v>-0.0001365709851156582</v>
       </c>
       <c r="N8" t="n">
-        <v>-1015.843890303083</v>
+        <v>-1015.843890303033</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01525604204344892</v>
+        <v>0.01525604197975264</v>
       </c>
       <c r="P8" t="n">
-        <v>-711.7278994447261</v>
+        <v>-711.7278994445778</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.003335535100540082</v>
+        <v>-0.003335535075336502</v>
       </c>
       <c r="R8" t="n">
-        <v>-262.7461943766323</v>
+        <v>-262.7461943766295</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0001365709848609731</v>
+        <v>0.0001365709851156582</v>
       </c>
       <c r="T8" t="n">
-        <v>-1010.633275956709</v>
+        <v>-1010.633275956742</v>
       </c>
       <c r="U8" t="n">
-        <v>0.004757168559791573</v>
+        <v>0.004757168472266371</v>
       </c>
     </row>
     <row r="9">
@@ -2075,52 +2075,52 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.004504606958511742</v>
+        <v>-0.004504606958510099</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0007507678264186236</v>
+        <v>-0.0007507678264183498</v>
       </c>
       <c r="H9" t="n">
-        <v>-711.7278994448552</v>
+        <v>-711.7278994445957</v>
       </c>
       <c r="I9" t="n">
-        <v>-150153.5652837247</v>
+        <v>-150153.56528367</v>
       </c>
       <c r="J9" t="n">
-        <v>711.7278994448554</v>
+        <v>711.7278994445958</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.003335535256706077</v>
+        <v>-0.003335535281918336</v>
       </c>
       <c r="L9" t="n">
-        <v>412.7461943768008</v>
+        <v>412.7461943768724</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001365709833188455</v>
+        <v>0.0001365709830680184</v>
       </c>
       <c r="N9" t="n">
-        <v>-1015.843890303616</v>
+        <v>-1015.843890303781</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.01525604253028832</v>
+        <v>-0.01525604259399728</v>
       </c>
       <c r="P9" t="n">
-        <v>-711.7278994448554</v>
+        <v>-711.7278994445958</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003335535256706077</v>
+        <v>0.003335535281918336</v>
       </c>
       <c r="R9" t="n">
-        <v>-262.7461943768008</v>
+        <v>-262.7461943768724</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0001365709833188455</v>
+        <v>-0.0001365709830680184</v>
       </c>
       <c r="T9" t="n">
-        <v>-1010.633275957188</v>
+        <v>-1010.633275957454</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.004757169009948131</v>
+        <v>-0.00475716909751274</v>
       </c>
     </row>
     <row r="10">
@@ -2142,52 +2142,52 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002010446251388883</v>
+        <v>0.002010446251387233</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003350743752314805</v>
+        <v>0.0003350743752312055</v>
       </c>
       <c r="H10" t="n">
-        <v>317.6505077194435</v>
+        <v>317.6505077191828</v>
       </c>
       <c r="I10" t="n">
-        <v>67014.87504629609</v>
+        <v>67014.8750462411</v>
       </c>
       <c r="J10" t="n">
-        <v>-317.6505077194436</v>
+        <v>-317.6505077191828</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0007256796201811321</v>
+        <v>-0.000725679616803785</v>
       </c>
       <c r="L10" t="n">
-        <v>213.7549774489485</v>
+        <v>213.7549774489315</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.330920423731063e-07</v>
+        <v>-1.330920974471073e-07</v>
       </c>
       <c r="N10" t="n">
-        <v>-493.6679683554712</v>
+        <v>-493.6679683552808</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.003335086749574341</v>
+        <v>-0.003335086766222121</v>
       </c>
       <c r="P10" t="n">
-        <v>317.6505077194436</v>
+        <v>317.6505077191828</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0007256796201811321</v>
+        <v>0.000725679616803785</v>
       </c>
       <c r="R10" t="n">
-        <v>-213.7549774489485</v>
+        <v>-213.7549774489315</v>
       </c>
       <c r="S10" t="n">
-        <v>1.330920423731063e-07</v>
+        <v>1.330920974471073e-07</v>
       </c>
       <c r="T10" t="n">
-        <v>-788.8618963382187</v>
+        <v>-788.861896338309</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.001018990971512444</v>
+        <v>-0.00101899093460061</v>
       </c>
     </row>
     <row r="11">
@@ -2209,52 +2209,52 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002010446251388151</v>
+        <v>0.00201044625138745</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003350743752313584</v>
+        <v>0.0003350743752312416</v>
       </c>
       <c r="H11" t="n">
-        <v>317.6505077193278</v>
+        <v>317.6505077192171</v>
       </c>
       <c r="I11" t="n">
-        <v>67014.87504627169</v>
+        <v>67014.87504624833</v>
       </c>
       <c r="J11" t="n">
-        <v>-317.6505077193278</v>
+        <v>-317.6505077192171</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0007256797671678136</v>
+        <v>0.0007256797704882252</v>
       </c>
       <c r="L11" t="n">
-        <v>213.7549774488043</v>
+        <v>213.7549774487221</v>
       </c>
       <c r="M11" t="n">
-        <v>1.330905198618226e-07</v>
+        <v>1.330904625743146e-07</v>
       </c>
       <c r="N11" t="n">
-        <v>-493.6679683550301</v>
+        <v>-493.6679683547802</v>
       </c>
       <c r="O11" t="n">
-        <v>0.003335087161719666</v>
+        <v>0.003335087144958782</v>
       </c>
       <c r="P11" t="n">
-        <v>317.6505077193278</v>
+        <v>317.6505077192171</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.0007256797671678136</v>
+        <v>-0.0007256797704882252</v>
       </c>
       <c r="R11" t="n">
-        <v>-213.7549774488043</v>
+        <v>-213.7549774487221</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.330905198618226e-07</v>
+        <v>-1.330904625743146e-07</v>
       </c>
       <c r="T11" t="n">
-        <v>-788.8618963377921</v>
+        <v>-788.8618963375543</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001018991441287212</v>
+        <v>0.001018991477970577</v>
       </c>
     </row>
     <row r="12">
@@ -2276,52 +2276,52 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.002010446251388158</v>
+        <v>-0.002010446251387455</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0003350743752313596</v>
+        <v>-0.0003350743752312425</v>
       </c>
       <c r="H12" t="n">
-        <v>-317.6505077193289</v>
+        <v>-317.6505077192179</v>
       </c>
       <c r="I12" t="n">
-        <v>-67014.87504627192</v>
+        <v>-67014.8750462485</v>
       </c>
       <c r="J12" t="n">
-        <v>317.650507719329</v>
+        <v>317.6505077192182</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0007256797668005119</v>
+        <v>-0.0007256797706754747</v>
       </c>
       <c r="L12" t="n">
-        <v>286.245022550801</v>
+        <v>286.2450225507185</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.460843549183632e-07</v>
+        <v>-1.460844122613825e-07</v>
       </c>
       <c r="N12" t="n">
-        <v>-565.1279698863391</v>
+        <v>-565.1279698860859</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.003335087160977454</v>
+        <v>-0.003335087145519354</v>
       </c>
       <c r="P12" t="n">
-        <v>-317.650507719329</v>
+        <v>-317.6505077192182</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0007256797668005119</v>
+        <v>0.0007256797706754747</v>
       </c>
       <c r="R12" t="n">
-        <v>-136.245022550801</v>
+        <v>-136.2450225507185</v>
       </c>
       <c r="S12" t="n">
-        <v>1.460843549183632e-07</v>
+        <v>1.460844122613825e-07</v>
       </c>
       <c r="T12" t="n">
-        <v>-702.3421654184676</v>
+        <v>-702.342165418225</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.001018991439825603</v>
+        <v>-0.001018991478533501</v>
       </c>
     </row>
     <row r="13">
@@ -2343,52 +2343,52 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.002010446251388881</v>
+        <v>-0.002010446251387236</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0003350743752314801</v>
+        <v>-0.0003350743752312061</v>
       </c>
       <c r="H13" t="n">
-        <v>-317.6505077194432</v>
+        <v>-317.6505077191833</v>
       </c>
       <c r="I13" t="n">
-        <v>-67014.87504629603</v>
+        <v>-67014.87504624121</v>
       </c>
       <c r="J13" t="n">
-        <v>317.6505077194431</v>
+        <v>317.6505077191835</v>
       </c>
       <c r="K13" t="n">
-        <v>0.000725679620527225</v>
+        <v>0.0007256796166823266</v>
       </c>
       <c r="L13" t="n">
-        <v>286.2450225509428</v>
+        <v>286.245022550927</v>
       </c>
       <c r="M13" t="n">
-        <v>1.460828327748409e-07</v>
+        <v>1.460827712407298e-07</v>
       </c>
       <c r="N13" t="n">
-        <v>-565.1279698867711</v>
+        <v>-565.127969886584</v>
       </c>
       <c r="O13" t="n">
-        <v>0.003335086750263713</v>
+        <v>0.003335086765759374</v>
       </c>
       <c r="P13" t="n">
-        <v>-317.6505077194431</v>
+        <v>-317.6505077191835</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.000725679620527225</v>
+        <v>-0.0007256796166823266</v>
       </c>
       <c r="R13" t="n">
-        <v>-136.2450225509428</v>
+        <v>-136.245022550927</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.460828327748409e-07</v>
+        <v>-1.460827712407298e-07</v>
       </c>
       <c r="T13" t="n">
-        <v>-702.342165418886</v>
+        <v>-702.3421654189774</v>
       </c>
       <c r="U13" t="n">
-        <v>0.001018990972899647</v>
+        <v>0.001018990934334565</v>
       </c>
     </row>
     <row r="14">
@@ -2410,52 +2410,52 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0005556571193584946</v>
+        <v>0.0005556571193576412</v>
       </c>
       <c r="G14" t="n">
-        <v>9.260951989308244e-05</v>
+        <v>9.260951989294019e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>87.79382485864215</v>
+        <v>87.79382485850731</v>
       </c>
       <c r="I14" t="n">
-        <v>18521.90397861649</v>
+        <v>18521.90397858804</v>
       </c>
       <c r="J14" t="n">
-        <v>-87.79382485864198</v>
+        <v>-87.79382485850738</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0001355530381578693</v>
+        <v>0.000135553010461472</v>
       </c>
       <c r="L14" t="n">
-        <v>81.74248202023045</v>
+        <v>81.74248202001982</v>
       </c>
       <c r="M14" t="n">
-        <v>2.066094795249995e-09</v>
+        <v>2.066456408766904e-09</v>
       </c>
       <c r="N14" t="n">
-        <v>-128.1207564944852</v>
+        <v>-128.1207564938366</v>
       </c>
       <c r="O14" t="n">
-        <v>0.000697320311130005</v>
+        <v>0.0006973202224174468</v>
       </c>
       <c r="P14" t="n">
-        <v>87.79382485864198</v>
+        <v>87.79382485850738</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.0001355530381578693</v>
+        <v>-0.000135553010461472</v>
       </c>
       <c r="R14" t="n">
-        <v>-81.74248202023045</v>
+        <v>-81.74248202001982</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.066094795249995e-09</v>
+        <v>-2.066456408766904e-09</v>
       </c>
       <c r="T14" t="n">
-        <v>-362.3341356268993</v>
+        <v>-362.3341356262787</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0001159979178172107</v>
+        <v>0.0001159978403513784</v>
       </c>
     </row>
     <row r="15">
@@ -2477,52 +2477,52 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0005556571193580991</v>
+        <v>0.0005556571193578615</v>
       </c>
       <c r="G15" t="n">
-        <v>9.260951989301652e-05</v>
+        <v>9.260951989297692e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>87.79382485857967</v>
+        <v>87.79382485854211</v>
       </c>
       <c r="I15" t="n">
-        <v>18521.9039786033</v>
+        <v>18521.90397859538</v>
       </c>
       <c r="J15" t="n">
-        <v>-87.79382485857968</v>
+        <v>-87.79382485854194</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0001355529254980607</v>
+        <v>-0.0001355529532395382</v>
       </c>
       <c r="L15" t="n">
-        <v>81.74248202003355</v>
+        <v>81.74248202002072</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.067424516305483e-09</v>
+        <v>-2.06706612937424e-09</v>
       </c>
       <c r="N15" t="n">
-        <v>-128.1207564939577</v>
+        <v>-128.1207564939566</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0006973200453612369</v>
+        <v>-0.0006973201342787144</v>
       </c>
       <c r="P15" t="n">
-        <v>87.79382485857968</v>
+        <v>87.79382485854194</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0001355529254980607</v>
+        <v>0.0001355529532395382</v>
       </c>
       <c r="R15" t="n">
-        <v>-81.74248202003355</v>
+        <v>-81.74248202002072</v>
       </c>
       <c r="S15" t="n">
-        <v>2.067424516305483e-09</v>
+        <v>2.06706612937424e-09</v>
       </c>
       <c r="T15" t="n">
-        <v>-362.3341356262445</v>
+        <v>-362.3341356261658</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0001159975076271205</v>
+        <v>-0.0001159975851585185</v>
       </c>
     </row>
     <row r="16">
@@ -2544,52 +2544,52 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0005556571193581009</v>
+        <v>-0.0005556571193578649</v>
       </c>
       <c r="G16" t="n">
-        <v>-9.260951989301681e-05</v>
+        <v>-9.260951989297748e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>-87.79382485857994</v>
+        <v>-87.79382485854266</v>
       </c>
       <c r="I16" t="n">
-        <v>-18521.90397860336</v>
+        <v>-18521.9039785955</v>
       </c>
       <c r="J16" t="n">
-        <v>87.79382485858014</v>
+        <v>87.79382485854239</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0001355529252306444</v>
+        <v>0.0001355529529342408</v>
       </c>
       <c r="L16" t="n">
-        <v>168.2575179795031</v>
+        <v>168.2575179794908</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.424425771252459e-09</v>
+        <v>-2.424063477723948e-09</v>
       </c>
       <c r="N16" t="n">
-        <v>-219.528644635031</v>
+        <v>-219.5286446350328</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0006973200443666297</v>
+        <v>0.0006973201332486564</v>
       </c>
       <c r="P16" t="n">
-        <v>-87.79382485858014</v>
+        <v>-87.79382485854239</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.0001355529252306444</v>
+        <v>-0.0001355529529342408</v>
       </c>
       <c r="R16" t="n">
-        <v>-18.25751797950306</v>
+        <v>-18.25751797949079</v>
       </c>
       <c r="S16" t="n">
-        <v>2.424425771252459e-09</v>
+        <v>2.424063477723948e-09</v>
       </c>
       <c r="T16" t="n">
-        <v>-340.0164632419874</v>
+        <v>-340.0164632419128</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0001159975070172403</v>
+        <v>0.0001159975843567848</v>
       </c>
     </row>
     <row r="17">
@@ -2611,52 +2611,52 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0005556571193584964</v>
+        <v>-0.0005556571193576377</v>
       </c>
       <c r="G17" t="n">
-        <v>-9.260951989308273e-05</v>
+        <v>-9.260951989293962e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>-87.79382485864242</v>
+        <v>-87.79382485850675</v>
       </c>
       <c r="I17" t="n">
-        <v>-18521.90397861654</v>
+        <v>-18521.90397858792</v>
       </c>
       <c r="J17" t="n">
-        <v>87.79382485864244</v>
+        <v>87.79382485850692</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0001355530383835308</v>
+        <v>-0.0001355530108317436</v>
       </c>
       <c r="L17" t="n">
-        <v>168.2575179797013</v>
+        <v>168.2575179794911</v>
       </c>
       <c r="M17" t="n">
-        <v>2.42309672326968e-09</v>
+        <v>2.423457712286137e-09</v>
       </c>
       <c r="N17" t="n">
-        <v>-219.528644635564</v>
+        <v>-219.528644634917</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0006973203120697463</v>
+        <v>-0.000697320223406836</v>
       </c>
       <c r="P17" t="n">
-        <v>-87.79382485864244</v>
+        <v>-87.79382485850692</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0001355530383835308</v>
+        <v>0.0001355530108317436</v>
       </c>
       <c r="R17" t="n">
-        <v>-18.25751797970133</v>
+        <v>-18.2575179794911</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.42309672326968e-09</v>
+        <v>-2.423457712286137e-09</v>
       </c>
       <c r="T17" t="n">
-        <v>-340.0164632426458</v>
+        <v>-340.0164632420323</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0001159979182314488</v>
+        <v>-0.0001159978415836149</v>
       </c>
     </row>
     <row r="18">
@@ -2678,52 +2678,52 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0001052931328663773</v>
+        <v>-0.0001052931328663778</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.316164160829716e-05</v>
+        <v>-1.316164160829722e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>-12.47723624466571</v>
+        <v>-12.47723624466577</v>
       </c>
       <c r="I18" t="n">
-        <v>-2632.328321659432</v>
+        <v>-2632.328321659445</v>
       </c>
       <c r="J18" t="n">
-        <v>12.47723624466571</v>
+        <v>12.47723624466577</v>
       </c>
       <c r="K18" t="n">
-        <v>1.13686837721616e-12</v>
+        <v>-3.865352482534945e-12</v>
       </c>
       <c r="L18" t="n">
-        <v>9.748801765852022e-11</v>
+        <v>1.28306291372754e-10</v>
       </c>
       <c r="M18" t="n">
-        <v>5.082601006733967e-13</v>
+        <v>7.23199278240827e-13</v>
       </c>
       <c r="N18" t="n">
-        <v>0.006457521496698426</v>
+        <v>0.006457521373425529</v>
       </c>
       <c r="O18" t="n">
-        <v>16.62376087108873</v>
+        <v>16.62376087106873</v>
       </c>
       <c r="P18" t="n">
-        <v>-12.47723624466571</v>
+        <v>-12.47723624466577</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.13686837721616e-12</v>
+        <v>3.865352482534945e-12</v>
       </c>
       <c r="R18" t="n">
-        <v>-9.748801765852022e-11</v>
+        <v>-1.28306291372754e-10</v>
       </c>
       <c r="S18" t="n">
-        <v>-5.082601006733967e-13</v>
+        <v>-7.23199278240827e-13</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.006457522276602568</v>
+        <v>-0.006457522399876302</v>
       </c>
       <c r="U18" t="n">
-        <v>-16.62376087107964</v>
+        <v>-16.62376087109965</v>
       </c>
     </row>
     <row r="19">
@@ -2757,40 +2757,40 @@
         <v>26420.5486660507</v>
       </c>
       <c r="J19" t="n">
-        <v>-125.2334006770398</v>
+        <v>-125.233400677098</v>
       </c>
       <c r="K19" t="n">
-        <v>12.48925291830579</v>
+        <v>12.48925291831083</v>
       </c>
       <c r="L19" t="n">
-        <v>-475.9154605522591</v>
+        <v>-475.9154605522502</v>
       </c>
       <c r="M19" t="n">
-        <v>2.483662313930812e-05</v>
+        <v>2.48366232994117e-05</v>
       </c>
       <c r="N19" t="n">
-        <v>1903.485520698568</v>
+        <v>1903.485520698533</v>
       </c>
       <c r="O19" t="n">
-        <v>16.66630415554469</v>
+        <v>16.66630415556484</v>
       </c>
       <c r="P19" t="n">
-        <v>125.2334006770398</v>
+        <v>125.233400677098</v>
       </c>
       <c r="Q19" t="n">
-        <v>-12.48925291830579</v>
+        <v>-12.48925291831083</v>
       </c>
       <c r="R19" t="n">
-        <v>475.9154605522591</v>
+        <v>475.9154605522502</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.483662313930812e-05</v>
+        <v>-2.48366232994117e-05</v>
       </c>
       <c r="T19" t="n">
-        <v>1903.838163719504</v>
+        <v>1903.838163719469</v>
       </c>
       <c r="U19" t="n">
-        <v>83.24771919090161</v>
+        <v>83.24771919092179</v>
       </c>
     </row>
     <row r="20">
@@ -2812,52 +2812,52 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001052931328663773</v>
+        <v>0.0001052931328663774</v>
       </c>
       <c r="G20" t="n">
-        <v>1.316164160829716e-05</v>
+        <v>1.316164160829718e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>12.4772362446657</v>
+        <v>12.47723624466572</v>
       </c>
       <c r="I20" t="n">
-        <v>2632.328321659431</v>
+        <v>2632.328321659435</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.4772362446657</v>
+        <v>-12.47723624466572</v>
       </c>
       <c r="K20" t="n">
-        <v>-99.99999999999892</v>
+        <v>-100.000000000004</v>
       </c>
       <c r="L20" t="n">
-        <v>9.704281822564553e-11</v>
+        <v>1.285480819013252e-10</v>
       </c>
       <c r="M20" t="n">
-        <v>5.091482790930968e-13</v>
+        <v>7.238654120556021e-13</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.006457522274820882</v>
+        <v>-0.006457522400840577</v>
       </c>
       <c r="O20" t="n">
-        <v>-83.3756791690565</v>
+        <v>-83.37567916907628</v>
       </c>
       <c r="P20" t="n">
-        <v>12.4772362446657</v>
+        <v>12.47723624466572</v>
       </c>
       <c r="Q20" t="n">
-        <v>-100.0000000000011</v>
+        <v>-99.99999999999602</v>
       </c>
       <c r="R20" t="n">
-        <v>-9.704281822564553e-11</v>
+        <v>-1.285480819013252e-10</v>
       </c>
       <c r="S20" t="n">
-        <v>-5.091482790930968e-13</v>
+        <v>-7.238654120556021e-13</v>
       </c>
       <c r="T20" t="n">
-        <v>0.00645752149847878</v>
+        <v>0.006457521372455919</v>
       </c>
       <c r="U20" t="n">
-        <v>83.37567916906491</v>
+        <v>83.37567916904467</v>
       </c>
     </row>
     <row r="21">
@@ -2891,40 +2891,40 @@
         <v>26420.5486660618</v>
       </c>
       <c r="J21" t="n">
-        <v>-125.2334006771562</v>
+        <v>-125.233400677098</v>
       </c>
       <c r="K21" t="n">
-        <v>12.48925291830772</v>
+        <v>12.48925291830278</v>
       </c>
       <c r="L21" t="n">
-        <v>-475.9154605524574</v>
+        <v>-475.9154605525324</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.483662214261725e-05</v>
+        <v>-2.483662198250748e-05</v>
       </c>
       <c r="N21" t="n">
-        <v>1903.838163720297</v>
+        <v>1903.838163720598</v>
       </c>
       <c r="O21" t="n">
-        <v>83.24771919090941</v>
+        <v>83.24771919088963</v>
       </c>
       <c r="P21" t="n">
-        <v>125.2334006771562</v>
+        <v>125.233400677098</v>
       </c>
       <c r="Q21" t="n">
-        <v>-12.48925291830772</v>
+        <v>-12.48925291830278</v>
       </c>
       <c r="R21" t="n">
-        <v>475.9154605524574</v>
+        <v>475.9154605525324</v>
       </c>
       <c r="S21" t="n">
-        <v>2.483662214261725e-05</v>
+        <v>2.483662198250748e-05</v>
       </c>
       <c r="T21" t="n">
-        <v>1903.485520699361</v>
+        <v>1903.485520699661</v>
       </c>
       <c r="U21" t="n">
-        <v>16.66630415555239</v>
+        <v>16.6663041555326</v>
       </c>
     </row>
     <row r="22">
@@ -2946,52 +2946,52 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0001054962997791663</v>
+        <v>-0.0001054962997791679</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.318703747239578e-05</v>
+        <v>-1.318703747239599e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>-12.5013115238312</v>
+        <v>-12.5013115238314</v>
       </c>
       <c r="I22" t="n">
-        <v>-2637.407494479156</v>
+        <v>-2637.407494479197</v>
       </c>
       <c r="J22" t="n">
-        <v>12.5013115238312</v>
+        <v>12.5013115238314</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.433786671143025e-12</v>
+        <v>-2.592059900052845e-11</v>
       </c>
       <c r="L22" t="n">
-        <v>1.079225597777622e-10</v>
+        <v>1.251894328219844e-10</v>
       </c>
       <c r="M22" t="n">
-        <v>5.864198016070077e-13</v>
+        <v>7.758238496080594e-13</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.001416633671542655</v>
+        <v>-0.001416633740610715</v>
       </c>
       <c r="O22" t="n">
-        <v>16.65564080097101</v>
+        <v>16.65564080088552</v>
       </c>
       <c r="P22" t="n">
-        <v>-12.5013115238312</v>
+        <v>-12.5013115238314</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.433786671143025e-12</v>
+        <v>2.592059900052845e-11</v>
       </c>
       <c r="R22" t="n">
-        <v>-1.079225597777622e-10</v>
+        <v>-1.251894328219844e-10</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.864198016070077e-13</v>
+        <v>-7.758238496080594e-13</v>
       </c>
       <c r="T22" t="n">
-        <v>0.001416632808162177</v>
+        <v>0.001416632739095252</v>
       </c>
       <c r="U22" t="n">
-        <v>-16.65564080100648</v>
+        <v>-16.65564080109243</v>
       </c>
     </row>
     <row r="23">
@@ -3013,52 +3013,52 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.001042184203999597</v>
+        <v>0.001042184204001373</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001302730254999496</v>
+        <v>0.0001302730255001716</v>
       </c>
       <c r="H23" t="n">
-        <v>123.4988281739522</v>
+        <v>123.4988281741627</v>
       </c>
       <c r="I23" t="n">
-        <v>26054.60509998991</v>
+        <v>26054.60510003432</v>
       </c>
       <c r="J23" t="n">
-        <v>-123.4988281739643</v>
+        <v>-123.4988281741971</v>
       </c>
       <c r="K23" t="n">
-        <v>12.49725030896388</v>
+        <v>12.49725030898538</v>
       </c>
       <c r="L23" t="n">
-        <v>-394.0773917252902</v>
+        <v>-394.0773917252354</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.448588832704337e-06</v>
+        <v>-5.448588741532367e-06</v>
       </c>
       <c r="N23" t="n">
-        <v>1576.857887959274</v>
+        <v>1576.857887959055</v>
       </c>
       <c r="O23" t="n">
-        <v>16.65572241132731</v>
+        <v>16.65572241141295</v>
       </c>
       <c r="P23" t="n">
-        <v>123.4988281739643</v>
+        <v>123.4988281741971</v>
       </c>
       <c r="Q23" t="n">
-        <v>-12.49725030896388</v>
+        <v>-12.49725030898538</v>
       </c>
       <c r="R23" t="n">
-        <v>394.0773917252902</v>
+        <v>394.0773917252354</v>
       </c>
       <c r="S23" t="n">
-        <v>5.448588832704337e-06</v>
+        <v>5.448588741532367e-06</v>
       </c>
       <c r="T23" t="n">
-        <v>1575.761245843047</v>
+        <v>1575.761245842828</v>
       </c>
       <c r="U23" t="n">
-        <v>83.32228006038376</v>
+        <v>83.32228006047011</v>
       </c>
     </row>
     <row r="24">
@@ -3080,7 +3080,7 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0001054962997791678</v>
+        <v>0.0001054962997791679</v>
       </c>
       <c r="G24" t="n">
         <v>1.318703747239598e-05</v>
@@ -3089,43 +3089,43 @@
         <v>12.50131152383139</v>
       </c>
       <c r="I24" t="n">
-        <v>2637.407494479196</v>
+        <v>2637.407494479197</v>
       </c>
       <c r="J24" t="n">
         <v>-12.50131152383139</v>
       </c>
       <c r="K24" t="n">
-        <v>-100.0000000000048</v>
+        <v>-100.0000000000263</v>
       </c>
       <c r="L24" t="n">
-        <v>1.074449418325685e-10</v>
+        <v>1.254654333985444e-10</v>
       </c>
       <c r="M24" t="n">
-        <v>5.864198016070077e-13</v>
+        <v>7.751577157932843e-13</v>
       </c>
       <c r="N24" t="n">
-        <v>0.001416632810069984</v>
+        <v>0.001416632737978864</v>
       </c>
       <c r="O24" t="n">
-        <v>-83.32241648528483</v>
+        <v>-83.32241648536987</v>
       </c>
       <c r="P24" t="n">
         <v>12.50131152383139</v>
       </c>
       <c r="Q24" t="n">
-        <v>-99.99999999999523</v>
+        <v>-99.99999999997374</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.074449418325685e-10</v>
+        <v>-1.254654333985444e-10</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.864198016070077e-13</v>
+        <v>-7.751577157932843e-13</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.001416633669628631</v>
+        <v>-0.00141663374170233</v>
       </c>
       <c r="U24" t="n">
-        <v>83.32241648524663</v>
+        <v>83.32241648516023</v>
       </c>
     </row>
     <row r="25">
@@ -3147,52 +3147,52 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.001042184204003149</v>
+        <v>0.001042184204001373</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001302730255003937</v>
+        <v>0.0001302730255001716</v>
       </c>
       <c r="H25" t="n">
-        <v>123.4988281743732</v>
+        <v>123.4988281741627</v>
       </c>
       <c r="I25" t="n">
-        <v>26054.60510007873</v>
+        <v>26054.60510003432</v>
       </c>
       <c r="J25" t="n">
-        <v>-123.4988281744299</v>
+        <v>-123.4988281741971</v>
       </c>
       <c r="K25" t="n">
-        <v>12.49725030895394</v>
+        <v>12.49725030893287</v>
       </c>
       <c r="L25" t="n">
-        <v>-394.0773917255186</v>
+        <v>-394.0773917255378</v>
       </c>
       <c r="M25" t="n">
-        <v>5.448589935378031e-06</v>
+        <v>5.448590026519767e-06</v>
       </c>
       <c r="N25" t="n">
-        <v>1575.761245843961</v>
+        <v>1575.761245844037</v>
       </c>
       <c r="O25" t="n">
-        <v>83.32228006034393</v>
+        <v>83.32228006026035</v>
       </c>
       <c r="P25" t="n">
-        <v>123.4988281744299</v>
+        <v>123.4988281741971</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.49725030895394</v>
+        <v>-12.49725030893287</v>
       </c>
       <c r="R25" t="n">
-        <v>394.0773917255186</v>
+        <v>394.0773917255378</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.448589935378031e-06</v>
+        <v>-5.448590026519767e-06</v>
       </c>
       <c r="T25" t="n">
-        <v>1576.857887960188</v>
+        <v>1576.857887960265</v>
       </c>
       <c r="U25" t="n">
-        <v>16.6557224112876</v>
+        <v>16.65572241120256</v>
       </c>
     </row>
     <row r="26">
@@ -3214,52 +3214,52 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0001054548126048011</v>
+        <v>-0.0001054548126048016</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.318185157560014e-05</v>
+        <v>-1.318185157560019e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>-12.49639529366893</v>
+        <v>-12.49639529366899</v>
       </c>
       <c r="I26" t="n">
-        <v>-2636.370315120028</v>
+        <v>-2636.370315120039</v>
       </c>
       <c r="J26" t="n">
-        <v>12.49639529366894</v>
+        <v>12.49639529366899</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.70530256582424e-11</v>
+        <v>-4.843059286940843e-11</v>
       </c>
       <c r="L26" t="n">
-        <v>9.179013105153899e-11</v>
+        <v>7.886364625849396e-11</v>
       </c>
       <c r="M26" t="n">
-        <v>6.076250613773482e-13</v>
+        <v>4.087841176669826e-13</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0003204382049224463</v>
+        <v>0.0003204382566711034</v>
       </c>
       <c r="O26" t="n">
-        <v>16.65569270651849</v>
+        <v>16.65569270639389</v>
       </c>
       <c r="P26" t="n">
-        <v>-12.49639529366894</v>
+        <v>-12.49639529366899</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.70530256582424e-11</v>
+        <v>4.843059286940843e-11</v>
       </c>
       <c r="R26" t="n">
-        <v>-9.179013105153899e-11</v>
+        <v>-7.886364625849396e-11</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.076250613773482e-13</v>
+        <v>-4.087841176669826e-13</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0003204389392434948</v>
+        <v>-0.0003204388875802733</v>
       </c>
       <c r="U26" t="n">
-        <v>-16.65569270665674</v>
+        <v>-16.65569270678225</v>
       </c>
     </row>
     <row r="27">
@@ -3296,37 +3296,37 @@
         <v>-132.0124954287894</v>
       </c>
       <c r="K27" t="n">
-        <v>12.49725652636022</v>
+        <v>12.49725652639148</v>
       </c>
       <c r="L27" t="n">
-        <v>-229.856682860657</v>
+        <v>-229.8566828605958</v>
       </c>
       <c r="M27" t="n">
-        <v>1.232456515734565e-06</v>
+        <v>1.232456451699434e-06</v>
       </c>
       <c r="N27" t="n">
-        <v>916.9826528317536</v>
+        <v>916.9826528315087</v>
       </c>
       <c r="O27" t="n">
-        <v>16.65569284181208</v>
+        <v>16.65569284193676</v>
       </c>
       <c r="P27" t="n">
         <v>132.0124954287894</v>
       </c>
       <c r="Q27" t="n">
-        <v>-12.49725652636022</v>
+        <v>-12.49725652639148</v>
       </c>
       <c r="R27" t="n">
-        <v>229.856682860657</v>
+        <v>229.8566828605958</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.232456515734565e-06</v>
+        <v>-1.232456451699434e-06</v>
       </c>
       <c r="T27" t="n">
-        <v>921.8708100535018</v>
+        <v>921.8708100532576</v>
       </c>
       <c r="U27" t="n">
-        <v>83.32235936906969</v>
+        <v>83.32235936919508</v>
       </c>
     </row>
     <row r="28">
@@ -3348,52 +3348,52 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0001054548126047953</v>
+        <v>0.000105454812604793</v>
       </c>
       <c r="G28" t="n">
-        <v>1.318185157559941e-05</v>
+        <v>1.318185157559913e-05</v>
       </c>
       <c r="H28" t="n">
-        <v>12.49639529366824</v>
+        <v>12.49639529366798</v>
       </c>
       <c r="I28" t="n">
-        <v>2636.370315119882</v>
+        <v>2636.370315119826</v>
       </c>
       <c r="J28" t="n">
-        <v>-12.49639529366824</v>
+        <v>-12.49639529366798</v>
       </c>
       <c r="K28" t="n">
-        <v>-100.0000000000168</v>
+        <v>-100.0000000000475</v>
       </c>
       <c r="L28" t="n">
-        <v>9.171041703837091e-11</v>
+        <v>7.919405605740729e-11</v>
       </c>
       <c r="M28" t="n">
-        <v>6.078471059822732e-13</v>
+        <v>4.084510507595951e-13</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.000320438938936185</v>
+        <v>-0.0003204388888398558</v>
       </c>
       <c r="O28" t="n">
-        <v>-83.32235951273137</v>
+        <v>-83.32235951285415</v>
       </c>
       <c r="P28" t="n">
-        <v>12.49639529366824</v>
+        <v>12.49639529366798</v>
       </c>
       <c r="Q28" t="n">
-        <v>-99.99999999998317</v>
+        <v>-99.99999999995248</v>
       </c>
       <c r="R28" t="n">
-        <v>-9.171041703837091e-11</v>
+        <v>-7.919405605740729e-11</v>
       </c>
       <c r="S28" t="n">
-        <v>-6.078471059822732e-13</v>
+        <v>-4.084510507595951e-13</v>
       </c>
       <c r="T28" t="n">
-        <v>0.0003204382052528487</v>
+        <v>0.0003204382552865191</v>
       </c>
       <c r="U28" t="n">
-        <v>83.32235951259676</v>
+        <v>83.32235951247489</v>
       </c>
     </row>
     <row r="29">
@@ -3415,52 +3415,52 @@
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>0.001114029497284008</v>
+        <v>0.001114029497285784</v>
       </c>
       <c r="G29" t="n">
-        <v>0.000139253687160501</v>
+        <v>0.0001392536871607231</v>
       </c>
       <c r="H29" t="n">
-        <v>132.012495428155</v>
+        <v>132.0124954283655</v>
       </c>
       <c r="I29" t="n">
-        <v>27850.73743210021</v>
+        <v>27850.73743214461</v>
       </c>
       <c r="J29" t="n">
-        <v>-132.0124954280909</v>
+        <v>-132.0124954283237</v>
       </c>
       <c r="K29" t="n">
-        <v>12.49725652632724</v>
+        <v>12.49725652629611</v>
       </c>
       <c r="L29" t="n">
-        <v>-229.8566828608935</v>
+        <v>-229.8566828607552</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.232455577255556e-06</v>
+        <v>-1.232455641335499e-06</v>
       </c>
       <c r="N29" t="n">
-        <v>921.8708100544479</v>
+        <v>921.870810053895</v>
       </c>
       <c r="O29" t="n">
-        <v>83.32235936893775</v>
+        <v>83.32235936881273</v>
       </c>
       <c r="P29" t="n">
-        <v>132.0124954280909</v>
+        <v>132.0124954283237</v>
       </c>
       <c r="Q29" t="n">
-        <v>-12.49725652632724</v>
+        <v>-12.49725652629611</v>
       </c>
       <c r="R29" t="n">
-        <v>229.8566828608935</v>
+        <v>229.8566828607552</v>
       </c>
       <c r="S29" t="n">
-        <v>1.232455577255556e-06</v>
+        <v>1.232455641335499e-06</v>
       </c>
       <c r="T29" t="n">
-        <v>916.9826528326996</v>
+        <v>916.9826528321462</v>
       </c>
       <c r="U29" t="n">
-        <v>16.65569284168014</v>
+        <v>16.65569284155616</v>
       </c>
     </row>
     <row r="30">
@@ -3482,52 +3482,52 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0001054632224549718</v>
+        <v>-0.0001054632224549705</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.318290280687148e-05</v>
+        <v>-1.318290280687131e-05</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.49739186091416</v>
+        <v>-12.49739186091401</v>
       </c>
       <c r="I30" t="n">
-        <v>-2636.580561374296</v>
+        <v>-2636.580561374263</v>
       </c>
       <c r="J30" t="n">
-        <v>12.49739186091416</v>
+        <v>12.49739186091401</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.616129783447832e-11</v>
+        <v>-2.91038304567337e-11</v>
       </c>
       <c r="L30" t="n">
-        <v>5.1213033813724e-11</v>
+        <v>3.185670624457392e-11</v>
       </c>
       <c r="M30" t="n">
-        <v>4.203304371230843e-13</v>
+        <v>7.083222897108499e-14</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.0001155534819119453</v>
+        <v>-0.000115553404494969</v>
       </c>
       <c r="O30" t="n">
-        <v>16.65569190032693</v>
+        <v>16.65569190043516</v>
       </c>
       <c r="P30" t="n">
-        <v>-12.49739186091416</v>
+        <v>-12.49739186091401</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.616129783447832e-11</v>
+        <v>2.91038304567337e-11</v>
       </c>
       <c r="R30" t="n">
-        <v>-5.1213033813724e-11</v>
+        <v>-3.185670624457392e-11</v>
       </c>
       <c r="S30" t="n">
-        <v>-4.203304371230843e-13</v>
+        <v>-7.083222897108499e-14</v>
       </c>
       <c r="T30" t="n">
-        <v>0.0001155530722067866</v>
+        <v>0.0001155531496422071</v>
       </c>
       <c r="U30" t="n">
-        <v>-16.65569190077713</v>
+        <v>-16.65569190066799</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>-81.74248202005401</v>
       </c>
       <c r="K31" t="n">
-        <v>12.49725630798878</v>
+        <v>12.49725630796159</v>
       </c>
       <c r="L31" t="n">
-        <v>-87.79382485852895</v>
+        <v>-87.79382485851036</v>
       </c>
       <c r="M31" t="n">
-        <v>-4.444354194820428e-07</v>
+        <v>-4.444355165871917e-07</v>
       </c>
       <c r="N31" t="n">
-        <v>362.3341356262432</v>
+        <v>362.3341356261689</v>
       </c>
       <c r="O31" t="n">
-        <v>16.65569189871105</v>
+        <v>16.65569189860274</v>
       </c>
       <c r="P31" t="n">
         <v>81.74248202005401</v>
       </c>
       <c r="Q31" t="n">
-        <v>-12.49725630798878</v>
+        <v>-12.49725630796159</v>
       </c>
       <c r="R31" t="n">
-        <v>87.79382485852895</v>
+        <v>87.79382485851036</v>
       </c>
       <c r="S31" t="n">
-        <v>4.444354194820428e-07</v>
+        <v>4.444355165871917e-07</v>
       </c>
       <c r="T31" t="n">
-        <v>340.0164632419883</v>
+        <v>340.0164632419138</v>
       </c>
       <c r="U31" t="n">
-        <v>83.32235856519915</v>
+        <v>83.32235856509004</v>
       </c>
     </row>
     <row r="32">
@@ -3616,52 +3616,52 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0001054632224549722</v>
+        <v>0.000105463222454975</v>
       </c>
       <c r="G32" t="n">
-        <v>1.318290280687152e-05</v>
+        <v>1.318290280687187e-05</v>
       </c>
       <c r="H32" t="n">
-        <v>12.4973918609142</v>
+        <v>12.49739186091453</v>
       </c>
       <c r="I32" t="n">
-        <v>2636.580561374304</v>
+        <v>2636.580561374374</v>
       </c>
       <c r="J32" t="n">
-        <v>-12.4973918609142</v>
+        <v>-12.49739186091453</v>
       </c>
       <c r="K32" t="n">
-        <v>-100.0000000000568</v>
+        <v>-100.0000000000293</v>
       </c>
       <c r="L32" t="n">
-        <v>5.138911518542955e-11</v>
+        <v>3.218251569913049e-11</v>
       </c>
       <c r="M32" t="n">
-        <v>4.23938661953116e-13</v>
+        <v>7.255307465925398e-14</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0001155530715442055</v>
+        <v>0.0001155531482243991</v>
       </c>
       <c r="O32" t="n">
-        <v>-83.32235856762449</v>
+        <v>-83.32235856751535</v>
       </c>
       <c r="P32" t="n">
-        <v>12.4973918609142</v>
+        <v>12.49739186091453</v>
       </c>
       <c r="Q32" t="n">
-        <v>-99.99999999994316</v>
+        <v>-99.99999999997067</v>
       </c>
       <c r="R32" t="n">
-        <v>-5.138911518542955e-11</v>
+        <v>-3.218251569913049e-11</v>
       </c>
       <c r="S32" t="n">
-        <v>-4.23938661953116e-13</v>
+        <v>-7.255307465925398e-14</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.0001155534826580151</v>
+        <v>-0.0001155534056854128</v>
       </c>
       <c r="U32" t="n">
-        <v>83.32235856716974</v>
+        <v>83.32235856727888</v>
       </c>
     </row>
     <row r="33">
@@ -3683,52 +3683,52 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>0.000689809974856459</v>
+        <v>0.0006898099748582354</v>
       </c>
       <c r="G33" t="n">
-        <v>8.622624685705738e-05</v>
+        <v>8.622624685727942e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>81.7424820204904</v>
+        <v>81.74248202070089</v>
       </c>
       <c r="I33" t="n">
-        <v>17245.24937141148</v>
+        <v>17245.24937145588</v>
       </c>
       <c r="J33" t="n">
-        <v>-81.74248202051967</v>
+        <v>-81.7424820207525</v>
       </c>
       <c r="K33" t="n">
-        <v>12.49725630787598</v>
+        <v>12.49725630790358</v>
       </c>
       <c r="L33" t="n">
-        <v>-87.793824858693</v>
+        <v>-87.79382485853831</v>
       </c>
       <c r="M33" t="n">
-        <v>4.44435942673907e-07</v>
+        <v>4.444358450432963e-07</v>
       </c>
       <c r="N33" t="n">
-        <v>340.0164632426455</v>
+        <v>340.0164632420261</v>
       </c>
       <c r="O33" t="n">
-        <v>83.32235856474811</v>
+        <v>83.32235856485785</v>
       </c>
       <c r="P33" t="n">
-        <v>81.74248202051967</v>
+        <v>81.7424820207525</v>
       </c>
       <c r="Q33" t="n">
-        <v>-12.49725630787598</v>
+        <v>-12.49725630790358</v>
       </c>
       <c r="R33" t="n">
-        <v>87.793824858693</v>
+        <v>87.79382485853831</v>
       </c>
       <c r="S33" t="n">
-        <v>-4.44435942673907e-07</v>
+        <v>-4.444358450432963e-07</v>
       </c>
       <c r="T33" t="n">
-        <v>362.3341356268984</v>
+        <v>362.3341356262804</v>
       </c>
       <c r="U33" t="n">
-        <v>16.65569189825973</v>
+        <v>16.65569189837078</v>
       </c>
     </row>
   </sheetData>
@@ -3991,16 +3991,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007516730126564649</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001252788354427442</v>
+        <v>0.001252788354427215</v>
       </c>
       <c r="H2" t="n">
-        <v>1187.643359997215</v>
+        <v>1187.643359997</v>
       </c>
       <c r="I2" t="n">
-        <v>250557.6708854883</v>
+        <v>250557.670885443</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -4021,22 +4021,22 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.595119805279023</v>
+        <v>3.595119805279563</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.264656576807992e-05</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007516730126564649</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="S2" t="n">
-        <v>-5.81758716827277e-06</v>
+        <v>-5.817587131184721e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5733905572098467</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01497636114528572</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -4057,58 +4057,58 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007516730126564649</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.264656576807992e-05</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="AD2" t="n">
-        <v>-3.595119805279023</v>
+        <v>-3.595119805279563</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.01497636114528572</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5733905572098467</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="AG2" t="n">
-        <v>5.81758716827277e-06</v>
+        <v>5.817587131184721e-06</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1187.643359997215</v>
+        <v>-1187.643359997</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.008681138384937864</v>
+        <v>-0.008681138355291034</v>
       </c>
       <c r="AJ2" t="n">
-        <v>462.4872063002059</v>
+        <v>462.4872063002725</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.04262502787504397</v>
+        <v>-0.04262502787522724</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1811.770631235904</v>
+        <v>-1811.770631236171</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.03034842965933544</v>
+        <v>-0.03034842954294979</v>
       </c>
       <c r="AN2" t="n">
-        <v>1187.643359997215</v>
+        <v>1187.643359997</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.008681138384937864</v>
+        <v>0.008681138355291034</v>
       </c>
       <c r="AP2" t="n">
-        <v>-462.4872063002059</v>
+        <v>-462.4872063002725</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.04262502787504397</v>
+        <v>0.04262502787522724</v>
       </c>
       <c r="AR2" t="n">
-        <v>-963.1526065653311</v>
+        <v>-963.1526065654646</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.02173840065029174</v>
+        <v>-0.02173840058879641</v>
       </c>
     </row>
     <row r="3">
@@ -4130,16 +4130,16 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007516730126563812</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001252788354427302</v>
+        <v>0.001252788354427168</v>
       </c>
       <c r="H3" t="n">
-        <v>1187.643359997082</v>
+        <v>1187.643359996955</v>
       </c>
       <c r="I3" t="n">
-        <v>250557.6708854604</v>
+        <v>250557.6708854335</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -4160,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.595119805277716</v>
+        <v>3.595119805277692</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.264656709829736e-05</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007516730126563812</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="S3" t="n">
-        <v>5.817587402268885e-06</v>
+        <v>5.817587439357226e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5733905572096085</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0149763611449562</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -4196,58 +4196,58 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007516730126563812</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="AC3" t="n">
-        <v>-5.264656709829736e-05</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="AD3" t="n">
-        <v>-3.595119805277716</v>
+        <v>-3.595119805277692</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.0149763611449562</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5733905572096085</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="AG3" t="n">
-        <v>-5.817587402268885e-06</v>
+        <v>-5.817587439357226e-06</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1187.643359997083</v>
+        <v>-1187.643359996955</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.008681138539901042</v>
+        <v>0.00868113856954778</v>
       </c>
       <c r="AJ3" t="n">
-        <v>462.4872063000596</v>
+        <v>462.4872063000618</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0426250278741061</v>
+        <v>0.04262502787392255</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1811.770631235289</v>
+        <v>-1811.770631235287</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0303484302973821</v>
+        <v>0.03034843041376769</v>
       </c>
       <c r="AN3" t="n">
-        <v>1187.643359997083</v>
+        <v>1187.643359996955</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.008681138539901042</v>
+        <v>-0.00868113856954778</v>
       </c>
       <c r="AP3" t="n">
-        <v>-462.4872063000596</v>
+        <v>-462.4872063000618</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.0426250278741061</v>
+        <v>-0.04262502787392255</v>
       </c>
       <c r="AR3" t="n">
-        <v>-963.1526065650683</v>
+        <v>-963.1526065650828</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.02173840094202415</v>
+        <v>0.021738401003519</v>
       </c>
     </row>
     <row r="4">
@@ -4269,16 +4269,16 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.007516730126563806</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001252788354427301</v>
+        <v>-0.00125278835442717</v>
       </c>
       <c r="H4" t="n">
-        <v>-1187.643359997081</v>
+        <v>-1187.643359996957</v>
       </c>
       <c r="I4" t="n">
-        <v>-250557.6708854602</v>
+        <v>-250557.6708854339</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.596176627224358</v>
+        <v>3.596176627224334</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.264656709531542e-05</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.007516730126563806</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="S4" t="n">
-        <v>-5.817587401731315e-06</v>
+        <v>-5.817587439646455e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5737082536248662</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04500689564365364</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -4335,58 +4335,58 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.007516730126563806</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.264656709531542e-05</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3.596176627224358</v>
+        <v>-3.596176627224334</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.04500689564365364</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5737082536248662</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.817587401731315e-06</v>
+        <v>5.817587439646455e-06</v>
       </c>
       <c r="AH4" t="n">
-        <v>1187.643359997082</v>
+        <v>1187.643359996957</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.008681138539563298</v>
+        <v>-0.008681138569743792</v>
       </c>
       <c r="AJ4" t="n">
-        <v>537.5127936996073</v>
+        <v>537.5127936996093</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.1280965491396296</v>
+        <v>-0.1280965491398132</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1887.082488781223</v>
+        <v>-1887.082488781221</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.03034843029597107</v>
+        <v>-0.03034843041456974</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1187.643359997082</v>
+        <v>-1187.643359996957</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.008681138539563298</v>
+        <v>0.008681138569743792</v>
       </c>
       <c r="AP4" t="n">
-        <v>-387.5127936996073</v>
+        <v>-387.5127936996093</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.1280965491396296</v>
+        <v>0.1280965491398132</v>
       </c>
       <c r="AR4" t="n">
-        <v>-887.9942734164206</v>
+        <v>-887.9942734164347</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0.02173840094140872</v>
+        <v>-0.02173840100389299</v>
       </c>
     </row>
     <row r="5">
@@ -4408,16 +4408,16 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.007516730126564661</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.001252788354427443</v>
+        <v>-0.001252788354427215</v>
       </c>
       <c r="H5" t="n">
-        <v>-1187.643359997216</v>
+        <v>-1187.643359997</v>
       </c>
       <c r="I5" t="n">
-        <v>-250557.6708854887</v>
+        <v>-250557.670885443</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.596176627225665</v>
+        <v>3.596176627226205</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.264656577106183e-05</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.007516730126564661</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="S5" t="n">
-        <v>5.817587168809183e-06</v>
+        <v>5.817587130890855e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5737082536251048</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0450068956433242</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -4474,58 +4474,58 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.007516730126564661</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="AC5" t="n">
-        <v>-5.264656577106183e-05</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3.596176627225665</v>
+        <v>-3.596176627226205</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.0450068956433242</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.5737082536251048</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="AG5" t="n">
-        <v>-5.817587168809183e-06</v>
+        <v>-5.817587130890855e-06</v>
       </c>
       <c r="AH5" t="n">
-        <v>1187.643359997217</v>
+        <v>1187.643359997</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.008681138385276456</v>
+        <v>0.008681138355098365</v>
       </c>
       <c r="AJ5" t="n">
-        <v>537.5127936997534</v>
+        <v>537.51279369982</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1280965491386919</v>
+        <v>0.1280965491385087</v>
       </c>
       <c r="AL5" t="n">
-        <v>-1887.082488781838</v>
+        <v>-1887.082488782104</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.03034842966074816</v>
+        <v>0.03034842954215432</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1187.643359997217</v>
+        <v>-1187.643359997</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.008681138385276456</v>
+        <v>-0.008681138355098365</v>
       </c>
       <c r="AP5" t="n">
-        <v>-387.5127936997534</v>
+        <v>-387.51279369982</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.1280965491386919</v>
+        <v>-0.1280965491385087</v>
       </c>
       <c r="AR5" t="n">
-        <v>-887.9942734166825</v>
+        <v>-887.9942734168162</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.02173840065091057</v>
+        <v>0.02173840058843586</v>
       </c>
     </row>
     <row r="6">
@@ -4547,124 +4547,124 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004504606958511741</v>
+        <v>0.004504606958510098</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0007507678264186235</v>
+        <v>0.0007507678264183497</v>
       </c>
       <c r="H6" t="n">
-        <v>711.7278994448551</v>
+        <v>711.7278994445956</v>
       </c>
       <c r="I6" t="n">
-        <v>150153.5652837247</v>
+        <v>150153.5652836699</v>
       </c>
       <c r="J6" t="n">
-        <v>3.595119805279023</v>
+        <v>3.595119805279563</v>
       </c>
       <c r="K6" t="n">
-        <v>5.264656576807992e-05</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007516730126564649</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.81758716827277e-06</v>
+        <v>-5.817587131184721e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5733905572098467</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01497636114528572</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="P6" t="n">
-        <v>8.113133295380457</v>
+        <v>8.113133295381624</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.274814816710414e-05</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01202133708507639</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="S6" t="n">
-        <v>1.276246291459122e-06</v>
+        <v>1.276246312356512e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4768655535134355</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01500508180312803</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007516730126564649</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="W6" t="n">
-        <v>5.264656576807992e-05</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.595119805279023</v>
+        <v>-3.595119805279563</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01497636114528572</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5733905572098467</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.81758716827277e-06</v>
+        <v>5.817587131184721e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01202133708507639</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.274814816710414e-05</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="AD6" t="n">
-        <v>-8.113133295380457</v>
+        <v>-8.113133295381624</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.01500508180312803</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.4768655535134355</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="AG6" t="n">
-        <v>-1.276246291459122e-06</v>
+        <v>-1.276246312356512e-06</v>
       </c>
       <c r="AH6" t="n">
-        <v>-711.7278994448552</v>
+        <v>-711.7278994445956</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.00333553525708279</v>
+        <v>0.003335535281722257</v>
       </c>
       <c r="AJ6" t="n">
-        <v>337.2538056231251</v>
+        <v>337.2538056231967</v>
       </c>
       <c r="AK6" t="n">
-        <v>-8.17434107819523e-05</v>
+        <v>-8.174341103647093e-05</v>
       </c>
       <c r="AL6" t="n">
-        <v>-940.3329141340305</v>
+        <v>-940.3329141341959</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.01525604253144997</v>
+        <v>0.01525604259338728</v>
       </c>
       <c r="AN6" t="n">
-        <v>711.7278994448552</v>
+        <v>711.7278994445956</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.00333553525708279</v>
+        <v>-0.003335535281722257</v>
       </c>
       <c r="AP6" t="n">
-        <v>-337.2538056231251</v>
+        <v>-337.2538056231967</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.17434107819523e-05</v>
+        <v>8.174341103647093e-05</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1083.189919604719</v>
+        <v>-1083.189919604984</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.004757169011046773</v>
+        <v>0.004757169096946262</v>
       </c>
     </row>
     <row r="7">
@@ -4686,124 +4686,124 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004504606958510925</v>
+        <v>0.004504606958509978</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007507678264184874</v>
+        <v>0.0007507678264183296</v>
       </c>
       <c r="H7" t="n">
-        <v>711.7278994447261</v>
+        <v>711.7278994445765</v>
       </c>
       <c r="I7" t="n">
-        <v>150153.5652836975</v>
+        <v>150153.5652836659</v>
       </c>
       <c r="J7" t="n">
-        <v>3.595119805277716</v>
+        <v>3.595119805277692</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.264656709829736e-05</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007516730126563812</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="M7" t="n">
-        <v>5.817587402268885e-06</v>
+        <v>5.817587439357226e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5733905572096085</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0149763611449562</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="P7" t="n">
-        <v>8.11313329537693</v>
+        <v>8.113133295376661</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.274815161206213e-05</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01202133708507474</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.276246032599108e-06</v>
+        <v>-1.276246011702428e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4768655535131607</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.01500508180225687</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="V7" t="n">
-        <v>0.007516730126563812</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="W7" t="n">
-        <v>-5.264656709829736e-05</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.595119805277716</v>
+        <v>-3.595119805277692</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.0149763611449562</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5733905572096085</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="AA7" t="n">
-        <v>-5.817587402268885e-06</v>
+        <v>-5.817587439357226e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01202133708507474</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.274815161206213e-05</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="AD7" t="n">
-        <v>-8.11313329537693</v>
+        <v>-8.113133295376661</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.01500508180225687</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.4768655535131607</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.276246032599108e-06</v>
+        <v>1.276246011702428e-06</v>
       </c>
       <c r="AH7" t="n">
-        <v>-711.7278994447263</v>
+        <v>-711.7278994445767</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.003335535100160325</v>
+        <v>-0.003335535075520275</v>
       </c>
       <c r="AJ7" t="n">
-        <v>337.2538056229571</v>
+        <v>337.2538056229537</v>
       </c>
       <c r="AK7" t="n">
-        <v>8.174340924035906e-05</v>
+        <v>8.174340898744331e-05</v>
       </c>
       <c r="AL7" t="n">
-        <v>-940.3329141334998</v>
+        <v>-940.3329141334489</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.0152560420422833</v>
+        <v>-0.01525604198034497</v>
       </c>
       <c r="AN7" t="n">
-        <v>711.7278994447263</v>
+        <v>711.7278994445767</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.003335535100160325</v>
+        <v>0.003335535075520275</v>
       </c>
       <c r="AP7" t="n">
-        <v>-337.2538056229571</v>
+        <v>-337.2538056229537</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-8.174340924035906e-05</v>
+        <v>-8.174340898744331e-05</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1083.189919604242</v>
+        <v>-1083.189919604273</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.004757168558678665</v>
+        <v>-0.004757168472776685</v>
       </c>
     </row>
     <row r="8">
@@ -4825,124 +4825,124 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.004504606958510924</v>
+        <v>-0.004504606958509985</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0007507678264184873</v>
+        <v>-0.0007507678264183309</v>
       </c>
       <c r="H8" t="n">
-        <v>-711.7278994447259</v>
+        <v>-711.7278994445777</v>
       </c>
       <c r="I8" t="n">
-        <v>-150153.5652836974</v>
+        <v>-150153.5652836662</v>
       </c>
       <c r="J8" t="n">
-        <v>3.596176627224358</v>
+        <v>3.596176627224334</v>
       </c>
       <c r="K8" t="n">
-        <v>5.264656709531542e-05</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.007516730126563806</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.817587401731315e-06</v>
+        <v>-5.817587439646455e-06</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5737082536248662</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04500689564365364</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="P8" t="n">
-        <v>8.114175479580929</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.274815160420837e-05</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.01202133708507473</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="S8" t="n">
-        <v>1.276246033172293e-06</v>
+        <v>1.27624601135778e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4758775876426864</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="U8" t="n">
-        <v>0.04505488004373993</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.007516730126563806</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="W8" t="n">
-        <v>5.264656709531542e-05</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.596176627224358</v>
+        <v>-3.596176627224334</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.04500689564365364</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5737082536248662</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.817587401731315e-06</v>
+        <v>5.817587439646455e-06</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.01202133708507473</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.274815160420837e-05</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="AD8" t="n">
-        <v>-8.114175479580929</v>
+        <v>-8.114175479580663</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.04505488004373993</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.4758775876426864</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="AG8" t="n">
-        <v>-1.276246033172293e-06</v>
+        <v>-1.27624601135778e-06</v>
       </c>
       <c r="AH8" t="n">
-        <v>711.7278994447261</v>
+        <v>711.7278994445778</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.003335535100540082</v>
+        <v>0.003335535075336502</v>
       </c>
       <c r="AJ8" t="n">
-        <v>412.7461943766323</v>
+        <v>412.7461943766295</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.0001365709848609731</v>
+        <v>-0.0001365709851156582</v>
       </c>
       <c r="AL8" t="n">
-        <v>-1015.843890303083</v>
+        <v>-1015.843890303033</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.01525604204344892</v>
+        <v>0.01525604197975264</v>
       </c>
       <c r="AN8" t="n">
-        <v>-711.7278994447261</v>
+        <v>-711.7278994445778</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.003335535100540082</v>
+        <v>-0.003335535075336502</v>
       </c>
       <c r="AP8" t="n">
-        <v>-262.7461943766323</v>
+        <v>-262.7461943766295</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0001365709848609731</v>
+        <v>0.0001365709851156582</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1010.633275956709</v>
+        <v>-1010.633275956742</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.004757168559791573</v>
+        <v>0.004757168472266371</v>
       </c>
     </row>
     <row r="9">
@@ -4964,124 +4964,124 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.004504606958511742</v>
+        <v>-0.004504606958510099</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0007507678264186236</v>
+        <v>-0.0007507678264183498</v>
       </c>
       <c r="H9" t="n">
-        <v>-711.7278994448552</v>
+        <v>-711.7278994445957</v>
       </c>
       <c r="I9" t="n">
-        <v>-150153.5652837247</v>
+        <v>-150153.56528367</v>
       </c>
       <c r="J9" t="n">
-        <v>3.596176627225665</v>
+        <v>3.596176627226205</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.264656577106183e-05</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.007516730126564661</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="M9" t="n">
-        <v>5.817587168809183e-06</v>
+        <v>5.817587130890855e-06</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5737082536251048</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0450068956433242</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="P9" t="n">
-        <v>8.114175479584461</v>
+        <v>8.114175479585626</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.274814817495947e-05</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.0120213370850764</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.276246290880136e-06</v>
+        <v>-1.276246312679776e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4758775876429612</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.04505488004286866</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.007516730126564661</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="W9" t="n">
-        <v>-5.264656577106183e-05</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.596176627225665</v>
+        <v>-3.596176627226205</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.0450068956433242</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.5737082536251048</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="AA9" t="n">
-        <v>-5.817587168809183e-06</v>
+        <v>-5.817587130890855e-06</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.0120213370850764</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.274814817495947e-05</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="AD9" t="n">
-        <v>-8.114175479584461</v>
+        <v>-8.114175479585626</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.04505488004286866</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.4758775876429612</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.276246290880136e-06</v>
+        <v>1.276246312679776e-06</v>
       </c>
       <c r="AH9" t="n">
-        <v>711.7278994448554</v>
+        <v>711.7278994445958</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.003335535256706077</v>
+        <v>-0.003335535281918336</v>
       </c>
       <c r="AJ9" t="n">
-        <v>412.7461943768008</v>
+        <v>412.7461943768724</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0001365709833188455</v>
+        <v>0.0001365709830680184</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1015.843890303616</v>
+        <v>-1015.843890303781</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.01525604253028832</v>
+        <v>-0.01525604259399728</v>
       </c>
       <c r="AN9" t="n">
-        <v>-711.7278994448554</v>
+        <v>-711.7278994445958</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.003335535256706077</v>
+        <v>0.003335535281918336</v>
       </c>
       <c r="AP9" t="n">
-        <v>-262.7461943768008</v>
+        <v>-262.7461943768724</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.0001365709833188455</v>
+        <v>-0.0001365709830680184</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1010.633275957188</v>
+        <v>-1010.633275957454</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0.004757169009948131</v>
+        <v>-0.00475716909751274</v>
       </c>
     </row>
     <row r="10">
@@ -5103,124 +5103,124 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002010446251388883</v>
+        <v>0.002010446251387233</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003350743752314805</v>
+        <v>0.0003350743752312055</v>
       </c>
       <c r="H10" t="n">
-        <v>317.6505077194435</v>
+        <v>317.6505077191828</v>
       </c>
       <c r="I10" t="n">
-        <v>67014.87504629609</v>
+        <v>67014.8750462411</v>
       </c>
       <c r="J10" t="n">
-        <v>8.113133295380457</v>
+        <v>8.113133295381624</v>
       </c>
       <c r="K10" t="n">
-        <v>5.274814816710414e-05</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01202133708507639</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="M10" t="n">
-        <v>1.276246291459122e-06</v>
+        <v>1.276246312356512e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4768655535134355</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01500508180312803</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="P10" t="n">
-        <v>11.24253477912691</v>
+        <v>11.24253477912758</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.272740356380378e-05</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01403178333646527</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.886832883124274e-07</v>
+        <v>-2.886833036039658e-07</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2774101967683359</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01500512856519697</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01202133708507639</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="W10" t="n">
-        <v>5.274814816710414e-05</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="X10" t="n">
-        <v>-8.113133295380457</v>
+        <v>-8.113133295381624</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01500508180312803</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.4768655535134355</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.276246291459122e-06</v>
+        <v>-1.276246312356512e-06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.01403178333646527</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.272740356380378e-05</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="AD10" t="n">
-        <v>-11.24253477912691</v>
+        <v>-11.24253477912758</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.01500512856519697</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2774101967683359</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.886832883124274e-07</v>
+        <v>2.886833036039658e-07</v>
       </c>
       <c r="AH10" t="n">
-        <v>-317.6505077194436</v>
+        <v>-317.6505077191828</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.0007256796201811321</v>
+        <v>-0.000725679616803785</v>
       </c>
       <c r="AJ10" t="n">
-        <v>213.7549774489485</v>
+        <v>213.7549774489315</v>
       </c>
       <c r="AK10" t="n">
-        <v>-1.330920423731063e-07</v>
+        <v>-1.330920974471073e-07</v>
       </c>
       <c r="AL10" t="n">
-        <v>-493.6679683554712</v>
+        <v>-493.6679683552808</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.003335086749574341</v>
+        <v>-0.003335086766222121</v>
       </c>
       <c r="AN10" t="n">
-        <v>317.6505077194436</v>
+        <v>317.6505077191828</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0007256796201811321</v>
+        <v>0.000725679616803785</v>
       </c>
       <c r="AP10" t="n">
-        <v>-213.7549774489485</v>
+        <v>-213.7549774489315</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.330920423731063e-07</v>
+        <v>1.330920974471073e-07</v>
       </c>
       <c r="AR10" t="n">
-        <v>-788.8618963382187</v>
+        <v>-788.861896338309</v>
       </c>
       <c r="AS10" t="n">
-        <v>-0.001018990971512444</v>
+        <v>-0.00101899093460061</v>
       </c>
     </row>
     <row r="11">
@@ -5242,124 +5242,124 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002010446251388151</v>
+        <v>0.00201044625138745</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003350743752313584</v>
+        <v>0.0003350743752312416</v>
       </c>
       <c r="H11" t="n">
-        <v>317.6505077193278</v>
+        <v>317.6505077192171</v>
       </c>
       <c r="I11" t="n">
-        <v>67014.87504627169</v>
+        <v>67014.87504624833</v>
       </c>
       <c r="J11" t="n">
-        <v>8.11313329537693</v>
+        <v>8.113133295376661</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.274815161206213e-05</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01202133708507474</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.276246032599108e-06</v>
+        <v>-1.276246011702428e-06</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4768655535131607</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.01500508180225687</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="P11" t="n">
-        <v>11.24253477912112</v>
+        <v>11.2425347791201</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.272740904099736e-05</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01403178333646289</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="S11" t="n">
-        <v>2.886835082336281e-07</v>
+        <v>2.886834930193329e-07</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2774101967680513</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.01500512856379087</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01202133708507474</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="W11" t="n">
-        <v>-5.274815161206213e-05</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.11313329537693</v>
+        <v>-8.113133295376661</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.01500508180225687</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.4768655535131607</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.276246032599108e-06</v>
+        <v>1.276246011702428e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01403178333646289</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="AC11" t="n">
-        <v>-5.272740904099736e-05</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="AD11" t="n">
-        <v>-11.24253477912112</v>
+        <v>-11.2425347791201</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.01500512856379087</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.2774101967680513</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="AG11" t="n">
-        <v>-2.886835082336281e-07</v>
+        <v>-2.886834930193329e-07</v>
       </c>
       <c r="AH11" t="n">
-        <v>-317.6505077193278</v>
+        <v>-317.6505077192171</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0007256797671678136</v>
+        <v>0.0007256797704882252</v>
       </c>
       <c r="AJ11" t="n">
-        <v>213.7549774488043</v>
+        <v>213.7549774487221</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.330905198618226e-07</v>
+        <v>1.330904625743146e-07</v>
       </c>
       <c r="AL11" t="n">
-        <v>-493.6679683550301</v>
+        <v>-493.6679683547802</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.003335087161719666</v>
+        <v>0.003335087144958782</v>
       </c>
       <c r="AN11" t="n">
-        <v>317.6505077193278</v>
+        <v>317.6505077192171</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.0007256797671678136</v>
+        <v>-0.0007256797704882252</v>
       </c>
       <c r="AP11" t="n">
-        <v>-213.7549774488043</v>
+        <v>-213.7549774487221</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.330905198618226e-07</v>
+        <v>-1.330904625743146e-07</v>
       </c>
       <c r="AR11" t="n">
-        <v>-788.8618963377921</v>
+        <v>-788.8618963375543</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.001018991441287212</v>
+        <v>0.001018991477970577</v>
       </c>
     </row>
     <row r="12">
@@ -5381,124 +5381,124 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.002010446251388158</v>
+        <v>-0.002010446251387455</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0003350743752313596</v>
+        <v>-0.0003350743752312425</v>
       </c>
       <c r="H12" t="n">
-        <v>-317.6505077193289</v>
+        <v>-317.6505077192179</v>
       </c>
       <c r="I12" t="n">
-        <v>-67014.87504627192</v>
+        <v>-67014.8750462485</v>
       </c>
       <c r="J12" t="n">
-        <v>8.114175479580929</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="K12" t="n">
-        <v>5.274815160420837e-05</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.01202133708507473</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="M12" t="n">
-        <v>1.276246033172293e-06</v>
+        <v>1.27624601135778e-06</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4758775876426864</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04505488004373993</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="P12" t="n">
-        <v>11.24364880861841</v>
+        <v>11.24364880861739</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.27274090296737e-05</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.01403178333646289</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.886835081465285e-07</v>
+        <v>-2.886834933623841e-07</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2818139420128695</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="U12" t="n">
-        <v>0.04505493137067544</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.01202133708507473</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="W12" t="n">
-        <v>5.274815160420837e-05</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.114175479580929</v>
+        <v>-8.114175479580663</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.04505488004373993</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.4758775876426864</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="AA12" t="n">
-        <v>-1.276246033172293e-06</v>
+        <v>-1.27624601135778e-06</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.01403178333646289</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.27274090296737e-05</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="AD12" t="n">
-        <v>-11.24364880861841</v>
+        <v>-11.24364880861739</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.04505493137067544</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2818139420128695</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.886835081465285e-07</v>
+        <v>2.886834933623841e-07</v>
       </c>
       <c r="AH12" t="n">
-        <v>317.650507719329</v>
+        <v>317.6505077192182</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.0007256797668005119</v>
+        <v>-0.0007256797706754747</v>
       </c>
       <c r="AJ12" t="n">
-        <v>286.245022550801</v>
+        <v>286.2450225507185</v>
       </c>
       <c r="AK12" t="n">
-        <v>-1.460843549183632e-07</v>
+        <v>-1.460844122613825e-07</v>
       </c>
       <c r="AL12" t="n">
-        <v>-565.1279698863391</v>
+        <v>-565.1279698860859</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.003335087160977454</v>
+        <v>-0.003335087145519354</v>
       </c>
       <c r="AN12" t="n">
-        <v>-317.650507719329</v>
+        <v>-317.6505077192182</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0007256797668005119</v>
+        <v>0.0007256797706754747</v>
       </c>
       <c r="AP12" t="n">
-        <v>-136.245022550801</v>
+        <v>-136.2450225507185</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.460843549183632e-07</v>
+        <v>1.460844122613825e-07</v>
       </c>
       <c r="AR12" t="n">
-        <v>-702.3421654184676</v>
+        <v>-702.342165418225</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0.001018991439825603</v>
+        <v>-0.001018991478533501</v>
       </c>
     </row>
     <row r="13">
@@ -5520,124 +5520,124 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.002010446251388881</v>
+        <v>-0.002010446251387236</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0003350743752314801</v>
+        <v>-0.0003350743752312061</v>
       </c>
       <c r="H13" t="n">
-        <v>-317.6505077194432</v>
+        <v>-317.6505077191833</v>
       </c>
       <c r="I13" t="n">
-        <v>-67014.87504629603</v>
+        <v>-67014.87504624121</v>
       </c>
       <c r="J13" t="n">
-        <v>8.114175479584461</v>
+        <v>8.114175479585626</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.274814817495947e-05</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0120213370850764</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.276246290880136e-06</v>
+        <v>-1.276246312679776e-06</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4758775876429612</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.04505488004286866</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="P13" t="n">
-        <v>11.2436488086242</v>
+        <v>11.24364880862486</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.272740357512158e-05</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.01403178333646528</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="S13" t="n">
-        <v>2.88683288419905e-07</v>
+        <v>2.886833031477993e-07</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2818139420131543</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.04505493136926936</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.0120213370850764</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="W13" t="n">
-        <v>-5.274814817495947e-05</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.114175479584461</v>
+        <v>-8.114175479585626</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.04505488004286866</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.4758775876429612</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.276246290880136e-06</v>
+        <v>1.276246312679776e-06</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.01403178333646528</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="AC13" t="n">
-        <v>-5.272740357512158e-05</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="AD13" t="n">
-        <v>-11.2436488086242</v>
+        <v>-11.24364880862486</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.04505493136926936</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.2818139420131543</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="AG13" t="n">
-        <v>-2.88683288419905e-07</v>
+        <v>-2.886833031477993e-07</v>
       </c>
       <c r="AH13" t="n">
-        <v>317.6505077194431</v>
+        <v>317.6505077191835</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.000725679620527225</v>
+        <v>0.0007256796166823266</v>
       </c>
       <c r="AJ13" t="n">
-        <v>286.2450225509428</v>
+        <v>286.245022550927</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.460828327748409e-07</v>
+        <v>1.460827712407298e-07</v>
       </c>
       <c r="AL13" t="n">
-        <v>-565.1279698867711</v>
+        <v>-565.127969886584</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.003335086750263713</v>
+        <v>0.003335086765759374</v>
       </c>
       <c r="AN13" t="n">
-        <v>-317.6505077194431</v>
+        <v>-317.6505077191835</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.000725679620527225</v>
+        <v>-0.0007256796166823266</v>
       </c>
       <c r="AP13" t="n">
-        <v>-136.2450225509428</v>
+        <v>-136.245022550927</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-1.460828327748409e-07</v>
+        <v>-1.460827712407298e-07</v>
       </c>
       <c r="AR13" t="n">
-        <v>-702.342165418886</v>
+        <v>-702.3421654189774</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.001018990972899647</v>
+        <v>0.001018990934334565</v>
       </c>
     </row>
     <row r="14">
@@ -5659,124 +5659,124 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0005556571193584946</v>
+        <v>0.0005556571193576412</v>
       </c>
       <c r="G14" t="n">
-        <v>9.260951989308244e-05</v>
+        <v>9.260951989294019e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>87.79382485864215</v>
+        <v>87.79382485850731</v>
       </c>
       <c r="I14" t="n">
-        <v>18521.90397861649</v>
+        <v>18521.90397858804</v>
       </c>
       <c r="J14" t="n">
-        <v>11.24253477912691</v>
+        <v>11.24253477912758</v>
       </c>
       <c r="K14" t="n">
-        <v>5.272740356380378e-05</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01403178333646527</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.886832883124274e-07</v>
+        <v>-2.886833036039658e-07</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2774101967683359</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01500512856519697</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="P14" t="n">
-        <v>12.76362755076675</v>
+        <v>12.7636275507655</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.273160774713402e-05</v>
+        <v>5.273160743815383e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01458744045582377</v>
+        <v>0.01458744045581826</v>
       </c>
       <c r="S14" t="n">
-        <v>1.041021125745989e-07</v>
+        <v>1.041020896839185e-07</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1191579135707582</v>
+        <v>0.1191579135705716</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01500512783927177</v>
+        <v>0.01500512783931789</v>
       </c>
       <c r="V14" t="n">
-        <v>0.01403178333646527</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="W14" t="n">
-        <v>5.272740356380378e-05</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.24253477912691</v>
+        <v>-11.24253477912758</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.01500512856519697</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.2774101967683359</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.886832883124274e-07</v>
+        <v>2.886833036039658e-07</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.01458744045582377</v>
+        <v>0.01458744045581826</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.273160774713402e-05</v>
+        <v>5.273160743815383e-05</v>
       </c>
       <c r="AD14" t="n">
-        <v>-12.76362755076675</v>
+        <v>-12.7636275507655</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.01500512783927177</v>
+        <v>0.01500512783931789</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1191579135707582</v>
+        <v>0.1191579135705716</v>
       </c>
       <c r="AG14" t="n">
-        <v>-1.041021125745989e-07</v>
+        <v>-1.041020896839185e-07</v>
       </c>
       <c r="AH14" t="n">
-        <v>-87.79382485864198</v>
+        <v>-87.79382485850738</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0001355530381578693</v>
+        <v>0.000135553010461472</v>
       </c>
       <c r="AJ14" t="n">
-        <v>81.74248202023045</v>
+        <v>81.74248202001982</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.066094795249995e-09</v>
+        <v>2.066456408766904e-09</v>
       </c>
       <c r="AL14" t="n">
-        <v>-128.1207564944852</v>
+        <v>-128.1207564938366</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.000697320311130005</v>
+        <v>0.0006973202224174468</v>
       </c>
       <c r="AN14" t="n">
-        <v>87.79382485864198</v>
+        <v>87.79382485850738</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.0001355530381578693</v>
+        <v>-0.000135553010461472</v>
       </c>
       <c r="AP14" t="n">
-        <v>-81.74248202023045</v>
+        <v>-81.74248202001982</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-2.066094795249995e-09</v>
+        <v>-2.066456408766904e-09</v>
       </c>
       <c r="AR14" t="n">
-        <v>-362.3341356268993</v>
+        <v>-362.3341356262787</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0001159979178172107</v>
+        <v>0.0001159978403513784</v>
       </c>
     </row>
     <row r="15">
@@ -5798,124 +5798,124 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0005556571193580991</v>
+        <v>0.0005556571193578615</v>
       </c>
       <c r="G15" t="n">
-        <v>9.260951989301652e-05</v>
+        <v>9.260951989297692e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>87.79382485857967</v>
+        <v>87.79382485854211</v>
       </c>
       <c r="I15" t="n">
-        <v>18521.9039786033</v>
+        <v>18521.90397859538</v>
       </c>
       <c r="J15" t="n">
-        <v>11.24253477912112</v>
+        <v>11.2425347791201</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.272740904099736e-05</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01403178333646289</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="M15" t="n">
-        <v>2.886835082336281e-07</v>
+        <v>2.886834930193329e-07</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2774101967680513</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.01500512856379087</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="P15" t="n">
-        <v>12.76362755075872</v>
+        <v>12.76362755075735</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.273161470783783e-05</v>
+        <v>-5.273161501681668e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>0.01458744045582099</v>
+        <v>0.01458744045581829</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.041019902353731e-07</v>
+        <v>-1.041020131429611e-07</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1191579135705613</v>
+        <v>0.1191579135705384</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.01500512783739848</v>
+        <v>-0.01500512783735091</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01403178333646289</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="W15" t="n">
-        <v>-5.272740904099736e-05</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="X15" t="n">
-        <v>-11.24253477912112</v>
+        <v>-11.2425347791201</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.01500512856379087</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.2774101967680513</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="AA15" t="n">
-        <v>-2.886835082336281e-07</v>
+        <v>-2.886834930193329e-07</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.01458744045582099</v>
+        <v>0.01458744045581829</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.273161470783783e-05</v>
+        <v>-5.273161501681668e-05</v>
       </c>
       <c r="AD15" t="n">
-        <v>-12.76362755075872</v>
+        <v>-12.76362755075735</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.01500512783739848</v>
+        <v>-0.01500512783735091</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1191579135705613</v>
+        <v>0.1191579135705384</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.041019902353731e-07</v>
+        <v>1.041020131429611e-07</v>
       </c>
       <c r="AH15" t="n">
-        <v>-87.79382485857968</v>
+        <v>-87.79382485854194</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.0001355529254980607</v>
+        <v>-0.0001355529532395382</v>
       </c>
       <c r="AJ15" t="n">
-        <v>81.74248202003355</v>
+        <v>81.74248202002072</v>
       </c>
       <c r="AK15" t="n">
-        <v>-2.067424516305483e-09</v>
+        <v>-2.06706612937424e-09</v>
       </c>
       <c r="AL15" t="n">
-        <v>-128.1207564939577</v>
+        <v>-128.1207564939566</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0.0006973200453612369</v>
+        <v>-0.0006973201342787144</v>
       </c>
       <c r="AN15" t="n">
-        <v>87.79382485857968</v>
+        <v>87.79382485854194</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0001355529254980607</v>
+        <v>0.0001355529532395382</v>
       </c>
       <c r="AP15" t="n">
-        <v>-81.74248202003355</v>
+        <v>-81.74248202002072</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.067424516305483e-09</v>
+        <v>2.06706612937424e-09</v>
       </c>
       <c r="AR15" t="n">
-        <v>-362.3341356262445</v>
+        <v>-362.3341356261658</v>
       </c>
       <c r="AS15" t="n">
-        <v>-0.0001159975076271205</v>
+        <v>-0.0001159975851585185</v>
       </c>
     </row>
     <row r="16">
@@ -5937,124 +5937,124 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0005556571193581009</v>
+        <v>-0.0005556571193578649</v>
       </c>
       <c r="G16" t="n">
-        <v>-9.260951989301681e-05</v>
+        <v>-9.260951989297748e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>-87.79382485857994</v>
+        <v>-87.79382485854266</v>
       </c>
       <c r="I16" t="n">
-        <v>-18521.90397860336</v>
+        <v>-18521.9039785955</v>
       </c>
       <c r="J16" t="n">
-        <v>11.24364880861841</v>
+        <v>11.24364880861739</v>
       </c>
       <c r="K16" t="n">
-        <v>5.27274090296737e-05</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.01403178333646289</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.886835081465285e-07</v>
+        <v>-2.886834933623841e-07</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2818139420128695</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="O16" t="n">
-        <v>0.04505493137067544</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="P16" t="n">
-        <v>12.76431736073357</v>
+        <v>12.76431736073221</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.273161469785554e-05</v>
+        <v>5.273161502770671e-05</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.01458744045582099</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="S16" t="n">
-        <v>1.041019900625209e-07</v>
+        <v>1.041020126456332e-07</v>
       </c>
       <c r="T16" t="n">
-        <v>0.09905190241357491</v>
+        <v>0.09905190241355175</v>
       </c>
       <c r="U16" t="n">
-        <v>0.04505493222250071</v>
+        <v>0.04505493222254756</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.01403178333646289</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="W16" t="n">
-        <v>5.27274090296737e-05</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="X16" t="n">
-        <v>-11.24364880861841</v>
+        <v>-11.24364880861739</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.04505493137067544</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.2818139420128695</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.886835081465285e-07</v>
+        <v>2.886834933623841e-07</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.01458744045582099</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.273161469785554e-05</v>
+        <v>5.273161502770671e-05</v>
       </c>
       <c r="AD16" t="n">
-        <v>-12.76431736073357</v>
+        <v>-12.76431736073221</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.04505493222250071</v>
+        <v>0.04505493222254756</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.09905190241357491</v>
+        <v>0.09905190241355175</v>
       </c>
       <c r="AG16" t="n">
-        <v>-1.041019900625209e-07</v>
+        <v>-1.041020126456332e-07</v>
       </c>
       <c r="AH16" t="n">
-        <v>87.79382485858014</v>
+        <v>87.79382485854239</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0001355529252306444</v>
+        <v>0.0001355529529342408</v>
       </c>
       <c r="AJ16" t="n">
-        <v>168.2575179795031</v>
+        <v>168.2575179794908</v>
       </c>
       <c r="AK16" t="n">
-        <v>-2.424425771252459e-09</v>
+        <v>-2.424063477723948e-09</v>
       </c>
       <c r="AL16" t="n">
-        <v>-219.528644635031</v>
+        <v>-219.5286446350328</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.0006973200443666297</v>
+        <v>0.0006973201332486564</v>
       </c>
       <c r="AN16" t="n">
-        <v>-87.79382485858014</v>
+        <v>-87.79382485854239</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.0001355529252306444</v>
+        <v>-0.0001355529529342408</v>
       </c>
       <c r="AP16" t="n">
-        <v>-18.25751797950306</v>
+        <v>-18.25751797949079</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.424425771252459e-09</v>
+        <v>2.424063477723948e-09</v>
       </c>
       <c r="AR16" t="n">
-        <v>-340.0164632419874</v>
+        <v>-340.0164632419128</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.0001159975070172403</v>
+        <v>0.0001159975843567848</v>
       </c>
     </row>
     <row r="17">
@@ -6076,124 +6076,124 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0005556571193584964</v>
+        <v>-0.0005556571193576377</v>
       </c>
       <c r="G17" t="n">
-        <v>-9.260951989308273e-05</v>
+        <v>-9.260951989293962e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>-87.79382485864242</v>
+        <v>-87.79382485850675</v>
       </c>
       <c r="I17" t="n">
-        <v>-18521.90397861654</v>
+        <v>-18521.90397858792</v>
       </c>
       <c r="J17" t="n">
-        <v>11.2436488086242</v>
+        <v>11.24364880862486</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.272740357512158e-05</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.01403178333646528</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="M17" t="n">
-        <v>2.88683288419905e-07</v>
+        <v>2.886833031477993e-07</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2818139420131543</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.04505493136926936</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="P17" t="n">
-        <v>12.76431736074161</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.273160775711663e-05</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.01458744045582378</v>
+        <v>-0.01458744045581826</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.041021128221863e-07</v>
+        <v>-1.041020899760041e-07</v>
       </c>
       <c r="T17" t="n">
-        <v>0.09905190241377351</v>
+        <v>0.09905190241358573</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.04505493222062767</v>
+        <v>-0.04505493222058038</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.01403178333646528</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="W17" t="n">
-        <v>-5.272740357512158e-05</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="X17" t="n">
-        <v>-11.2436488086242</v>
+        <v>-11.24364880862486</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.04505493136926936</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.2818139420131543</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="AA17" t="n">
-        <v>-2.88683288419905e-07</v>
+        <v>-2.886833031477993e-07</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.01458744045582378</v>
+        <v>-0.01458744045581826</v>
       </c>
       <c r="AC17" t="n">
-        <v>-5.273160775711663e-05</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="AD17" t="n">
-        <v>-12.76431736074161</v>
+        <v>-12.76431736074036</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.04505493222062767</v>
+        <v>-0.04505493222058038</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.09905190241377351</v>
+        <v>0.09905190241358573</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.041021128221863e-07</v>
+        <v>1.041020899760041e-07</v>
       </c>
       <c r="AH17" t="n">
-        <v>87.79382485864244</v>
+        <v>87.79382485850692</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.0001355530383835308</v>
+        <v>-0.0001355530108317436</v>
       </c>
       <c r="AJ17" t="n">
-        <v>168.2575179797013</v>
+        <v>168.2575179794911</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.42309672326968e-09</v>
+        <v>2.423457712286137e-09</v>
       </c>
       <c r="AL17" t="n">
-        <v>-219.528644635564</v>
+        <v>-219.528644634917</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.0006973203120697463</v>
+        <v>-0.000697320223406836</v>
       </c>
       <c r="AN17" t="n">
-        <v>-87.79382485864244</v>
+        <v>-87.79382485850692</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.0001355530383835308</v>
+        <v>0.0001355530108317436</v>
       </c>
       <c r="AP17" t="n">
-        <v>-18.25751797970133</v>
+        <v>-18.2575179794911</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-2.42309672326968e-09</v>
+        <v>-2.423457712286137e-09</v>
       </c>
       <c r="AR17" t="n">
-        <v>-340.0164632426458</v>
+        <v>-340.0164632420323</v>
       </c>
       <c r="AS17" t="n">
-        <v>-0.0001159979182314488</v>
+        <v>-0.0001159978415836149</v>
       </c>
     </row>
     <row r="18">
@@ -6215,124 +6215,124 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0001052931328663773</v>
+        <v>-0.0001052931328663778</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.316164160829716e-05</v>
+        <v>-1.316164160829722e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>-12.47723624466571</v>
+        <v>-12.47723624466577</v>
       </c>
       <c r="I18" t="n">
-        <v>-2632.328321659432</v>
+        <v>-2632.328321659445</v>
       </c>
       <c r="J18" t="n">
-        <v>3.595119805279023</v>
+        <v>3.595119805279563</v>
       </c>
       <c r="K18" t="n">
-        <v>5.264656576807992e-05</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.007516730126564649</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.81758716827277e-06</v>
+        <v>-5.817587131184721e-06</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5733905572098467</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01497636114528572</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="P18" t="n">
-        <v>3.595119805277716</v>
+        <v>3.595119805277692</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.264656709829736e-05</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="R18" t="n">
-        <v>0.007516730126563812</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="S18" t="n">
-        <v>5.817587402268885e-06</v>
+        <v>5.817587439357226e-06</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5733905572096085</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0149763611449562</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="V18" t="n">
-        <v>5.264656576807992e-05</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="W18" t="n">
-        <v>-3.595119805279023</v>
+        <v>-3.595119805279563</v>
       </c>
       <c r="X18" t="n">
-        <v>0.007516730126564649</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.5733905572098467</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.81758716827277e-06</v>
+        <v>5.817587131184721e-06</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.01497636114528572</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="AB18" t="n">
-        <v>-5.264656709829736e-05</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.595119805277716</v>
+        <v>-3.595119805277692</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.007516730126563812</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.5733905572096085</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="AF18" t="n">
-        <v>-5.817587402268885e-06</v>
+        <v>-5.817587439357226e-06</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.0149763611449562</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="AH18" t="n">
-        <v>12.47723624466571</v>
+        <v>12.47723624466577</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.13686837721616e-12</v>
+        <v>-3.865352482534945e-12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>9.748801765852022e-11</v>
+        <v>1.28306291372754e-10</v>
       </c>
       <c r="AK18" t="n">
-        <v>5.082601006733967e-13</v>
+        <v>7.23199278240827e-13</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.006457521496698426</v>
+        <v>0.006457521373425529</v>
       </c>
       <c r="AM18" t="n">
-        <v>16.62376087108873</v>
+        <v>16.62376087106873</v>
       </c>
       <c r="AN18" t="n">
-        <v>-12.47723624466571</v>
+        <v>-12.47723624466577</v>
       </c>
       <c r="AO18" t="n">
-        <v>-1.13686837721616e-12</v>
+        <v>3.865352482534945e-12</v>
       </c>
       <c r="AP18" t="n">
-        <v>-9.748801765852022e-11</v>
+        <v>-1.28306291372754e-10</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-5.082601006733967e-13</v>
+        <v>-7.23199278240827e-13</v>
       </c>
       <c r="AR18" t="n">
-        <v>-0.006457522276602568</v>
+        <v>-0.006457522399876302</v>
       </c>
       <c r="AS18" t="n">
-        <v>-16.62376087107964</v>
+        <v>-16.62376087109965</v>
       </c>
     </row>
     <row r="19">
@@ -6366,112 +6366,112 @@
         <v>26420.5486660507</v>
       </c>
       <c r="J19" t="n">
-        <v>3.595119805277716</v>
+        <v>3.595119805277692</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.264656709829736e-05</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.007516730126563812</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="M19" t="n">
-        <v>5.817587402268885e-06</v>
+        <v>5.817587439357226e-06</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5733905572096085</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0149763611449562</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="P19" t="n">
-        <v>3.596176627224358</v>
+        <v>3.596176627224334</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.264656709531542e-05</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.007516730126563806</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="S19" t="n">
-        <v>-5.817587401731315e-06</v>
+        <v>-5.817587439646455e-06</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5737082536248662</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="U19" t="n">
-        <v>0.04500689564365364</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="V19" t="n">
-        <v>3.595119805277716</v>
+        <v>3.595119805277692</v>
       </c>
       <c r="W19" t="n">
-        <v>-5.264656709829736e-05</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="X19" t="n">
-        <v>0.007516730126563812</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.817587402268885e-06</v>
+        <v>5.817587439357226e-06</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.5733905572096085</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.0149763611449562</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.596176627224358</v>
+        <v>3.596176627224334</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.264656709531542e-05</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.007516730126563806</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="AE19" t="n">
-        <v>-5.817587401731315e-06</v>
+        <v>-5.817587439646455e-06</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.5737082536248662</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.04500689564365364</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="AH19" t="n">
-        <v>-125.2334006770398</v>
+        <v>-125.233400677098</v>
       </c>
       <c r="AI19" t="n">
-        <v>12.48925291830579</v>
+        <v>12.48925291831083</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-475.9154605522591</v>
+        <v>-475.9154605522502</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.483662313930812e-05</v>
+        <v>2.48366232994117e-05</v>
       </c>
       <c r="AL19" t="n">
-        <v>1903.485520698568</v>
+        <v>1903.485520698533</v>
       </c>
       <c r="AM19" t="n">
-        <v>16.66630415554469</v>
+        <v>16.66630415556484</v>
       </c>
       <c r="AN19" t="n">
-        <v>125.2334006770398</v>
+        <v>125.233400677098</v>
       </c>
       <c r="AO19" t="n">
-        <v>-12.48925291830579</v>
+        <v>-12.48925291831083</v>
       </c>
       <c r="AP19" t="n">
-        <v>475.9154605522591</v>
+        <v>475.9154605522502</v>
       </c>
       <c r="AQ19" t="n">
-        <v>-2.483662313930812e-05</v>
+        <v>-2.48366232994117e-05</v>
       </c>
       <c r="AR19" t="n">
-        <v>1903.838163719504</v>
+        <v>1903.838163719469</v>
       </c>
       <c r="AS19" t="n">
-        <v>83.24771919090161</v>
+        <v>83.24771919092179</v>
       </c>
     </row>
     <row r="20">
@@ -6493,124 +6493,124 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001052931328663773</v>
+        <v>0.0001052931328663774</v>
       </c>
       <c r="G20" t="n">
-        <v>1.316164160829716e-05</v>
+        <v>1.316164160829718e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>12.4772362446657</v>
+        <v>12.47723624466572</v>
       </c>
       <c r="I20" t="n">
-        <v>2632.328321659431</v>
+        <v>2632.328321659435</v>
       </c>
       <c r="J20" t="n">
-        <v>3.596176627224358</v>
+        <v>3.596176627224334</v>
       </c>
       <c r="K20" t="n">
-        <v>5.264656709531542e-05</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.007516730126563806</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.817587401731315e-06</v>
+        <v>-5.817587439646455e-06</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5737082536248662</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04500689564365364</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="P20" t="n">
-        <v>3.596176627225665</v>
+        <v>3.596176627226205</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.264656577106183e-05</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.007516730126564661</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="S20" t="n">
-        <v>5.817587168809183e-06</v>
+        <v>5.817587130890855e-06</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5737082536251048</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0450068956433242</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="V20" t="n">
-        <v>-5.264656709531542e-05</v>
+        <v>-5.264656733141418e-05</v>
       </c>
       <c r="W20" t="n">
-        <v>3.596176627224358</v>
+        <v>3.596176627224334</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.007516730126563806</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.5737082536248662</v>
+        <v>-0.5737082536248554</v>
       </c>
       <c r="Z20" t="n">
-        <v>-5.817587401731315e-06</v>
+        <v>-5.817587439646455e-06</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.04500689564365364</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.264656577106183e-05</v>
+        <v>5.264656553496323e-05</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.596176627225665</v>
+        <v>3.596176627226205</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.007516730126564661</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.5737082536251048</v>
+        <v>-0.5737082536251945</v>
       </c>
       <c r="AF20" t="n">
-        <v>5.817587168809183e-06</v>
+        <v>5.817587130890855e-06</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.0450068956433242</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="AH20" t="n">
-        <v>-12.4772362446657</v>
+        <v>-12.47723624466572</v>
       </c>
       <c r="AI20" t="n">
-        <v>-99.99999999999892</v>
+        <v>-100.000000000004</v>
       </c>
       <c r="AJ20" t="n">
-        <v>9.704281822564553e-11</v>
+        <v>1.285480819013252e-10</v>
       </c>
       <c r="AK20" t="n">
-        <v>5.091482790930968e-13</v>
+        <v>7.238654120556021e-13</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.006457522274820882</v>
+        <v>-0.006457522400840577</v>
       </c>
       <c r="AM20" t="n">
-        <v>-83.3756791690565</v>
+        <v>-83.37567916907628</v>
       </c>
       <c r="AN20" t="n">
-        <v>12.4772362446657</v>
+        <v>12.47723624466572</v>
       </c>
       <c r="AO20" t="n">
-        <v>-100.0000000000011</v>
+        <v>-99.99999999999602</v>
       </c>
       <c r="AP20" t="n">
-        <v>-9.704281822564553e-11</v>
+        <v>-1.285480819013252e-10</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-5.091482790930968e-13</v>
+        <v>-7.238654120556021e-13</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.00645752149847878</v>
+        <v>0.006457521372455919</v>
       </c>
       <c r="AS20" t="n">
-        <v>83.37567916906491</v>
+        <v>83.37567916904467</v>
       </c>
     </row>
     <row r="21">
@@ -6644,112 +6644,112 @@
         <v>26420.5486660618</v>
       </c>
       <c r="J21" t="n">
-        <v>3.596176627225665</v>
+        <v>3.596176627226205</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.264656577106183e-05</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.007516730126564661</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="M21" t="n">
-        <v>5.817587168809183e-06</v>
+        <v>5.817587130890855e-06</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5737082536251048</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0450068956433242</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="P21" t="n">
-        <v>3.595119805279023</v>
+        <v>3.595119805279563</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.264656576807992e-05</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="R21" t="n">
-        <v>0.007516730126564649</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="S21" t="n">
-        <v>-5.81758716827277e-06</v>
+        <v>-5.817587131184721e-06</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5733905572098467</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="U21" t="n">
-        <v>0.01497636114528572</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.596176627225665</v>
+        <v>-3.596176627226205</v>
       </c>
       <c r="W21" t="n">
-        <v>-5.264656577106183e-05</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="X21" t="n">
-        <v>0.007516730126564661</v>
+        <v>0.00751673012656329</v>
       </c>
       <c r="Y21" t="n">
-        <v>-5.817587168809183e-06</v>
+        <v>-5.817587130890855e-06</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.5737082536251048</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.0450068956433242</v>
+        <v>0.04500689564325982</v>
       </c>
       <c r="AB21" t="n">
-        <v>-3.595119805279023</v>
+        <v>-3.595119805279563</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.264656576807992e-05</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.007516730126564649</v>
+        <v>-0.007516730126563289</v>
       </c>
       <c r="AE21" t="n">
-        <v>5.81758716827277e-06</v>
+        <v>5.817587131184721e-06</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.5733905572098467</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.01497636114528572</v>
+        <v>-0.01497636114535011</v>
       </c>
       <c r="AH21" t="n">
-        <v>-125.2334006771562</v>
+        <v>-125.233400677098</v>
       </c>
       <c r="AI21" t="n">
-        <v>12.48925291830772</v>
+        <v>12.48925291830278</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-475.9154605524574</v>
+        <v>-475.9154605525324</v>
       </c>
       <c r="AK21" t="n">
-        <v>-2.483662214261725e-05</v>
+        <v>-2.483662198250748e-05</v>
       </c>
       <c r="AL21" t="n">
-        <v>1903.838163720297</v>
+        <v>1903.838163720598</v>
       </c>
       <c r="AM21" t="n">
-        <v>83.24771919090941</v>
+        <v>83.24771919088963</v>
       </c>
       <c r="AN21" t="n">
-        <v>125.2334006771562</v>
+        <v>125.233400677098</v>
       </c>
       <c r="AO21" t="n">
-        <v>-12.48925291830772</v>
+        <v>-12.48925291830278</v>
       </c>
       <c r="AP21" t="n">
-        <v>475.9154605524574</v>
+        <v>475.9154605525324</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.483662214261725e-05</v>
+        <v>2.483662198250748e-05</v>
       </c>
       <c r="AR21" t="n">
-        <v>1903.485520699361</v>
+        <v>1903.485520699661</v>
       </c>
       <c r="AS21" t="n">
-        <v>16.66630415555239</v>
+        <v>16.6663041555326</v>
       </c>
     </row>
     <row r="22">
@@ -6771,124 +6771,124 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0001054962997791663</v>
+        <v>-0.0001054962997791679</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.318703747239578e-05</v>
+        <v>-1.318703747239599e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>-12.5013115238312</v>
+        <v>-12.5013115238314</v>
       </c>
       <c r="I22" t="n">
-        <v>-2637.407494479156</v>
+        <v>-2637.407494479197</v>
       </c>
       <c r="J22" t="n">
-        <v>8.113133295380457</v>
+        <v>8.113133295381624</v>
       </c>
       <c r="K22" t="n">
-        <v>5.274814816710414e-05</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01202133708507639</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="M22" t="n">
-        <v>1.276246291459122e-06</v>
+        <v>1.276246312356512e-06</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4768655535134355</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="O22" t="n">
-        <v>0.01500508180312803</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="P22" t="n">
-        <v>8.11313329537693</v>
+        <v>8.113133295376661</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.274815161206213e-05</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="R22" t="n">
-        <v>0.01202133708507474</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.276246032599108e-06</v>
+        <v>-1.276246011702428e-06</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4768655535131607</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.01500508180225687</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="V22" t="n">
-        <v>5.274814816710414e-05</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="W22" t="n">
-        <v>-8.113133295380457</v>
+        <v>-8.113133295381624</v>
       </c>
       <c r="X22" t="n">
-        <v>0.01202133708507639</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.4768655535134355</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="Z22" t="n">
-        <v>-1.276246291459122e-06</v>
+        <v>-1.276246312356512e-06</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.01500508180312803</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="AB22" t="n">
-        <v>-5.274815161206213e-05</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="AC22" t="n">
-        <v>-8.11313329537693</v>
+        <v>-8.113133295376661</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.01202133708507474</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.4768655535131607</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.276246032599108e-06</v>
+        <v>1.276246011702428e-06</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.01500508180225687</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="AH22" t="n">
-        <v>12.5013115238312</v>
+        <v>12.5013115238314</v>
       </c>
       <c r="AI22" t="n">
-        <v>-4.433786671143025e-12</v>
+        <v>-2.592059900052845e-11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.079225597777622e-10</v>
+        <v>1.251894328219844e-10</v>
       </c>
       <c r="AK22" t="n">
-        <v>5.864198016070077e-13</v>
+        <v>7.758238496080594e-13</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.001416633671542655</v>
+        <v>-0.001416633740610715</v>
       </c>
       <c r="AM22" t="n">
-        <v>16.65564080097101</v>
+        <v>16.65564080088552</v>
       </c>
       <c r="AN22" t="n">
-        <v>-12.5013115238312</v>
+        <v>-12.5013115238314</v>
       </c>
       <c r="AO22" t="n">
-        <v>4.433786671143025e-12</v>
+        <v>2.592059900052845e-11</v>
       </c>
       <c r="AP22" t="n">
-        <v>-1.079225597777622e-10</v>
+        <v>-1.251894328219844e-10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>-5.864198016070077e-13</v>
+        <v>-7.758238496080594e-13</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.001416632808162177</v>
+        <v>0.001416632739095252</v>
       </c>
       <c r="AS22" t="n">
-        <v>-16.65564080100648</v>
+        <v>-16.65564080109243</v>
       </c>
     </row>
     <row r="23">
@@ -6910,124 +6910,124 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.001042184203999597</v>
+        <v>0.001042184204001373</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001302730254999496</v>
+        <v>0.0001302730255001716</v>
       </c>
       <c r="H23" t="n">
-        <v>123.4988281739522</v>
+        <v>123.4988281741627</v>
       </c>
       <c r="I23" t="n">
-        <v>26054.60509998991</v>
+        <v>26054.60510003432</v>
       </c>
       <c r="J23" t="n">
-        <v>8.11313329537693</v>
+        <v>8.113133295376661</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.274815161206213e-05</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.01202133708507474</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.276246032599108e-06</v>
+        <v>-1.276246011702428e-06</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4768655535131607</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.01500508180225687</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="P23" t="n">
-        <v>8.114175479580929</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.274815160420837e-05</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.01202133708507473</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="S23" t="n">
-        <v>1.276246033172293e-06</v>
+        <v>1.27624601135778e-06</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4758775876426864</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="U23" t="n">
-        <v>0.04505488004373993</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="V23" t="n">
-        <v>8.11313329537693</v>
+        <v>8.113133295376661</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.274815161206213e-05</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="X23" t="n">
-        <v>0.01202133708507474</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="Y23" t="n">
-        <v>-1.276246032599108e-06</v>
+        <v>-1.276246011702428e-06</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.4768655535131607</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.01500508180225687</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.114175479580929</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.274815160420837e-05</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.01202133708507473</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.276246033172293e-06</v>
+        <v>1.27624601135778e-06</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.4758775876426864</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.04505488004373993</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="AH23" t="n">
-        <v>-123.4988281739643</v>
+        <v>-123.4988281741971</v>
       </c>
       <c r="AI23" t="n">
-        <v>12.49725030896388</v>
+        <v>12.49725030898538</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-394.0773917252902</v>
+        <v>-394.0773917252354</v>
       </c>
       <c r="AK23" t="n">
-        <v>-5.448588832704337e-06</v>
+        <v>-5.448588741532367e-06</v>
       </c>
       <c r="AL23" t="n">
-        <v>1576.857887959274</v>
+        <v>1576.857887959055</v>
       </c>
       <c r="AM23" t="n">
-        <v>16.65572241132731</v>
+        <v>16.65572241141295</v>
       </c>
       <c r="AN23" t="n">
-        <v>123.4988281739643</v>
+        <v>123.4988281741971</v>
       </c>
       <c r="AO23" t="n">
-        <v>-12.49725030896388</v>
+        <v>-12.49725030898538</v>
       </c>
       <c r="AP23" t="n">
-        <v>394.0773917252902</v>
+        <v>394.0773917252354</v>
       </c>
       <c r="AQ23" t="n">
-        <v>5.448588832704337e-06</v>
+        <v>5.448588741532367e-06</v>
       </c>
       <c r="AR23" t="n">
-        <v>1575.761245843047</v>
+        <v>1575.761245842828</v>
       </c>
       <c r="AS23" t="n">
-        <v>83.32228006038376</v>
+        <v>83.32228006047011</v>
       </c>
     </row>
     <row r="24">
@@ -7049,7 +7049,7 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0001054962997791678</v>
+        <v>0.0001054962997791679</v>
       </c>
       <c r="G24" t="n">
         <v>1.318703747239598e-05</v>
@@ -7058,115 +7058,115 @@
         <v>12.50131152383139</v>
       </c>
       <c r="I24" t="n">
-        <v>2637.407494479196</v>
+        <v>2637.407494479197</v>
       </c>
       <c r="J24" t="n">
-        <v>8.114175479580929</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="K24" t="n">
-        <v>5.274815160420837e-05</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.01202133708507473</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="M24" t="n">
-        <v>1.276246033172293e-06</v>
+        <v>1.27624601135778e-06</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4758775876426864</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="O24" t="n">
-        <v>0.04505488004373993</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="P24" t="n">
-        <v>8.114175479584461</v>
+        <v>8.114175479585626</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.274814817495947e-05</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.0120213370850764</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.276246290880136e-06</v>
+        <v>-1.276246312679776e-06</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4758775876429612</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.04505488004286866</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="V24" t="n">
-        <v>-5.274815160420837e-05</v>
+        <v>-5.274815212167277e-05</v>
       </c>
       <c r="W24" t="n">
-        <v>8.114175479580929</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.01202133708507473</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.4758775876426864</v>
+        <v>-0.4758775876426199</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.276246033172293e-06</v>
+        <v>1.27624601135778e-06</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.04505488004373993</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="AB24" t="n">
-        <v>5.274814817495947e-05</v>
+        <v>5.27481476574951e-05</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.114175479584461</v>
+        <v>8.114175479585626</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.0120213370850764</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.4758775876429612</v>
+        <v>-0.475877587642983</v>
       </c>
       <c r="AF24" t="n">
-        <v>-1.276246290880136e-06</v>
+        <v>-1.276246312679776e-06</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.04505488004286866</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="AH24" t="n">
         <v>-12.50131152383139</v>
       </c>
       <c r="AI24" t="n">
-        <v>-100.0000000000048</v>
+        <v>-100.0000000000263</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.074449418325685e-10</v>
+        <v>1.254654333985444e-10</v>
       </c>
       <c r="AK24" t="n">
-        <v>5.864198016070077e-13</v>
+        <v>7.751577157932843e-13</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.001416632810069984</v>
+        <v>0.001416632737978864</v>
       </c>
       <c r="AM24" t="n">
-        <v>-83.32241648528483</v>
+        <v>-83.32241648536987</v>
       </c>
       <c r="AN24" t="n">
         <v>12.50131152383139</v>
       </c>
       <c r="AO24" t="n">
-        <v>-99.99999999999523</v>
+        <v>-99.99999999997374</v>
       </c>
       <c r="AP24" t="n">
-        <v>-1.074449418325685e-10</v>
+        <v>-1.254654333985444e-10</v>
       </c>
       <c r="AQ24" t="n">
-        <v>-5.864198016070077e-13</v>
+        <v>-7.751577157932843e-13</v>
       </c>
       <c r="AR24" t="n">
-        <v>-0.001416633669628631</v>
+        <v>-0.00141663374170233</v>
       </c>
       <c r="AS24" t="n">
-        <v>83.32241648524663</v>
+        <v>83.32241648516023</v>
       </c>
     </row>
     <row r="25">
@@ -7188,124 +7188,124 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.001042184204003149</v>
+        <v>0.001042184204001373</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001302730255003937</v>
+        <v>0.0001302730255001716</v>
       </c>
       <c r="H25" t="n">
-        <v>123.4988281743732</v>
+        <v>123.4988281741627</v>
       </c>
       <c r="I25" t="n">
-        <v>26054.60510007873</v>
+        <v>26054.60510003432</v>
       </c>
       <c r="J25" t="n">
-        <v>8.114175479584461</v>
+        <v>8.114175479585626</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.274814817495947e-05</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0120213370850764</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.276246290880136e-06</v>
+        <v>-1.276246312679776e-06</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4758775876429612</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.04505488004286866</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="P25" t="n">
-        <v>8.113133295380457</v>
+        <v>8.113133295381624</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.274814816710414e-05</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="R25" t="n">
-        <v>0.01202133708507639</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="S25" t="n">
-        <v>1.276246291459122e-06</v>
+        <v>1.276246312356512e-06</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4768655535134355</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="U25" t="n">
-        <v>0.01500508180312803</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="V25" t="n">
-        <v>-8.114175479584461</v>
+        <v>-8.114175479585626</v>
       </c>
       <c r="W25" t="n">
-        <v>-5.274814817495947e-05</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0120213370850764</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.276246290880136e-06</v>
+        <v>1.276246312679776e-06</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.4758775876429612</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.04505488004286866</v>
+        <v>0.04505488004271615</v>
       </c>
       <c r="AB25" t="n">
-        <v>-8.113133295380457</v>
+        <v>-8.113133295381624</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.274814816710414e-05</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.01202133708507639</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="AE25" t="n">
-        <v>-1.276246291459122e-06</v>
+        <v>-1.276246312356512e-06</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.4768655535134355</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.01500508180312803</v>
+        <v>-0.01500508180328185</v>
       </c>
       <c r="AH25" t="n">
-        <v>-123.4988281744299</v>
+        <v>-123.4988281741971</v>
       </c>
       <c r="AI25" t="n">
-        <v>12.49725030895394</v>
+        <v>12.49725030893287</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-394.0773917255186</v>
+        <v>-394.0773917255378</v>
       </c>
       <c r="AK25" t="n">
-        <v>5.448589935378031e-06</v>
+        <v>5.448590026519767e-06</v>
       </c>
       <c r="AL25" t="n">
-        <v>1575.761245843961</v>
+        <v>1575.761245844037</v>
       </c>
       <c r="AM25" t="n">
-        <v>83.32228006034393</v>
+        <v>83.32228006026035</v>
       </c>
       <c r="AN25" t="n">
-        <v>123.4988281744299</v>
+        <v>123.4988281741971</v>
       </c>
       <c r="AO25" t="n">
-        <v>-12.49725030895394</v>
+        <v>-12.49725030893287</v>
       </c>
       <c r="AP25" t="n">
-        <v>394.0773917255186</v>
+        <v>394.0773917255378</v>
       </c>
       <c r="AQ25" t="n">
-        <v>-5.448589935378031e-06</v>
+        <v>-5.448590026519767e-06</v>
       </c>
       <c r="AR25" t="n">
-        <v>1576.857887960188</v>
+        <v>1576.857887960265</v>
       </c>
       <c r="AS25" t="n">
-        <v>16.6557224112876</v>
+        <v>16.65572241120256</v>
       </c>
     </row>
     <row r="26">
@@ -7327,124 +7327,124 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0001054548126048011</v>
+        <v>-0.0001054548126048016</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.318185157560014e-05</v>
+        <v>-1.318185157560019e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>-12.49639529366893</v>
+        <v>-12.49639529366899</v>
       </c>
       <c r="I26" t="n">
-        <v>-2636.370315120028</v>
+        <v>-2636.370315120039</v>
       </c>
       <c r="J26" t="n">
-        <v>11.24253477912691</v>
+        <v>11.24253477912758</v>
       </c>
       <c r="K26" t="n">
-        <v>5.272740356380378e-05</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01403178333646527</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.886832883124274e-07</v>
+        <v>-2.886833036039658e-07</v>
       </c>
       <c r="N26" t="n">
-        <v>0.2774101967683359</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="O26" t="n">
-        <v>0.01500512856519697</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="P26" t="n">
-        <v>11.24253477912112</v>
+        <v>11.2425347791201</v>
       </c>
       <c r="Q26" t="n">
-        <v>-5.272740904099736e-05</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="R26" t="n">
-        <v>0.01403178333646289</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="S26" t="n">
-        <v>2.886835082336281e-07</v>
+        <v>2.886834930193329e-07</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2774101967680513</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.01500512856379087</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="V26" t="n">
-        <v>5.272740356380378e-05</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="W26" t="n">
-        <v>-11.24253477912691</v>
+        <v>-11.24253477912758</v>
       </c>
       <c r="X26" t="n">
-        <v>0.01403178333646527</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.2774101967683359</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.886832883124274e-07</v>
+        <v>2.886833036039658e-07</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01500512856519697</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="AB26" t="n">
-        <v>-5.272740904099736e-05</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="AC26" t="n">
-        <v>-11.24253477912112</v>
+        <v>-11.2425347791201</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.01403178333646289</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.2774101967680513</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="AF26" t="n">
-        <v>-2.886835082336281e-07</v>
+        <v>-2.886834930193329e-07</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.01500512856379087</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="AH26" t="n">
-        <v>12.49639529366894</v>
+        <v>12.49639529366899</v>
       </c>
       <c r="AI26" t="n">
-        <v>-1.70530256582424e-11</v>
+        <v>-4.843059286940843e-11</v>
       </c>
       <c r="AJ26" t="n">
-        <v>9.179013105153899e-11</v>
+        <v>7.886364625849396e-11</v>
       </c>
       <c r="AK26" t="n">
-        <v>6.076250613773482e-13</v>
+        <v>4.087841176669826e-13</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.0003204382049224463</v>
+        <v>0.0003204382566711034</v>
       </c>
       <c r="AM26" t="n">
-        <v>16.65569270651849</v>
+        <v>16.65569270639389</v>
       </c>
       <c r="AN26" t="n">
-        <v>-12.49639529366894</v>
+        <v>-12.49639529366899</v>
       </c>
       <c r="AO26" t="n">
-        <v>1.70530256582424e-11</v>
+        <v>4.843059286940843e-11</v>
       </c>
       <c r="AP26" t="n">
-        <v>-9.179013105153899e-11</v>
+        <v>-7.886364625849396e-11</v>
       </c>
       <c r="AQ26" t="n">
-        <v>-6.076250613773482e-13</v>
+        <v>-4.087841176669826e-13</v>
       </c>
       <c r="AR26" t="n">
-        <v>-0.0003204389392434948</v>
+        <v>-0.0003204388875802733</v>
       </c>
       <c r="AS26" t="n">
-        <v>-16.65569270665674</v>
+        <v>-16.65569270678225</v>
       </c>
     </row>
     <row r="27">
@@ -7478,112 +7478,112 @@
         <v>27850.73743223343</v>
       </c>
       <c r="J27" t="n">
-        <v>11.24253477912112</v>
+        <v>11.2425347791201</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.272740904099736e-05</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01403178333646289</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="M27" t="n">
-        <v>2.886835082336281e-07</v>
+        <v>2.886834930193329e-07</v>
       </c>
       <c r="N27" t="n">
-        <v>0.2774101967680513</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.01500512856379087</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="P27" t="n">
-        <v>11.24364880861841</v>
+        <v>11.24364880861739</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.27274090296737e-05</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.01403178333646289</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.886835081465285e-07</v>
+        <v>-2.886834933623841e-07</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2818139420128695</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="U27" t="n">
-        <v>0.04505493137067544</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="V27" t="n">
-        <v>11.24253477912112</v>
+        <v>11.2425347791201</v>
       </c>
       <c r="W27" t="n">
-        <v>-5.272740904099736e-05</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="X27" t="n">
-        <v>0.01403178333646289</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.886835082336281e-07</v>
+        <v>2.886834930193329e-07</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.2774101967680513</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.01500512856379087</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="AB27" t="n">
-        <v>11.24364880861841</v>
+        <v>11.24364880861739</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.27274090296737e-05</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.01403178333646289</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="AE27" t="n">
-        <v>-2.886835081465285e-07</v>
+        <v>-2.886834933623841e-07</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.2818139420128695</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.04505493137067544</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="AH27" t="n">
         <v>-132.0124954287894</v>
       </c>
       <c r="AI27" t="n">
-        <v>12.49725652636022</v>
+        <v>12.49725652639148</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-229.856682860657</v>
+        <v>-229.8566828605958</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.232456515734565e-06</v>
+        <v>1.232456451699434e-06</v>
       </c>
       <c r="AL27" t="n">
-        <v>916.9826528317536</v>
+        <v>916.9826528315087</v>
       </c>
       <c r="AM27" t="n">
-        <v>16.65569284181208</v>
+        <v>16.65569284193676</v>
       </c>
       <c r="AN27" t="n">
         <v>132.0124954287894</v>
       </c>
       <c r="AO27" t="n">
-        <v>-12.49725652636022</v>
+        <v>-12.49725652639148</v>
       </c>
       <c r="AP27" t="n">
-        <v>229.856682860657</v>
+        <v>229.8566828605958</v>
       </c>
       <c r="AQ27" t="n">
-        <v>-1.232456515734565e-06</v>
+        <v>-1.232456451699434e-06</v>
       </c>
       <c r="AR27" t="n">
-        <v>921.8708100535018</v>
+        <v>921.8708100532576</v>
       </c>
       <c r="AS27" t="n">
-        <v>83.32235936906969</v>
+        <v>83.32235936919508</v>
       </c>
     </row>
     <row r="28">
@@ -7605,124 +7605,124 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0001054548126047953</v>
+        <v>0.000105454812604793</v>
       </c>
       <c r="G28" t="n">
-        <v>1.318185157559941e-05</v>
+        <v>1.318185157559913e-05</v>
       </c>
       <c r="H28" t="n">
-        <v>12.49639529366824</v>
+        <v>12.49639529366798</v>
       </c>
       <c r="I28" t="n">
-        <v>2636.370315119882</v>
+        <v>2636.370315119826</v>
       </c>
       <c r="J28" t="n">
-        <v>11.24364880861841</v>
+        <v>11.24364880861739</v>
       </c>
       <c r="K28" t="n">
-        <v>5.27274090296737e-05</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.01403178333646289</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="M28" t="n">
-        <v>-2.886835081465285e-07</v>
+        <v>-2.886834933623841e-07</v>
       </c>
       <c r="N28" t="n">
-        <v>0.2818139420128695</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="O28" t="n">
-        <v>0.04505493137067544</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="P28" t="n">
-        <v>11.2436488086242</v>
+        <v>11.24364880862486</v>
       </c>
       <c r="Q28" t="n">
-        <v>-5.272740357512158e-05</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.01403178333646528</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="S28" t="n">
-        <v>2.88683288419905e-07</v>
+        <v>2.886833031477993e-07</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2818139420131543</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.04505493136926936</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="V28" t="n">
-        <v>-5.27274090296737e-05</v>
+        <v>-5.272740958393851e-05</v>
       </c>
       <c r="W28" t="n">
-        <v>11.24364880861841</v>
+        <v>11.24364880861739</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.01403178333646289</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.2818139420128695</v>
+        <v>-0.2818139420127958</v>
       </c>
       <c r="Z28" t="n">
-        <v>-2.886835081465285e-07</v>
+        <v>-2.886834933623841e-07</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.04505493137067544</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="AB28" t="n">
-        <v>5.272740357512158e-05</v>
+        <v>5.272740302085454e-05</v>
       </c>
       <c r="AC28" t="n">
-        <v>11.2436488086242</v>
+        <v>11.24364880862486</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.01403178333646528</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.2818139420131543</v>
+        <v>-0.2818139420129872</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.88683288419905e-07</v>
+        <v>2.886833031477993e-07</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.04505493136926936</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="AH28" t="n">
-        <v>-12.49639529366824</v>
+        <v>-12.49639529366798</v>
       </c>
       <c r="AI28" t="n">
-        <v>-100.0000000000168</v>
+        <v>-100.0000000000475</v>
       </c>
       <c r="AJ28" t="n">
-        <v>9.171041703837091e-11</v>
+        <v>7.919405605740729e-11</v>
       </c>
       <c r="AK28" t="n">
-        <v>6.078471059822732e-13</v>
+        <v>4.084510507595951e-13</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.000320438938936185</v>
+        <v>-0.0003204388888398558</v>
       </c>
       <c r="AM28" t="n">
-        <v>-83.32235951273137</v>
+        <v>-83.32235951285415</v>
       </c>
       <c r="AN28" t="n">
-        <v>12.49639529366824</v>
+        <v>12.49639529366798</v>
       </c>
       <c r="AO28" t="n">
-        <v>-99.99999999998317</v>
+        <v>-99.99999999995248</v>
       </c>
       <c r="AP28" t="n">
-        <v>-9.171041703837091e-11</v>
+        <v>-7.919405605740729e-11</v>
       </c>
       <c r="AQ28" t="n">
-        <v>-6.078471059822732e-13</v>
+        <v>-4.084510507595951e-13</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.0003204382052528487</v>
+        <v>0.0003204382552865191</v>
       </c>
       <c r="AS28" t="n">
-        <v>83.32235951259676</v>
+        <v>83.32235951247489</v>
       </c>
     </row>
     <row r="29">
@@ -7744,124 +7744,124 @@
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>0.001114029497284008</v>
+        <v>0.001114029497285784</v>
       </c>
       <c r="G29" t="n">
-        <v>0.000139253687160501</v>
+        <v>0.0001392536871607231</v>
       </c>
       <c r="H29" t="n">
-        <v>132.012495428155</v>
+        <v>132.0124954283655</v>
       </c>
       <c r="I29" t="n">
-        <v>27850.73743210021</v>
+        <v>27850.73743214461</v>
       </c>
       <c r="J29" t="n">
-        <v>11.2436488086242</v>
+        <v>11.24364880862486</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.272740357512158e-05</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.01403178333646528</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="M29" t="n">
-        <v>2.88683288419905e-07</v>
+        <v>2.886833031477993e-07</v>
       </c>
       <c r="N29" t="n">
-        <v>0.2818139420131543</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.04505493136926936</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="P29" t="n">
-        <v>11.24253477912691</v>
+        <v>11.24253477912758</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.272740356380378e-05</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01403178333646527</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="S29" t="n">
-        <v>-2.886832883124274e-07</v>
+        <v>-2.886833036039658e-07</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2774101967683359</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="U29" t="n">
-        <v>0.01500512856519697</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="V29" t="n">
-        <v>-11.2436488086242</v>
+        <v>-11.24364880862486</v>
       </c>
       <c r="W29" t="n">
-        <v>-5.272740357512158e-05</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01403178333646528</v>
+        <v>0.01403178333646063</v>
       </c>
       <c r="Y29" t="n">
-        <v>-2.88683288419905e-07</v>
+        <v>-2.886833031477993e-07</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.2818139420131543</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.04505493136926936</v>
+        <v>0.04505493136909523</v>
       </c>
       <c r="AB29" t="n">
-        <v>-11.24253477912691</v>
+        <v>-11.24253477912758</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.272740356380378e-05</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.01403178333646527</v>
+        <v>-0.01403178333646062</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.886832883124274e-07</v>
+        <v>2.886833036039658e-07</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.2774101967683359</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.01500512856519697</v>
+        <v>-0.01500512856537014</v>
       </c>
       <c r="AH29" t="n">
-        <v>-132.0124954280909</v>
+        <v>-132.0124954283237</v>
       </c>
       <c r="AI29" t="n">
-        <v>12.49725652632724</v>
+        <v>12.49725652629611</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-229.8566828608935</v>
+        <v>-229.8566828607552</v>
       </c>
       <c r="AK29" t="n">
-        <v>-1.232455577255556e-06</v>
+        <v>-1.232455641335499e-06</v>
       </c>
       <c r="AL29" t="n">
-        <v>921.8708100544479</v>
+        <v>921.870810053895</v>
       </c>
       <c r="AM29" t="n">
-        <v>83.32235936893775</v>
+        <v>83.32235936881273</v>
       </c>
       <c r="AN29" t="n">
-        <v>132.0124954280909</v>
+        <v>132.0124954283237</v>
       </c>
       <c r="AO29" t="n">
-        <v>-12.49725652632724</v>
+        <v>-12.49725652629611</v>
       </c>
       <c r="AP29" t="n">
-        <v>229.8566828608935</v>
+        <v>229.8566828607552</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.232455577255556e-06</v>
+        <v>1.232455641335499e-06</v>
       </c>
       <c r="AR29" t="n">
-        <v>916.9826528326996</v>
+        <v>916.9826528321462</v>
       </c>
       <c r="AS29" t="n">
-        <v>16.65569284168014</v>
+        <v>16.65569284155616</v>
       </c>
     </row>
     <row r="30">
@@ -7883,124 +7883,124 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0001054632224549718</v>
+        <v>-0.0001054632224549705</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.318290280687148e-05</v>
+        <v>-1.318290280687131e-05</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.49739186091416</v>
+        <v>-12.49739186091401</v>
       </c>
       <c r="I30" t="n">
-        <v>-2636.580561374296</v>
+        <v>-2636.580561374263</v>
       </c>
       <c r="J30" t="n">
-        <v>12.76362755076675</v>
+        <v>12.7636275507655</v>
       </c>
       <c r="K30" t="n">
-        <v>5.273160774713402e-05</v>
+        <v>5.273160743815383e-05</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01458744045582377</v>
+        <v>0.01458744045581826</v>
       </c>
       <c r="M30" t="n">
-        <v>1.041021125745989e-07</v>
+        <v>1.041020896839185e-07</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1191579135707582</v>
+        <v>0.1191579135705716</v>
       </c>
       <c r="O30" t="n">
-        <v>0.01500512783927177</v>
+        <v>0.01500512783931789</v>
       </c>
       <c r="P30" t="n">
-        <v>12.76362755075872</v>
+        <v>12.76362755075735</v>
       </c>
       <c r="Q30" t="n">
-        <v>-5.273161470783783e-05</v>
+        <v>-5.273161501681668e-05</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01458744045582099</v>
+        <v>0.01458744045581829</v>
       </c>
       <c r="S30" t="n">
-        <v>-1.041019902353731e-07</v>
+        <v>-1.041020131429611e-07</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1191579135705613</v>
+        <v>0.1191579135705384</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.01500512783739848</v>
+        <v>-0.01500512783735091</v>
       </c>
       <c r="V30" t="n">
-        <v>5.273160774713402e-05</v>
+        <v>5.273160743815383e-05</v>
       </c>
       <c r="W30" t="n">
-        <v>-12.76362755076675</v>
+        <v>-12.7636275507655</v>
       </c>
       <c r="X30" t="n">
-        <v>0.01458744045582377</v>
+        <v>0.01458744045581826</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.1191579135707582</v>
+        <v>0.1191579135705716</v>
       </c>
       <c r="Z30" t="n">
-        <v>-1.041021125745989e-07</v>
+        <v>-1.041020896839185e-07</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.01500512783927177</v>
+        <v>0.01500512783931789</v>
       </c>
       <c r="AB30" t="n">
-        <v>-5.273161470783783e-05</v>
+        <v>-5.273161501681668e-05</v>
       </c>
       <c r="AC30" t="n">
-        <v>-12.76362755075872</v>
+        <v>-12.76362755075735</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.01458744045582099</v>
+        <v>0.01458744045581829</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.1191579135705613</v>
+        <v>0.1191579135705384</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.041019902353731e-07</v>
+        <v>1.041020131429611e-07</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.01500512783739848</v>
+        <v>-0.01500512783735091</v>
       </c>
       <c r="AH30" t="n">
-        <v>12.49739186091416</v>
+        <v>12.49739186091401</v>
       </c>
       <c r="AI30" t="n">
-        <v>-5.616129783447832e-11</v>
+        <v>-2.91038304567337e-11</v>
       </c>
       <c r="AJ30" t="n">
-        <v>5.1213033813724e-11</v>
+        <v>3.185670624457392e-11</v>
       </c>
       <c r="AK30" t="n">
-        <v>4.203304371230843e-13</v>
+        <v>7.083222897108499e-14</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.0001155534819119453</v>
+        <v>-0.000115553404494969</v>
       </c>
       <c r="AM30" t="n">
-        <v>16.65569190032693</v>
+        <v>16.65569190043516</v>
       </c>
       <c r="AN30" t="n">
-        <v>-12.49739186091416</v>
+        <v>-12.49739186091401</v>
       </c>
       <c r="AO30" t="n">
-        <v>5.616129783447832e-11</v>
+        <v>2.91038304567337e-11</v>
       </c>
       <c r="AP30" t="n">
-        <v>-5.1213033813724e-11</v>
+        <v>-3.185670624457392e-11</v>
       </c>
       <c r="AQ30" t="n">
-        <v>-4.203304371230843e-13</v>
+        <v>-7.083222897108499e-14</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.0001155530722067866</v>
+        <v>0.0001155531496422071</v>
       </c>
       <c r="AS30" t="n">
-        <v>-16.65569190077713</v>
+        <v>-16.65569190066799</v>
       </c>
     </row>
     <row r="31">
@@ -8034,112 +8034,112 @@
         <v>17245.24937132265</v>
       </c>
       <c r="J31" t="n">
-        <v>12.76362755075872</v>
+        <v>12.76362755075735</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.273161470783783e-05</v>
+        <v>-5.273161501681668e-05</v>
       </c>
       <c r="L31" t="n">
-        <v>0.01458744045582099</v>
+        <v>0.01458744045581829</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.041019902353731e-07</v>
+        <v>-1.041020131429611e-07</v>
       </c>
       <c r="N31" t="n">
-        <v>0.1191579135705613</v>
+        <v>0.1191579135705384</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.01500512783739848</v>
+        <v>-0.01500512783735091</v>
       </c>
       <c r="P31" t="n">
-        <v>12.76431736073357</v>
+        <v>12.76431736073221</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.273161469785554e-05</v>
+        <v>5.273161502770671e-05</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.01458744045582099</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="S31" t="n">
-        <v>1.041019900625209e-07</v>
+        <v>1.041020126456332e-07</v>
       </c>
       <c r="T31" t="n">
-        <v>0.09905190241357491</v>
+        <v>0.09905190241355175</v>
       </c>
       <c r="U31" t="n">
-        <v>0.04505493222250071</v>
+        <v>0.04505493222254756</v>
       </c>
       <c r="V31" t="n">
-        <v>12.76362755075872</v>
+        <v>12.76362755075735</v>
       </c>
       <c r="W31" t="n">
-        <v>-5.273161470783783e-05</v>
+        <v>-5.273161501681668e-05</v>
       </c>
       <c r="X31" t="n">
-        <v>0.01458744045582099</v>
+        <v>0.01458744045581829</v>
       </c>
       <c r="Y31" t="n">
-        <v>-1.041019902353731e-07</v>
+        <v>-1.041020131429611e-07</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.1191579135705613</v>
+        <v>0.1191579135705384</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.01500512783739848</v>
+        <v>-0.01500512783735091</v>
       </c>
       <c r="AB31" t="n">
-        <v>12.76431736073357</v>
+        <v>12.76431736073221</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.273161469785554e-05</v>
+        <v>5.273161502770671e-05</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.01458744045582099</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.041019900625209e-07</v>
+        <v>1.041020126456332e-07</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.09905190241357491</v>
+        <v>0.09905190241355175</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.04505493222250071</v>
+        <v>0.04505493222254756</v>
       </c>
       <c r="AH31" t="n">
         <v>-81.74248202005401</v>
       </c>
       <c r="AI31" t="n">
-        <v>12.49725630798878</v>
+        <v>12.49725630796159</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-87.79382485852895</v>
+        <v>-87.79382485851036</v>
       </c>
       <c r="AK31" t="n">
-        <v>-4.444354194820428e-07</v>
+        <v>-4.444355165871917e-07</v>
       </c>
       <c r="AL31" t="n">
-        <v>362.3341356262432</v>
+        <v>362.3341356261689</v>
       </c>
       <c r="AM31" t="n">
-        <v>16.65569189871105</v>
+        <v>16.65569189860274</v>
       </c>
       <c r="AN31" t="n">
         <v>81.74248202005401</v>
       </c>
       <c r="AO31" t="n">
-        <v>-12.49725630798878</v>
+        <v>-12.49725630796159</v>
       </c>
       <c r="AP31" t="n">
-        <v>87.79382485852895</v>
+        <v>87.79382485851036</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4.444354194820428e-07</v>
+        <v>4.444355165871917e-07</v>
       </c>
       <c r="AR31" t="n">
-        <v>340.0164632419883</v>
+        <v>340.0164632419138</v>
       </c>
       <c r="AS31" t="n">
-        <v>83.32235856519915</v>
+        <v>83.32235856509004</v>
       </c>
     </row>
     <row r="32">
@@ -8161,124 +8161,124 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0001054632224549722</v>
+        <v>0.000105463222454975</v>
       </c>
       <c r="G32" t="n">
-        <v>1.318290280687152e-05</v>
+        <v>1.318290280687187e-05</v>
       </c>
       <c r="H32" t="n">
-        <v>12.4973918609142</v>
+        <v>12.49739186091453</v>
       </c>
       <c r="I32" t="n">
-        <v>2636.580561374304</v>
+        <v>2636.580561374374</v>
       </c>
       <c r="J32" t="n">
-        <v>12.76431736073357</v>
+        <v>12.76431736073221</v>
       </c>
       <c r="K32" t="n">
-        <v>5.273161469785554e-05</v>
+        <v>5.273161502770671e-05</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.01458744045582099</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="M32" t="n">
-        <v>1.041019900625209e-07</v>
+        <v>1.041020126456332e-07</v>
       </c>
       <c r="N32" t="n">
-        <v>0.09905190241357491</v>
+        <v>0.09905190241355175</v>
       </c>
       <c r="O32" t="n">
-        <v>0.04505493222250071</v>
+        <v>0.04505493222254756</v>
       </c>
       <c r="P32" t="n">
-        <v>12.76431736074161</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="Q32" t="n">
-        <v>-5.273160775711663e-05</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.01458744045582378</v>
+        <v>-0.01458744045581826</v>
       </c>
       <c r="S32" t="n">
-        <v>-1.041021128221863e-07</v>
+        <v>-1.041020899760041e-07</v>
       </c>
       <c r="T32" t="n">
-        <v>0.09905190241377351</v>
+        <v>0.09905190241358573</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.04505493222062767</v>
+        <v>-0.04505493222058038</v>
       </c>
       <c r="V32" t="n">
-        <v>-5.273161469785554e-05</v>
+        <v>-5.273161502770671e-05</v>
       </c>
       <c r="W32" t="n">
-        <v>12.76431736073357</v>
+        <v>12.76431736073221</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.01458744045582099</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.09905190241357491</v>
+        <v>-0.09905190241355175</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.041019900625209e-07</v>
+        <v>1.041020126456332e-07</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.04505493222250071</v>
+        <v>0.04505493222254756</v>
       </c>
       <c r="AB32" t="n">
-        <v>5.273160775711663e-05</v>
+        <v>5.273160742726827e-05</v>
       </c>
       <c r="AC32" t="n">
-        <v>12.76431736074161</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.01458744045582378</v>
+        <v>-0.01458744045581826</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.09905190241377351</v>
+        <v>-0.09905190241358573</v>
       </c>
       <c r="AF32" t="n">
-        <v>-1.041021128221863e-07</v>
+        <v>-1.041020899760041e-07</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.04505493222062767</v>
+        <v>-0.04505493222058038</v>
       </c>
       <c r="AH32" t="n">
-        <v>-12.4973918609142</v>
+        <v>-12.49739186091453</v>
       </c>
       <c r="AI32" t="n">
-        <v>-100.0000000000568</v>
+        <v>-100.0000000000293</v>
       </c>
       <c r="AJ32" t="n">
-        <v>5.138911518542955e-11</v>
+        <v>3.218251569913049e-11</v>
       </c>
       <c r="AK32" t="n">
-        <v>4.23938661953116e-13</v>
+        <v>7.255307465925398e-14</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.0001155530715442055</v>
+        <v>0.0001155531482243991</v>
       </c>
       <c r="AM32" t="n">
-        <v>-83.32235856762449</v>
+        <v>-83.32235856751535</v>
       </c>
       <c r="AN32" t="n">
-        <v>12.4973918609142</v>
+        <v>12.49739186091453</v>
       </c>
       <c r="AO32" t="n">
-        <v>-99.99999999994316</v>
+        <v>-99.99999999997067</v>
       </c>
       <c r="AP32" t="n">
-        <v>-5.138911518542955e-11</v>
+        <v>-3.218251569913049e-11</v>
       </c>
       <c r="AQ32" t="n">
-        <v>-4.23938661953116e-13</v>
+        <v>-7.255307465925398e-14</v>
       </c>
       <c r="AR32" t="n">
-        <v>-0.0001155534826580151</v>
+        <v>-0.0001155534056854128</v>
       </c>
       <c r="AS32" t="n">
-        <v>83.32235856716974</v>
+        <v>83.32235856727888</v>
       </c>
     </row>
     <row r="33">
@@ -8300,124 +8300,124 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>0.000689809974856459</v>
+        <v>0.0006898099748582354</v>
       </c>
       <c r="G33" t="n">
-        <v>8.622624685705738e-05</v>
+        <v>8.622624685727942e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>81.7424820204904</v>
+        <v>81.74248202070089</v>
       </c>
       <c r="I33" t="n">
-        <v>17245.24937141148</v>
+        <v>17245.24937145588</v>
       </c>
       <c r="J33" t="n">
-        <v>12.76431736074161</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.273160775711663e-05</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.01458744045582378</v>
+        <v>-0.01458744045581826</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.041021128221863e-07</v>
+        <v>-1.041020899760041e-07</v>
       </c>
       <c r="N33" t="n">
-        <v>0.09905190241377351</v>
+        <v>0.09905190241358573</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.04505493222062767</v>
+        <v>-0.04505493222058038</v>
       </c>
       <c r="P33" t="n">
-        <v>12.76362755076675</v>
+        <v>12.7636275507655</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.273160774713402e-05</v>
+        <v>5.273160743815383e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>0.01458744045582377</v>
+        <v>0.01458744045581826</v>
       </c>
       <c r="S33" t="n">
-        <v>1.041021125745989e-07</v>
+        <v>1.041020896839185e-07</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1191579135707582</v>
+        <v>0.1191579135705716</v>
       </c>
       <c r="U33" t="n">
-        <v>0.01500512783927177</v>
+        <v>0.01500512783931789</v>
       </c>
       <c r="V33" t="n">
-        <v>-12.76431736074161</v>
+        <v>-12.76431736074036</v>
       </c>
       <c r="W33" t="n">
-        <v>-5.273160775711663e-05</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="X33" t="n">
-        <v>0.01458744045582378</v>
+        <v>0.01458744045581826</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.041021128221863e-07</v>
+        <v>1.041020899760041e-07</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.09905190241377351</v>
+        <v>0.09905190241358573</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.04505493222062767</v>
+        <v>0.04505493222058038</v>
       </c>
       <c r="AB33" t="n">
-        <v>-12.76362755076675</v>
+        <v>-12.7636275507655</v>
       </c>
       <c r="AC33" t="n">
-        <v>5.273160774713402e-05</v>
+        <v>5.273160743815383e-05</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.01458744045582377</v>
+        <v>-0.01458744045581826</v>
       </c>
       <c r="AE33" t="n">
-        <v>-1.041021125745989e-07</v>
+        <v>-1.041020896839185e-07</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.1191579135707582</v>
+        <v>0.1191579135705716</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.01500512783927177</v>
+        <v>-0.01500512783931789</v>
       </c>
       <c r="AH33" t="n">
-        <v>-81.74248202051967</v>
+        <v>-81.7424820207525</v>
       </c>
       <c r="AI33" t="n">
-        <v>12.49725630787598</v>
+        <v>12.49725630790358</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-87.793824858693</v>
+        <v>-87.79382485853831</v>
       </c>
       <c r="AK33" t="n">
-        <v>4.44435942673907e-07</v>
+        <v>4.444358450432963e-07</v>
       </c>
       <c r="AL33" t="n">
-        <v>340.0164632426455</v>
+        <v>340.0164632420261</v>
       </c>
       <c r="AM33" t="n">
-        <v>83.32235856474811</v>
+        <v>83.32235856485785</v>
       </c>
       <c r="AN33" t="n">
-        <v>81.74248202051967</v>
+        <v>81.7424820207525</v>
       </c>
       <c r="AO33" t="n">
-        <v>-12.49725630787598</v>
+        <v>-12.49725630790358</v>
       </c>
       <c r="AP33" t="n">
-        <v>87.793824858693</v>
+        <v>87.79382485853831</v>
       </c>
       <c r="AQ33" t="n">
-        <v>-4.44435942673907e-07</v>
+        <v>-4.444358450432963e-07</v>
       </c>
       <c r="AR33" t="n">
-        <v>362.3341356268984</v>
+        <v>362.3341356262804</v>
       </c>
       <c r="AS33" t="n">
-        <v>16.65569189825973</v>
+        <v>16.65569189837078</v>
       </c>
     </row>
   </sheetData>
